--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20950A98-EF30-4C7B-83CF-DD45714555DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CC4B1-5884-4FA8-B789-522E5E77B996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="417">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1463,6 +1463,30 @@
   </si>
   <si>
     <t xml:space="preserve">Instalación de roseta fuera de norma a petición de cliente, técnico ocupa herramientas one click según procedimiento </t>
+  </si>
+  <si>
+    <t>1-3NSYNSJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profesor fuentes maturana 5550, Quinta Normal </t>
+  </si>
+  <si>
+    <t>Victor Poblete</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1A1HdoZV4K2-AV-NhQvzQZXyfq2e4TI7J</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PTIDd-AS6cynot9xfLospy-xuV3Vkr1A</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OVqFnS5KM8dMxyy7T1aZEPfk1W1x8s1F</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vKkd3BF0vSLMJrZVAjhV9LScvzP4jr0M</t>
+  </si>
+  <si>
+    <t>Se conversa sobre indicador de calidad para su mejora</t>
   </si>
 </sst>
 </file>
@@ -2315,8 +2339,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ46" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ46" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ47" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ47" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
@@ -2566,7 +2590,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ46"/>
+  <dimension ref="A1:AJ47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -7135,175 +7159,280 @@
         <v>-</v>
       </c>
     </row>
+    <row r="47" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46279.750844733797</v>
+      </c>
+      <c r="B47" s="10">
+        <v>8</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="T47" s="3">
+        <v>4</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="V47" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="W47" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="X47" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH47" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI47" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ47" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{DDBFDC9A-1F33-4E03-ADB9-6268541CBC04}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{37A63072-5673-4FDB-B792-AD2E8A8E369E}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{7560B42B-76B0-4E97-BCA7-F8FAEBD33588}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{F154A939-7995-471B-8AB0-4A7753B33551}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{E0F44651-48B1-4B38-BC1D-47CA23FF8C0B}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{BE30D6A7-46DB-4F6C-AD72-1752CB939B95}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{CA167C38-8F38-4D12-AE3E-36A962686EEB}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{D097F255-C057-4EA6-9959-F5E9FE6D4DAF}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{667BF350-5C7E-4BED-BAB4-B70AD633AC2B}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{F204F857-ABAC-4851-9133-5468969ED01B}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{DBB757EF-35DB-4D87-BB71-25929AE0A4DD}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{6CFA9AA9-5BF6-4FEE-B7D1-7CD1E09C49B2}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{2064B47C-688E-4391-B5A3-325534D4FDE9}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{01CC9F0F-7D6E-4F7E-A1BF-0E1F848836E4}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{AB478435-471C-4371-91AD-4C7AE618A5FF}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{1EA9BA0C-5718-40EC-809B-97CAF885DFC4}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{0AACC061-E43D-4813-BE65-7C3A318243DE}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{AB734527-DA29-4B4E-85CD-8A81E8978831}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{F0234C13-FC96-4BFA-B4E9-1276D809C0EB}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{56890858-0899-46E3-84C8-28783176AD09}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{F3DFDF6D-9060-4F4C-A52E-3C3B20622D9A}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{8556F2B1-6E7D-4DEF-97C4-C23C1A13369C}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{55EF873B-9B2F-4306-98AB-4564E0A9F058}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{451F7615-519A-4673-9E53-5786221C25D1}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{688A3B1F-0BA4-4781-A0CB-6809A29080F9}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{317B89F5-DC8F-4170-B014-3CA990B1D0B1}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{259F6E59-0FB6-4428-84F6-5BCCED13C6EE}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{9C383BA3-6457-442F-B94C-BB4E0F80489C}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{1AE8D042-D7A5-4359-8C8B-0C7882A8659B}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{D5F855A3-32AB-452E-B7DA-6D286F75E434}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{2E98CCEC-C8DB-4CA1-8DF1-BD9EA71F5584}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{981B028C-BF4C-4551-B014-DB0DE6F682B9}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{79DCB601-B9E4-447B-A3E1-8B9A85B7F79D}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{369FE38C-C785-47EA-AF50-8E5D73FA114B}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{40241DDA-871F-41D8-9A1B-52D63CC16BE9}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{DEF10765-457C-487F-B247-FBFF1096ABA9}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{511B6544-9065-40F8-9721-670D67904B82}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{0B0DD9D6-D5CE-4586-8C57-D30A19CBF4ED}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{4FD65566-231D-43FE-814D-A35E38AA825B}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{7A2B9253-086D-46A5-803B-86583BB00CF6}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{DD0E201A-EB33-4386-9B23-38ABD9888947}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{599D673E-2ECA-4F67-8CEF-7EAA3021EF76}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{4FED9D57-B887-4464-B6B5-6DC77B90C335}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{C3C596D1-FEE6-40D1-BE1D-4AC2AABBF423}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{3D276E5B-D504-4EA8-8D39-BD14994B4C01}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{F471B65E-2254-4F7B-94EA-5C992C4CEAB7}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{2C34D939-BB6F-4D47-8AB3-5B0523DB10A4}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{7C7F9036-1BAA-47F0-A89D-0D42B5B7BB78}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{3DBA7FA1-36F8-4524-9900-B98697EF4E97}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{CABBCBCE-D583-4F73-B775-C0F0957771C2}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{C0EE8CB2-B23C-450F-B351-6E80558FB718}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{C4205633-57D5-4DD6-B7A0-9A6570C8C800}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{58F70ED4-8861-460A-A941-26C04771A6A5}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{C8972FD6-D88E-42B6-AE2A-2C9524BFF4EC}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{9CA89E4E-C7A6-4970-9900-1A55FA3DC74F}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{BC35CF3E-F8D9-42CA-9322-D66D328A3696}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{C4C2803B-118B-450D-A8E6-2B4E4078B4F4}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{0C50FE68-3073-4AD3-8C30-B01793E6DB01}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{9503D9B1-5A1D-4598-8B97-E87252E55B5C}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{FA52065B-FFCA-4253-8A9B-EAD6B5C700A9}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{7964542F-BD5D-420C-A653-0D406FD2F1B9}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{7737848E-5BF0-4DB7-BCFE-0801402157EC}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{0408DD99-6506-44EC-8379-D45F1F5FD787}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{0D4E291B-BBFF-4EDA-8258-82C66ACE68E0}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{BA91BCF2-1BCB-4C42-962B-B691DDE2B95E}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{439AD546-3F59-4679-9D74-50376B859BA6}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{7022BE44-7059-48B8-86D1-5400A32CEC42}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{0118C6BD-6D3E-4915-A88C-386FED5BAF52}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{807BD08A-F505-4466-A344-0A62A4A7A36C}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{26B2223F-93EA-4217-8D6A-28A705215955}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{6670DE45-74D5-4C34-8FC6-E11EC6125E35}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{E7CA74E5-2CDA-4C8A-B422-C818EEE83613}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{35AC1A89-9AA0-4F4B-A2A1-0E1FFE625852}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{918F7188-5576-42ED-9530-B4A43E4C4CC5}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{5CF6C3D7-EAEB-47CC-94F7-B6285EB6DD42}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{E1A2DA5B-AE8E-442A-967D-FDB628BDC924}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{C49F6890-93B4-4E5B-9FC4-A38171C07963}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{D0082366-8FFE-4760-B2F8-B02329DFA5B9}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{E5CB28BD-F8BD-4AD1-9DDF-EF68BF03A553}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{7FE4F5EC-3B3C-4BC0-A2E8-FB5BF28FE374}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{92478EA1-AE14-490F-8487-78619C16FBC3}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{B4C42EF2-F878-4CAE-9E4C-8027219B6D30}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{88605C68-F3D8-459A-B2BD-705156EB7A25}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{8F375607-EA18-4BDB-B936-3E8B3162395A}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{0B100F8D-4A99-44F7-9AAA-18AFF11963B0}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{7378445F-63C1-4933-BCBB-4217A8376AEF}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{609408E4-D310-4AAA-AE0F-491F2C7E0306}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{12A85933-7B62-4251-9DDD-2762425C87E4}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{D5FD3A1B-BB6A-4F38-B4F5-B18203EDF7EF}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{8F4C6928-FD68-4C0C-BEDD-8EF3FA59C8A6}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{D2CA4097-F182-47FC-BFE4-486A9446141F}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{30C333E4-51FD-42F8-85AE-3A2B17819CDD}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{C697959B-FEC2-4EEE-A464-12ACE2E4E6B0}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{14148B04-9C03-446D-9710-511F451BF5CD}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{F0CD0B32-7277-4B8E-9E9A-60E412EF605A}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{12206559-7A39-4CC6-AD1B-46116C490ED1}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{6F08EAFD-EF61-4B8E-8623-872BB46F1743}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{A30CDA79-83F0-4102-8F2E-49EE403D73AD}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{A1D6CA62-5AB4-4D99-8AA5-C457C7C96E23}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{3A5FF30B-3B14-449C-8674-927250ED0F19}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{556288A5-3ED8-4D40-8642-6225D91BE6A3}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{67AA8B3A-B50A-4C46-BB41-BD1500700BC9}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{6C80FFCB-6C9C-4C1D-8F97-5D5ED33D2E04}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{C0CAE8AE-8C4D-4FB5-8835-2732415A5848}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{62093E28-603B-4C75-9AD9-0FA8A8EAA92B}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{C93E48BF-A4E2-40E5-B794-44BE748FECFF}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{9A37D409-BB8D-43E2-9E67-7E22C38262DE}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{0B6855FF-AEA8-4429-96A9-EB840E2AC548}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{851C25A1-3A5D-49CA-90A9-2C07A5FC2D31}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{BFC72F42-BD63-490F-9A5F-249304ACAB94}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{F4ABDE7E-3849-4EB2-B359-92308053C2D0}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{39CC47C5-E27C-4D15-8366-18995F694D4D}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{0973F0A0-F246-4135-91C3-BCDB4022B69B}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{E0627294-079F-4D93-B0AB-680BCEBF04A7}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{1EA8C8C5-17CF-4AB6-86B3-B940AF53AF04}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{5CB991D7-EB0F-49B9-A1CC-E7B517EA7497}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{258784B4-7D62-4686-8FD9-268198C047EE}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{BA6E21FF-669A-4A62-9870-FF818366D7D0}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{3DC8FFAB-734A-4314-B54F-EABF89868C02}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{708568FB-C225-4F6E-912F-4A1B806A20BB}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{803E7794-076D-464A-A089-090F522374F7}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{AC14DA8F-4D2D-477C-995D-3F439F582B01}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{45BF6B29-0223-4AB2-9A03-DD51B15C078D}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{F03719BF-409D-4772-9EB1-2AB86F16F6A3}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{BFCFD6BE-B507-4DB3-AD20-BB6C76F2B6DC}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{D5530399-BF1B-44BD-AB3D-48D6EC63C5C9}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{D9E3AFCE-64EE-4B46-A602-4A93A24F3D28}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{6DEDB9B2-2770-4F58-A2D8-3FE4D10D8944}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{342EE9B3-57E7-4AE4-B762-857DBF54E92A}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{8819762E-1ABD-4D66-815D-DAE1FA03FBEB}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{C94EA869-5876-452F-8E01-3F8A6576CE73}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{FEA34FE3-C2C4-44DA-B716-9AC6B69887C8}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{01C97428-0630-471D-B216-C8B7A50A7AD9}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{A419126A-D3A6-479C-9830-F66D1F8BDBA2}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{894CEE8B-6F6D-4AA9-AAFB-9091582EFB9E}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{E94F2D77-5925-45AF-BA6B-5FC386EF2E67}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{F7C88AB4-B05F-4073-B49E-F0DAEF821069}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{133C79DA-F126-4C46-91CF-F10029D7BDD3}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{2F1E2530-0B87-418D-B751-59BCE3079115}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{5D174CDA-B2C8-498C-B13C-10CA0C1A712B}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{22539A30-A9BC-4892-B2EA-5C0CC44271B1}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{9435BECE-4C2E-4F25-BFAF-D82CF6494C4C}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{5FF4DCC7-15FF-433C-8914-E61CED61C49D}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{93C64831-21F0-4156-98CB-896CF9CC9FC8}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{51742480-CF1F-4E62-8BE1-3ADC4C9D3592}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{B68BE086-7928-4795-BFA9-6C99CFA086BE}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{6AAC6E43-1BEB-476D-B176-E9829F783F80}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{A7ECA785-BF1B-4155-B02C-F71259BE6504}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{68405735-469D-4C0E-A149-088FF907236A}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{18AA080B-C5EB-4482-B3DB-6C751E23CE57}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{CBEAE434-A402-4793-B945-B8843C6B78C2}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{D0A90D49-1628-4899-A82D-E8D91504C00B}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{40CB3DF2-5944-4898-997F-2E97DDE9EFF1}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{87194BE9-0DE4-4324-AC6A-991E697C9563}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{B293FE62-397B-48FB-96C8-EC7EEA85D7F2}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{70FFD98F-2A2C-4FFA-BD86-BAD6C4427400}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{0FCF52BF-D2C2-43A3-9530-E51FD88E85CB}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{96D1697A-64AC-4375-9702-061A649B6AFA}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{147C99A2-B5D0-4E67-8FA0-C541DB4A37AE}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{A9A315A8-117C-49B6-97C1-92EE0CB108EC}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{1E94CBC7-253C-414C-A9ED-24476AAFA640}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{F96F9756-2F53-48EF-B45F-CE45431B096E}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{5699F85F-7D2C-40DD-89DC-0A18973B2087}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{A3BDA528-E039-464C-BCCB-C538E9C0DE24}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{889AB803-68E1-4DF7-A450-F1E897DD9B2F}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{8E59A139-8EA0-42CC-A35A-68F2AB663890}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{4FE3177B-EE5D-41F0-B5C6-6C45AF81F5C6}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{A10D6A51-AD85-497C-AB3F-BC05714A98FE}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{62FF0B2F-4073-4CA6-89DC-D46C9623376F}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{E91EADA2-1D61-483B-8350-831F7CC58B2C}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{AFBF74EF-1CFF-408E-8C03-843E1530D31F}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{BA28C2D8-678C-4976-8ACC-1D6256602791}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{B90B30F8-61E2-4951-8091-1BDCCF2EFB25}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{D6B98549-7A61-46D2-AE02-85005264E4D5}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{30A4FE53-F4B6-4539-AEC4-7E9971DCC4A7}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{45CF8489-0158-4FA7-848E-C09C90BF8D5C}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{B612D259-9458-4040-B4BF-5811DACDDA5A}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{DF5166B2-BDE4-42F8-8DDB-D745F2446BDA}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{B13CC9BA-0B60-4093-A766-ABCC348E17C2}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{7BAA6812-2F93-44F5-85DC-7BEB44C4CB7D}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{D9E7982E-71A8-4ACA-ABB7-EACDCF00A257}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{C7AA25DB-FB4E-4FD8-8EDB-E0AFAFBF02A7}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{D961B604-A825-4762-A8BE-02A089FB3598}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{578C29FA-485E-43A9-94C7-7C21BD96A365}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{0115D73C-C7D0-4216-A810-FD23CF7CAED8}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{4EC4C0AA-C611-43E8-B2A0-191EF2DB6559}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{C3E7CA4D-FC83-47D8-A0F8-4005C99F5011}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{EF4E1CF2-C328-462D-B4CA-7858E4EFC27B}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{0934B214-089B-4A89-9386-6C443EDEB517}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{EF797B0E-E058-459D-B38C-6A134FC73EBA}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{845B93D4-EFBE-45B4-9EDE-27838082B42F}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{9D769A39-F138-4815-B1C4-3DA0AC2F44AD}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{CD0F7611-2ADD-4D91-ABC9-C7BDA5F5FF1C}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{E07598E5-7C8A-4F7F-B1AD-E157FD982479}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{AF2A79B4-326B-49EC-AB99-6F58C4CA0482}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{DC79C116-D018-43D9-9184-12CAFFBF9C93}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{A14CD7E3-6AB9-4AA7-8906-C0AD76ABF3D4}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{05A4D5A1-C90E-4F48-868C-1F6FE3E5A40D}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{4A39D551-4C02-4B47-85C3-9FEA22086947}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{30E65DA4-58B1-424D-B0B0-7F2F3DA09C98}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{51FE9DA9-4D59-42F7-97C9-06B499B155D4}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{2542F5CF-45CC-4540-B056-DC8DB3012B29}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{733902D6-FAC7-4F74-9C41-7087775B856F}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{E64BE463-A5CF-45DF-B83C-2FAF407453B2}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{4E9016D8-9894-4240-B16C-7EE44F323F4C}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{97A77373-DFB0-4FC3-86F9-29D5F74774D7}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{30877A24-B197-431A-BAF8-5B45C2CC8FDE}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{152FC0EE-30C0-4E98-BFCA-FE6C5EC1113B}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{3B5EAD5C-5037-4411-8207-71A0A711CA06}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{8B15D634-7723-4F50-8D3D-7918D3562B30}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{82C72397-C6A8-4362-A753-0FEC763585AF}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{835FFBAB-5915-4A33-98E2-AE0D221FA507}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{CB1D1819-F966-4F7D-A451-E9243F8FA04C}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{FDF4AE32-89D9-48E5-A8E7-E0C1B1FF3FDD}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{639AE886-2B20-4986-9BD8-6685AF4D6DE2}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{A65B61FF-1372-4685-A61B-F322780BAD30}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{9D27FC95-7451-43C2-976D-2D3DA941517A}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{9AED71E4-3B5F-4B0C-91B6-0D3FBAA37F58}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{7FD2CC69-618F-4E66-A87D-7AF9BDA6162A}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{D6CE77A3-5304-4A73-A3AE-A712CE884899}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{36B03DFE-2DD3-4B11-B8E2-7D0109837527}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{900FDA53-978E-453B-BE01-37F1033A9A6A}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{077668A2-B1D0-4075-863A-B115DCB98C63}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{0B099CA3-9F07-4E23-8C66-A10691B5497B}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{D036D37A-C6D8-43A8-9852-525A9B9FD672}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{8170681A-F499-4B29-BFA4-6543BA686313}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{1068FAC9-985D-485D-9E30-472F47FE644B}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{F6E36FE3-E6B5-4F0D-8D5F-03F7F35297DC}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{C539F459-9134-411B-A248-083361A58386}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{09EDF299-E413-484A-90A0-4AD6A2BB0B8F}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{562FD80C-C87B-4D15-87E1-BD79CB6A8680}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{39B8CFCE-FD6C-44CC-9A53-B626CAEE63F8}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{0B22791F-55F1-4762-859D-F6A04E75BC62}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{C3347C5D-A4BF-4CE2-8819-9C2DC9C1DDF0}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{E4360199-161C-40C7-8999-B518D6F25E35}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{727EA80A-830B-4D93-AD98-9894A7402C7F}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{07CB413B-9D7C-44F9-B0BE-644797110454}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{944E1793-9A61-45BE-9EAB-A7A30AB9A782}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{45F2360F-0C3E-4120-969C-4EB18BE4F026}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{29483A63-63C9-479C-87FC-B618A89EDC96}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{0539124B-ACD3-419F-B7C5-D8823E90706D}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{0E402A85-9A88-4A0E-82E4-5F3EDFCA205D}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{329CA64D-4F98-40C5-8521-463A4CA2A6E3}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{69C39D3E-0E35-4AC6-82BD-D09EB2509134}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{62DAA299-BD4C-4AEB-BBC2-8EFAA3E56582}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{2B8D7B04-0BB1-4AC2-82AB-C47FEF7F0740}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{83428AF8-7A23-4B0D-A4C9-D325D4D9EAF2}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{4DBAF39B-127C-4976-964C-91C89B6A67A5}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{9186BC07-69BD-4A1C-BA3D-823A95B271DA}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{741B61E2-56A0-417D-8C40-8844A59B2A74}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{108CE046-62A0-44D6-A1A2-C03DCED542D9}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{6D9429FA-C3F4-4B8E-B62D-D2B5896C751B}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{E341FDD6-BEF9-4074-B5E3-07202AE956B3}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{FD70A974-2427-46AC-BDC2-49D3314D627F}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{F8510BB7-2170-494A-B961-F57C79A160EA}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{396962ED-6D7C-41C0-9925-E61EB379BC9D}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{4881B6F4-038E-4A9B-A33D-B1F236CDA7CD}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{F2F6BA5C-CDAE-415C-AF53-D1BA26F7E8DA}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{8103B942-6A26-4E7C-8B09-7D06420C62EF}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{D2D2BEB2-0DD1-4ACC-8439-0A87A25BA1FF}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{FF56658E-C960-4DAF-AAB1-7906BB0BF9D6}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{859DC73B-9BBF-44DC-BFFA-64DFBE28C610}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{D33276F4-DAEF-4CE0-885E-CD393E511F71}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{EA67E6E5-BC65-428F-9676-816D37E66FC6}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{0C5BFFBB-251E-44FE-846A-08C85E0EA91F}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{38997356-0461-4FCD-88EC-D5E0BD60A6B9}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{A7EB0AC6-FDE8-416E-ACA5-131D142B7A32}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{29D0BE29-2021-4A7A-A3E3-8ED0980A3601}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{30E5606E-DF53-4D27-B49A-067D2D47E743}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{167F75AE-F53A-4155-B46B-B1FCC2000EE3}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{26DFD1B9-EBEE-4F6A-8839-91815DE40389}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{5FF5F1A3-994B-4535-A53E-30E42A77A3C8}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{ABEFBDBC-5FBE-4363-9970-37E4BF7520D3}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{CC036FAC-030A-4CE1-824E-FA574C13A522}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{59F6CBA4-390D-48DA-ADCE-3C7320EFB923}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{D08008EC-4BD9-4139-8CA9-11575B822B5F}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{856FD17D-5E6A-4FC0-B38A-92F3C95A6338}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{1F8BDA8A-A1D0-41BE-BEB7-C088E0D2C487}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{92D77070-3E89-4265-B8F9-604C1ABDE62A}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{2FED4E27-1D41-4216-A44B-DC6D0738A45A}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{3B9D45C5-A431-4E1D-BD03-8B26D200BA54}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{57C2A813-4EE6-46E7-8FB6-19EF60B1FBBA}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{8FE5AA19-FF9B-4A2F-8F47-734A4953E2A0}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{0B3C8844-5EF4-44F2-BC0E-8720B9A0219D}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{31B6B77A-F659-438E-AA54-D3C26602A0A9}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{4480104F-7D23-4AC9-A32F-52DD3A0DA153}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{8F6BD3B7-550F-4095-8150-5BB4732E5BF2}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{21FC3562-6CB7-49C7-AE49-2014F880C3CA}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{5C82486D-8E22-482A-84A2-EA64CED92C7F}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{3FFB1355-45CB-443A-8F56-B487734C9F7A}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{19908571-7D51-4F4C-9F10-F6A898FED479}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{C9D44F5F-328C-49B2-8C38-A169F8285C59}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{00DA5FD9-C79E-4BAE-823A-4CFB629F1004}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{59456C50-6CE4-4A01-A548-109CBFCB62C9}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{9FDE962A-2B41-4A6A-83DB-20F50D0FAA68}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{FA8E58CD-1FA7-4FC9-9857-E6C3D9A8BBEE}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{C293CE88-2A95-4923-8303-788E392A2DA4}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{42A19C7F-02BD-472A-A036-DCB1C7DB6CC6}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{FE56AE6C-D25D-417D-8D87-69877314DCCF}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{7FF32E48-E72B-4FF5-B7E4-8AFC9FB3F1DE}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{638DB38A-F7CA-4B6A-A696-FD37E28C9E23}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{07A83185-5611-44FF-B7E2-EC45AC66CF89}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{00579E4D-5A6A-4B16-AA45-178FB731C7B0}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{C27A87D2-BF39-4ED1-B3CF-4F47B60E1310}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{ABE930B5-F03D-4A63-AB03-80871E59C661}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{3E332559-519D-4C69-823D-14ECE0398BF2}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{BFD6B5DF-BFD0-4F4A-B79B-2AF7055FF7CD}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{E57B8BD5-F2A9-4F68-AFD3-A2573AD543D2}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{663D031B-432D-4A6F-AEBB-B27C7C52C5F5}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{8DA76BE4-25D7-4FDE-84D2-286B03D008D8}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{E9F3AB8D-8D06-4D14-A22E-20DE35792B80}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{E66B9718-F6D7-4062-A42E-D398067FC39F}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{A519EC7C-6528-4B2E-BBD9-516DC462FCFB}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{40C79F17-24F8-46D0-B25B-EB2F40ED8BB0}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{98478EA1-418C-416D-AB65-67CA8B5D0B8A}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{9D2438C6-6D86-478D-99C8-01C529231E6A}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{BA856BED-940F-4D36-832B-972720103F1A}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{BD52C3C9-1E06-4B8B-BE3D-4681A26BF0BD}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{D51506F5-3AFF-4197-9C0E-C02210C073D4}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{0F5882CE-122E-4C87-BEF9-C8CDF417F5D2}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{DB3835D3-8A3F-45E1-A828-1B948D9F9DC2}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{87914E3C-B8B0-47A5-8313-5627F05D39B8}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{DE71C4AD-F748-4016-B4E6-D161BCACF7C1}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{B282C641-D8EA-490D-8B0E-F243E9ED8F5E}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{7D8C73BD-5BC1-4046-954E-07FB1C84B349}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{75FB32AB-7E40-40A6-B96C-40B76220AC58}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{053C0D41-5ECB-4489-BC6E-373A82CC9864}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{9CF70643-8B33-438F-8312-0CEF008E136F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId163"/>
+    <tablePart r:id="rId167"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CC4B1-5884-4FA8-B789-522E5E77B996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDE3036-1EB6-45C9-A561-2139C636379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="432">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1487,6 +1487,51 @@
   </si>
   <si>
     <t>Se conversa sobre indicador de calidad para su mejora</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1-3NUIL83A</t>
+  </si>
+  <si>
+    <t>Lafayette 2017, Recoleta</t>
+  </si>
+  <si>
+    <t>Fabian Carvajal</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19WrR74n1etaBVMen-DyGV33OgXSmaz8L</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1KYFrVw1pL_0Q5oqO_iS8O72xbLCBhlDg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1E-Gbl11mMALafzRVGS9zWvYHrsIvefWr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ifBXJXqm2X_xYoaodxi7OSxX1hht8G-z</t>
+  </si>
+  <si>
+    <t>Instalación correcta, uso de cable utp para extensor, niveles de decodificador en norma, REALIZA RETIRO DE PESTAÑA EN ROSETA</t>
+  </si>
+  <si>
+    <t>1-3NUF59Z9</t>
+  </si>
+  <si>
+    <t>EL ROBLE 939 EDIF. B3 DEPTO 201, Recoleta</t>
+  </si>
+  <si>
+    <t>Carlos Huircapan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=199_vOyW5iFDWSkctyOAkdwUa0RLZsyBc</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1JzVJLMeQukMDW8y-h87SfivUGemI6kwr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1KHZKWNghcu8s60NHE0Cd7WS8HLqck28B</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_k81iD8sO1N3-jqZHJHpo_yONU6UPC_b</t>
   </si>
 </sst>
 </file>
@@ -1666,42 +1711,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2268,6 +2277,42 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2339,43 +2384,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ47" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ47" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ49" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ49" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="30"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="1"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="29"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="28" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2590,7 +2635,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ47"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -7260,179 +7305,386 @@
         <v>-</v>
       </c>
     </row>
+    <row r="48" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46280.683903900463</v>
+      </c>
+      <c r="B48" s="10">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="T48" s="3">
+        <v>4</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="V48" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="W48" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="X48" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH48" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI48" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ48" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46281.319375243052</v>
+      </c>
+      <c r="B49" s="10">
+        <v>7</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="T49" s="3">
+        <v>4</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="V49" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="W49" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="X49" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH49" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI49" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ49" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{5699F85F-7D2C-40DD-89DC-0A18973B2087}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{A3BDA528-E039-464C-BCCB-C538E9C0DE24}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{889AB803-68E1-4DF7-A450-F1E897DD9B2F}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{8E59A139-8EA0-42CC-A35A-68F2AB663890}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{4FE3177B-EE5D-41F0-B5C6-6C45AF81F5C6}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{A10D6A51-AD85-497C-AB3F-BC05714A98FE}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{62FF0B2F-4073-4CA6-89DC-D46C9623376F}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{E91EADA2-1D61-483B-8350-831F7CC58B2C}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{AFBF74EF-1CFF-408E-8C03-843E1530D31F}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{BA28C2D8-678C-4976-8ACC-1D6256602791}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{B90B30F8-61E2-4951-8091-1BDCCF2EFB25}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{D6B98549-7A61-46D2-AE02-85005264E4D5}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{30A4FE53-F4B6-4539-AEC4-7E9971DCC4A7}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{45CF8489-0158-4FA7-848E-C09C90BF8D5C}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{B612D259-9458-4040-B4BF-5811DACDDA5A}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{DF5166B2-BDE4-42F8-8DDB-D745F2446BDA}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{B13CC9BA-0B60-4093-A766-ABCC348E17C2}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{7BAA6812-2F93-44F5-85DC-7BEB44C4CB7D}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{D9E7982E-71A8-4ACA-ABB7-EACDCF00A257}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{C7AA25DB-FB4E-4FD8-8EDB-E0AFAFBF02A7}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{D961B604-A825-4762-A8BE-02A089FB3598}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{578C29FA-485E-43A9-94C7-7C21BD96A365}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{0115D73C-C7D0-4216-A810-FD23CF7CAED8}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{4EC4C0AA-C611-43E8-B2A0-191EF2DB6559}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{C3E7CA4D-FC83-47D8-A0F8-4005C99F5011}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{EF4E1CF2-C328-462D-B4CA-7858E4EFC27B}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{0934B214-089B-4A89-9386-6C443EDEB517}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{EF797B0E-E058-459D-B38C-6A134FC73EBA}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{845B93D4-EFBE-45B4-9EDE-27838082B42F}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{9D769A39-F138-4815-B1C4-3DA0AC2F44AD}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{CD0F7611-2ADD-4D91-ABC9-C7BDA5F5FF1C}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{E07598E5-7C8A-4F7F-B1AD-E157FD982479}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{AF2A79B4-326B-49EC-AB99-6F58C4CA0482}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{DC79C116-D018-43D9-9184-12CAFFBF9C93}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{A14CD7E3-6AB9-4AA7-8906-C0AD76ABF3D4}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{05A4D5A1-C90E-4F48-868C-1F6FE3E5A40D}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{4A39D551-4C02-4B47-85C3-9FEA22086947}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{30E65DA4-58B1-424D-B0B0-7F2F3DA09C98}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{51FE9DA9-4D59-42F7-97C9-06B499B155D4}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{2542F5CF-45CC-4540-B056-DC8DB3012B29}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{733902D6-FAC7-4F74-9C41-7087775B856F}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{E64BE463-A5CF-45DF-B83C-2FAF407453B2}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{4E9016D8-9894-4240-B16C-7EE44F323F4C}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{97A77373-DFB0-4FC3-86F9-29D5F74774D7}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{30877A24-B197-431A-BAF8-5B45C2CC8FDE}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{152FC0EE-30C0-4E98-BFCA-FE6C5EC1113B}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{3B5EAD5C-5037-4411-8207-71A0A711CA06}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{8B15D634-7723-4F50-8D3D-7918D3562B30}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{82C72397-C6A8-4362-A753-0FEC763585AF}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{835FFBAB-5915-4A33-98E2-AE0D221FA507}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{CB1D1819-F966-4F7D-A451-E9243F8FA04C}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{FDF4AE32-89D9-48E5-A8E7-E0C1B1FF3FDD}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{639AE886-2B20-4986-9BD8-6685AF4D6DE2}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{A65B61FF-1372-4685-A61B-F322780BAD30}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{9D27FC95-7451-43C2-976D-2D3DA941517A}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{9AED71E4-3B5F-4B0C-91B6-0D3FBAA37F58}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{7FD2CC69-618F-4E66-A87D-7AF9BDA6162A}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{D6CE77A3-5304-4A73-A3AE-A712CE884899}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{36B03DFE-2DD3-4B11-B8E2-7D0109837527}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{900FDA53-978E-453B-BE01-37F1033A9A6A}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{077668A2-B1D0-4075-863A-B115DCB98C63}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{0B099CA3-9F07-4E23-8C66-A10691B5497B}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{D036D37A-C6D8-43A8-9852-525A9B9FD672}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{8170681A-F499-4B29-BFA4-6543BA686313}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{1068FAC9-985D-485D-9E30-472F47FE644B}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{F6E36FE3-E6B5-4F0D-8D5F-03F7F35297DC}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{C539F459-9134-411B-A248-083361A58386}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{09EDF299-E413-484A-90A0-4AD6A2BB0B8F}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{562FD80C-C87B-4D15-87E1-BD79CB6A8680}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{39B8CFCE-FD6C-44CC-9A53-B626CAEE63F8}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{0B22791F-55F1-4762-859D-F6A04E75BC62}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{C3347C5D-A4BF-4CE2-8819-9C2DC9C1DDF0}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{E4360199-161C-40C7-8999-B518D6F25E35}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{727EA80A-830B-4D93-AD98-9894A7402C7F}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{07CB413B-9D7C-44F9-B0BE-644797110454}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{944E1793-9A61-45BE-9EAB-A7A30AB9A782}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{45F2360F-0C3E-4120-969C-4EB18BE4F026}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{29483A63-63C9-479C-87FC-B618A89EDC96}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{0539124B-ACD3-419F-B7C5-D8823E90706D}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{0E402A85-9A88-4A0E-82E4-5F3EDFCA205D}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{329CA64D-4F98-40C5-8521-463A4CA2A6E3}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{69C39D3E-0E35-4AC6-82BD-D09EB2509134}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{62DAA299-BD4C-4AEB-BBC2-8EFAA3E56582}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{2B8D7B04-0BB1-4AC2-82AB-C47FEF7F0740}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{83428AF8-7A23-4B0D-A4C9-D325D4D9EAF2}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{4DBAF39B-127C-4976-964C-91C89B6A67A5}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{9186BC07-69BD-4A1C-BA3D-823A95B271DA}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{741B61E2-56A0-417D-8C40-8844A59B2A74}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{108CE046-62A0-44D6-A1A2-C03DCED542D9}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{6D9429FA-C3F4-4B8E-B62D-D2B5896C751B}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{E341FDD6-BEF9-4074-B5E3-07202AE956B3}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{FD70A974-2427-46AC-BDC2-49D3314D627F}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{F8510BB7-2170-494A-B961-F57C79A160EA}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{396962ED-6D7C-41C0-9925-E61EB379BC9D}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{4881B6F4-038E-4A9B-A33D-B1F236CDA7CD}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{F2F6BA5C-CDAE-415C-AF53-D1BA26F7E8DA}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{8103B942-6A26-4E7C-8B09-7D06420C62EF}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{D2D2BEB2-0DD1-4ACC-8439-0A87A25BA1FF}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{FF56658E-C960-4DAF-AAB1-7906BB0BF9D6}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{859DC73B-9BBF-44DC-BFFA-64DFBE28C610}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{D33276F4-DAEF-4CE0-885E-CD393E511F71}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{EA67E6E5-BC65-428F-9676-816D37E66FC6}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{0C5BFFBB-251E-44FE-846A-08C85E0EA91F}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{38997356-0461-4FCD-88EC-D5E0BD60A6B9}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{A7EB0AC6-FDE8-416E-ACA5-131D142B7A32}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{29D0BE29-2021-4A7A-A3E3-8ED0980A3601}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{30E5606E-DF53-4D27-B49A-067D2D47E743}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{167F75AE-F53A-4155-B46B-B1FCC2000EE3}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{26DFD1B9-EBEE-4F6A-8839-91815DE40389}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{5FF5F1A3-994B-4535-A53E-30E42A77A3C8}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{ABEFBDBC-5FBE-4363-9970-37E4BF7520D3}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{CC036FAC-030A-4CE1-824E-FA574C13A522}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{59F6CBA4-390D-48DA-ADCE-3C7320EFB923}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{D08008EC-4BD9-4139-8CA9-11575B822B5F}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{856FD17D-5E6A-4FC0-B38A-92F3C95A6338}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{1F8BDA8A-A1D0-41BE-BEB7-C088E0D2C487}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{92D77070-3E89-4265-B8F9-604C1ABDE62A}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{2FED4E27-1D41-4216-A44B-DC6D0738A45A}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{3B9D45C5-A431-4E1D-BD03-8B26D200BA54}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{57C2A813-4EE6-46E7-8FB6-19EF60B1FBBA}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{8FE5AA19-FF9B-4A2F-8F47-734A4953E2A0}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{0B3C8844-5EF4-44F2-BC0E-8720B9A0219D}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{31B6B77A-F659-438E-AA54-D3C26602A0A9}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{4480104F-7D23-4AC9-A32F-52DD3A0DA153}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{8F6BD3B7-550F-4095-8150-5BB4732E5BF2}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{21FC3562-6CB7-49C7-AE49-2014F880C3CA}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{5C82486D-8E22-482A-84A2-EA64CED92C7F}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{3FFB1355-45CB-443A-8F56-B487734C9F7A}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{19908571-7D51-4F4C-9F10-F6A898FED479}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{C9D44F5F-328C-49B2-8C38-A169F8285C59}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{00DA5FD9-C79E-4BAE-823A-4CFB629F1004}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{59456C50-6CE4-4A01-A548-109CBFCB62C9}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{9FDE962A-2B41-4A6A-83DB-20F50D0FAA68}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{FA8E58CD-1FA7-4FC9-9857-E6C3D9A8BBEE}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{C293CE88-2A95-4923-8303-788E392A2DA4}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{42A19C7F-02BD-472A-A036-DCB1C7DB6CC6}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{FE56AE6C-D25D-417D-8D87-69877314DCCF}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{7FF32E48-E72B-4FF5-B7E4-8AFC9FB3F1DE}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{638DB38A-F7CA-4B6A-A696-FD37E28C9E23}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{07A83185-5611-44FF-B7E2-EC45AC66CF89}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{00579E4D-5A6A-4B16-AA45-178FB731C7B0}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{C27A87D2-BF39-4ED1-B3CF-4F47B60E1310}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{ABE930B5-F03D-4A63-AB03-80871E59C661}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{3E332559-519D-4C69-823D-14ECE0398BF2}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{BFD6B5DF-BFD0-4F4A-B79B-2AF7055FF7CD}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{E57B8BD5-F2A9-4F68-AFD3-A2573AD543D2}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{663D031B-432D-4A6F-AEBB-B27C7C52C5F5}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{8DA76BE4-25D7-4FDE-84D2-286B03D008D8}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{E9F3AB8D-8D06-4D14-A22E-20DE35792B80}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{E66B9718-F6D7-4062-A42E-D398067FC39F}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{A519EC7C-6528-4B2E-BBD9-516DC462FCFB}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{40C79F17-24F8-46D0-B25B-EB2F40ED8BB0}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{98478EA1-418C-416D-AB65-67CA8B5D0B8A}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{9D2438C6-6D86-478D-99C8-01C529231E6A}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{BA856BED-940F-4D36-832B-972720103F1A}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{BD52C3C9-1E06-4B8B-BE3D-4681A26BF0BD}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{D51506F5-3AFF-4197-9C0E-C02210C073D4}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{0F5882CE-122E-4C87-BEF9-C8CDF417F5D2}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{DB3835D3-8A3F-45E1-A828-1B948D9F9DC2}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{87914E3C-B8B0-47A5-8313-5627F05D39B8}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{DE71C4AD-F748-4016-B4E6-D161BCACF7C1}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{B282C641-D8EA-490D-8B0E-F243E9ED8F5E}"/>
-    <hyperlink ref="U47" r:id="rId163" xr:uid="{7D8C73BD-5BC1-4046-954E-07FB1C84B349}"/>
-    <hyperlink ref="V47" r:id="rId164" xr:uid="{75FB32AB-7E40-40A6-B96C-40B76220AC58}"/>
-    <hyperlink ref="W47" r:id="rId165" xr:uid="{053C0D41-5ECB-4489-BC6E-373A82CC9864}"/>
-    <hyperlink ref="X47" r:id="rId166" xr:uid="{9CF70643-8B33-438F-8312-0CEF008E136F}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{089757D0-F974-47A3-ADF6-F99450C811DD}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{EC47BDF5-884F-402D-AB11-22715112181E}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{8D87ADC2-65B8-4FFB-B80A-910AFE533B88}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{90F279FA-8E3E-4625-BB10-5BE68337A5AA}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{F88F74B9-2FB9-42AE-9604-25410071B1E5}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{E68F8C23-0520-4AF5-9A91-3EDA80D418A9}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{2DA5FDCC-6F39-4B57-BD77-05B99A957496}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{DA4629AE-F866-4484-B98C-60234DD943AD}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{61D45981-6064-414A-9107-AEA5775FA016}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{A3C92616-63C3-4916-941C-0671EE6FAD8A}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{EF55FFEC-6FD5-43E0-AEE0-E40073E32E4C}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{BCB2A153-9F15-4FE6-A89A-C82B71DA7AB3}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{7C1AEAA3-8EDD-4E73-AF7C-4EAA687F091D}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{1D0ABB80-E734-4BF3-851E-208352042A03}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{1471FE4E-EE78-4C2D-8A4D-57E320D04AEC}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{1DEF1C7B-52FE-4D38-A02B-E12C3F43CDAB}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{FCA28139-882E-4631-985A-8963605C236B}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{88CBEFF4-B443-4107-8E92-2CB1BB2AD015}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{5769AA2C-0F63-4C8B-BD56-B5C2520B56A8}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{E9CFC761-F867-47DE-8B10-098795FB4F1A}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{3B17ADC2-4C77-4110-84A4-8D83F6880A27}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{D414C4EC-FD4A-46B8-8716-835B5FA80793}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{54351FC1-924C-499F-970C-DAA687665247}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{15C634AF-84A4-4842-9442-A835177FDAC1}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{3EC03B49-2501-4370-AF43-30AFDECC4F6C}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{F7923731-BB53-47FC-A3D5-2558C3D7CCF7}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{0B507004-2844-4411-8BAD-5E3570FBCF72}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{DA15823C-AF0C-4DB9-941B-B2E2CAD87137}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{5C04EEA8-B996-43B9-B69F-6DC25A7FC2F9}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{12103B47-64DC-4DD1-81CF-4A447CC18044}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{FF293865-45D3-4C5F-A480-3CBEEB247455}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{9525C62D-23C1-416F-B084-9DF5FB8EA834}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{9A631294-DDB8-41A7-94C5-9A324AD57044}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{B5549C60-A5CE-443E-98CC-7E989F2F2FB6}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{04F3FFC0-F859-42F7-BB7D-97CC457CE75A}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{4C248E4E-3D18-4AF3-B48F-EB63D9F49D4E}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{B8D95528-BC19-4181-9FB9-DE812257D05D}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{4621246B-EF2B-4F85-A1AD-58AE704009D5}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{800E3FA0-2DBE-4E6E-8826-9E40AA80242D}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{741CC27B-3CBE-4384-9DF7-ABB5E351E782}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{C2635905-6FD5-464C-8931-D6B70D7E578E}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{843FC48C-1C2A-4A14-9416-FDE7621A9270}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{279AF171-90B5-4558-9DA0-2D775E14DFCD}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{E89AAC1A-2FE2-444B-A7D1-A704FBD9D2B6}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{8797C28D-B520-4A38-8333-52414DFAF945}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{F7C5F0FE-1574-4475-928A-D221BDF74A8B}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{BD567E08-202F-410D-A8A9-0FEF4E119E9B}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{CF4E3CE7-9D9C-437F-8361-16EDE636EDDF}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{1489BB84-5ED1-4A3F-8BD3-95E15B9F5ECE}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{9161DBC0-4547-4652-A055-A1757D3486CB}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{0BDA182F-6C11-4FB9-BD44-091683781AF3}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{7A32C7ED-710C-4A6B-B4E1-A8F2C81B7668}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{D3E0A770-A6C8-4F2F-8F98-C2DDD20A35C3}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{10FE478C-28BD-4DD9-8EA8-018E258111A0}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{BB71337C-9288-4B58-B454-ECBFD1E976A9}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{81B9F4A8-01BD-445B-BAD5-E4F509A9AA09}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{EB663CC1-3C57-412A-8576-8A1B5321AFC8}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{BF5EC143-76EF-4B74-9239-2654FDD786B3}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{5E127D5A-5074-417A-AF84-B45715A048A1}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{A5723574-1929-4FA1-A6AE-0BE6668BBA06}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{34D47132-03C6-4D13-9575-2ED23404AE8E}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{3F7C4DD5-D727-4AA2-B026-B9A3E97813AF}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{D1021BF2-B3D1-4FDE-BD0B-6F04CDAF6C81}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{9E021946-CEFC-4C0D-8624-2B88F4848396}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{C36ECB28-DFE1-49F2-BDC3-D7C09BC234E5}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{1E6660BB-1500-4A65-98E3-33003128CA1C}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{8BB8FFE5-E268-4DFE-A923-6EA4AD324CAC}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{F90A9A34-4E50-45EF-9C93-49AF3775D905}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{E131C7E7-EACC-4697-A4CD-0AE37A858F07}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{E42858F3-A50A-4CBC-B418-FACF4ECF2C1A}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{B6DB5C8E-212D-4444-81B3-CE77FC95E3CA}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{20BB1475-51CD-4C6A-8930-A9F3ADF9A80D}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{5E7D9FF6-3B46-43F5-8CDA-B3A8428DD38E}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{778A6B80-FEC1-438C-AB24-7901EBDD68EA}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{842CF253-0D1E-40E3-BAD1-A7E8972A979A}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{46EC810C-B74E-403F-9C9C-4DB94C4766D9}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{F530D1B8-A959-44D6-8EA5-9E82FDDA02B9}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{25290090-F735-4B74-8F24-0EA95702FF40}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{EA3670D9-08C1-44C2-B55E-4BC33EB037D2}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{D4638AC0-D09D-43E4-9AFA-73B8F99E004F}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{595AC1CE-C6ED-4F93-9EFC-1735BF645530}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{E4F937D3-7D2F-4F29-A77A-26136CBEAC23}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{2523A6F8-437B-4C5F-9DF8-E537CA83C11E}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{5439FC17-16EC-474F-928E-9AECE4D15295}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{1BE0EC4B-0EB3-48FD-93A7-F92BB28154FA}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{BCF4F22F-751C-43FC-BAD1-AE0E57061E31}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{3B1D1047-72C1-4140-B82F-6897EDC9E23E}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{6641D6CE-BE73-48D8-85B3-7593ECB936DE}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{D5F585EB-CA7B-48A1-8B97-7C8956BFF8A5}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{7D5C53F8-0B1C-4E73-B524-B635AB5E6951}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{DCC438CA-AFE8-4C99-8F22-34E2F28E2B52}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{3FB9B61A-6EB7-4987-AA63-0642B2A653E2}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{89F43572-95A9-464C-8530-AB3BB6F4430B}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{8D94421C-9190-4712-8E33-0DD5DA40800E}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{1956D1C4-0EDD-48ED-8A5A-325075C57F4D}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{B1FE081A-F35B-4A6D-8ED6-BB53CD115255}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{1B913B53-0299-45AC-8C6B-796C96807EFF}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{0B3EA5EC-A013-4867-B015-A332605828D4}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{570BBBCE-1C31-4353-9976-5D2739617983}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{14BEC2C1-25EF-4668-BCBD-AC4EC4D91D11}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{9574C2FB-A4CF-4FD8-9633-EEC1F16FCACF}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{195EC7F1-CA60-4BF9-960D-0B1EFB16FA3A}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{63071E06-ED46-4DEC-978E-D4C2E00E3B98}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{7807FB3B-12D1-44E8-818B-B63E922E9226}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{C26A62AB-F98E-47E9-A4C3-AEE7ABD9FB2D}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{951F3A63-332F-439F-B428-03555CFB9640}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{749B707C-6C83-4549-8D1A-977F23635F67}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{A5C0E6E7-9C49-49E7-9B2A-BE2C23486415}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{030C9652-9871-40F5-A72A-D2E3832E9EC3}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{69797A38-9E75-456C-9909-61906AAA8A8E}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{CA03BC49-1AB2-4B91-8910-8C5BED15707C}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{2952BF17-F9B7-420D-B34F-CB65FC8544D1}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{CE5FCC0C-4045-4EBF-8721-F2AD2847B65B}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{E498B230-2A9C-47CC-9B56-BC274830F857}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{FCCE68F9-B3B6-4E85-A43E-88D35A0FFF2E}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{6443244A-C371-447F-96ED-5987CFD9F870}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{CA5DA4BE-4E2C-45C9-8E44-359016F428FD}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{E5BBE734-D696-415F-94CB-C695707AADBE}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{C9D8545B-4D1E-4889-8D78-7221A5ADF387}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{59321A90-42B4-4B9F-8B54-3AF712975CFE}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{0A0178F0-3C59-4BC8-953A-F8D9B017DB31}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{33A75BB2-7B6D-4B25-A8F6-C43F08DA41B3}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{56C4932C-21C5-41BA-A28B-78919B0B5B7A}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{2E899971-DAC0-48F5-8C3F-16BD065BEBE1}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{FFE20643-CE0C-4782-866D-50A76CC53ACE}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{DAD7BAA0-8C4E-4420-A795-D2CC1C183C5F}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{422A098D-6D95-4CB1-8F03-0289BA95D71B}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{BBED4DE6-1E55-496A-ABF1-1982FB835E48}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{6E6A2D82-0591-441B-BB83-62AF5866947B}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{003990AC-666C-4E6A-8D6C-F9C677449A22}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{071A30FD-5971-4528-8A88-DC07E802D74C}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{2A5B708A-EECC-4677-8DC0-D4CA4137903A}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{FC9DAD5D-2000-4C6F-A3CD-776C5C6FE8CA}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{4D7BA322-B965-4178-A528-40E4F491024A}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{1541DB96-D2A6-4DD0-8EDA-9DBC1C2D7537}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{C7C488E9-FD65-44A3-8B2A-BE0C3EC4F2D2}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{AF8C7FB2-1BA3-46AF-9478-A9088B76DE48}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{0DABE799-17C0-4C3B-B9DD-7F2F9C26F9C8}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{EF8607F7-1696-4EC9-9EE9-883F37F6EFE7}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{C0031684-87C0-4C96-9A3D-9959CCFEFE62}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{452D6DC8-E308-432F-9CE1-A9A0BB80EDEC}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{543AEEF9-AB70-435B-B66B-C0C954B89238}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{ED873D10-810C-4A06-8928-2E2E75B1583C}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{04EAF3EC-6723-4826-9764-6CC08A280A7F}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{B0E11EF0-A9FF-4980-A896-092D70F6BD74}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{01E638F5-8118-4AA6-A3F4-C13AD59EA28E}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{C6FD9027-CA06-4A7D-8B00-B7E5651D9EBB}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{1F4A6A9D-9152-48BC-B6CD-3FB07672CFBB}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{FFB57BFA-9BD9-41AC-A679-D5D626B22CDD}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{133DB319-1543-4F2F-9CC7-14B5C16A282E}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{1B8F4AFD-D753-422D-BDB8-B6E64E256DA6}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{5007EA32-EA09-46C1-B989-A5647DF350E9}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{0DAD3C59-FFF2-462A-ABA5-A752880C38F6}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{3308D9E6-EB99-4E97-B76A-F02BF02D51A6}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{C1AA08F2-BDFA-4917-9A4F-2756AFCF23C8}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{FAD8D075-0455-4CF1-B34F-0E6D9D0E7434}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{5CA93736-8CF3-4F90-9CD2-658FB095C420}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{38D5C8F0-EFD2-4FA6-AD89-4B9D7D070445}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{B95713DB-4EDA-4082-ABD4-7347A02572F5}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{7F425E4D-A79C-44FD-AB57-880C4DC21184}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{E7885B60-F938-4FB7-B2B2-42F442EC4435}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{6CB3B4D6-DCB4-4756-A50D-E4628968269E}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{5064F66E-B893-489C-9CEA-DACE50D37FBB}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{203D9850-5425-43C3-B054-F76E457C806A}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{7751D484-B400-4F27-AA0E-5687B968E730}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{C909687C-C11E-40F7-A28E-C1D3F9639F3A}"/>
+    <hyperlink ref="U48" r:id="rId167" xr:uid="{52EFB059-CF86-409F-87D0-A6DF6BB4AEAF}"/>
+    <hyperlink ref="V48" r:id="rId168" xr:uid="{F842C504-84DB-48E1-9B41-36D391F84DEB}"/>
+    <hyperlink ref="W48" r:id="rId169" xr:uid="{94C970DB-6F91-4392-8D05-24B858AE3EFE}"/>
+    <hyperlink ref="X48" r:id="rId170" xr:uid="{D42E0461-B543-4FA3-AE5D-8E64841C55AE}"/>
+    <hyperlink ref="U49" r:id="rId171" xr:uid="{94CA8AA7-6AC6-47A4-B884-AC11EF18D8DD}"/>
+    <hyperlink ref="V49" r:id="rId172" xr:uid="{94E92EB0-F012-4886-B027-6AD59FB4399E}"/>
+    <hyperlink ref="W49" r:id="rId173" xr:uid="{8AD91B48-E993-42CE-8B95-45A263B91F2E}"/>
+    <hyperlink ref="X49" r:id="rId174" xr:uid="{4F4D5575-7997-44CC-87C1-1817C2D77CF8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId167"/>
+    <tablePart r:id="rId175"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDE3036-1EB6-45C9-A561-2139C636379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF13174-F61E-4682-8ACA-5ABFD4F9EB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -2177,24 +2177,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2220,6 +2202,24 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2387,22 +2387,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ49" headerRowDxfId="34">
   <autoFilter ref="A1:AJ49" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="20"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="32"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="30"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="14"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="13"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="12"/>
@@ -2415,12 +2415,12 @@
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="30"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="29"/>
     <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="2"/>
     <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="1"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="29"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="28"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="28" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="27" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -7507,180 +7507,180 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{089757D0-F974-47A3-ADF6-F99450C811DD}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{EC47BDF5-884F-402D-AB11-22715112181E}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{8D87ADC2-65B8-4FFB-B80A-910AFE533B88}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{90F279FA-8E3E-4625-BB10-5BE68337A5AA}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{F88F74B9-2FB9-42AE-9604-25410071B1E5}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{E68F8C23-0520-4AF5-9A91-3EDA80D418A9}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{2DA5FDCC-6F39-4B57-BD77-05B99A957496}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{DA4629AE-F866-4484-B98C-60234DD943AD}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{61D45981-6064-414A-9107-AEA5775FA016}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{A3C92616-63C3-4916-941C-0671EE6FAD8A}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{EF55FFEC-6FD5-43E0-AEE0-E40073E32E4C}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{BCB2A153-9F15-4FE6-A89A-C82B71DA7AB3}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{7C1AEAA3-8EDD-4E73-AF7C-4EAA687F091D}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{1D0ABB80-E734-4BF3-851E-208352042A03}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{1471FE4E-EE78-4C2D-8A4D-57E320D04AEC}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{1DEF1C7B-52FE-4D38-A02B-E12C3F43CDAB}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{FCA28139-882E-4631-985A-8963605C236B}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{88CBEFF4-B443-4107-8E92-2CB1BB2AD015}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{5769AA2C-0F63-4C8B-BD56-B5C2520B56A8}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{E9CFC761-F867-47DE-8B10-098795FB4F1A}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{3B17ADC2-4C77-4110-84A4-8D83F6880A27}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{D414C4EC-FD4A-46B8-8716-835B5FA80793}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{54351FC1-924C-499F-970C-DAA687665247}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{15C634AF-84A4-4842-9442-A835177FDAC1}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{3EC03B49-2501-4370-AF43-30AFDECC4F6C}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{F7923731-BB53-47FC-A3D5-2558C3D7CCF7}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{0B507004-2844-4411-8BAD-5E3570FBCF72}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{DA15823C-AF0C-4DB9-941B-B2E2CAD87137}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{5C04EEA8-B996-43B9-B69F-6DC25A7FC2F9}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{12103B47-64DC-4DD1-81CF-4A447CC18044}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{FF293865-45D3-4C5F-A480-3CBEEB247455}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{9525C62D-23C1-416F-B084-9DF5FB8EA834}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{9A631294-DDB8-41A7-94C5-9A324AD57044}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{B5549C60-A5CE-443E-98CC-7E989F2F2FB6}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{04F3FFC0-F859-42F7-BB7D-97CC457CE75A}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{4C248E4E-3D18-4AF3-B48F-EB63D9F49D4E}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{B8D95528-BC19-4181-9FB9-DE812257D05D}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{4621246B-EF2B-4F85-A1AD-58AE704009D5}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{800E3FA0-2DBE-4E6E-8826-9E40AA80242D}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{741CC27B-3CBE-4384-9DF7-ABB5E351E782}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{C2635905-6FD5-464C-8931-D6B70D7E578E}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{843FC48C-1C2A-4A14-9416-FDE7621A9270}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{279AF171-90B5-4558-9DA0-2D775E14DFCD}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{E89AAC1A-2FE2-444B-A7D1-A704FBD9D2B6}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{8797C28D-B520-4A38-8333-52414DFAF945}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{F7C5F0FE-1574-4475-928A-D221BDF74A8B}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{BD567E08-202F-410D-A8A9-0FEF4E119E9B}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{CF4E3CE7-9D9C-437F-8361-16EDE636EDDF}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{1489BB84-5ED1-4A3F-8BD3-95E15B9F5ECE}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{9161DBC0-4547-4652-A055-A1757D3486CB}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{0BDA182F-6C11-4FB9-BD44-091683781AF3}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{7A32C7ED-710C-4A6B-B4E1-A8F2C81B7668}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{D3E0A770-A6C8-4F2F-8F98-C2DDD20A35C3}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{10FE478C-28BD-4DD9-8EA8-018E258111A0}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{BB71337C-9288-4B58-B454-ECBFD1E976A9}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{81B9F4A8-01BD-445B-BAD5-E4F509A9AA09}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{EB663CC1-3C57-412A-8576-8A1B5321AFC8}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{BF5EC143-76EF-4B74-9239-2654FDD786B3}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{5E127D5A-5074-417A-AF84-B45715A048A1}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{A5723574-1929-4FA1-A6AE-0BE6668BBA06}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{34D47132-03C6-4D13-9575-2ED23404AE8E}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{3F7C4DD5-D727-4AA2-B026-B9A3E97813AF}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{D1021BF2-B3D1-4FDE-BD0B-6F04CDAF6C81}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{9E021946-CEFC-4C0D-8624-2B88F4848396}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{C36ECB28-DFE1-49F2-BDC3-D7C09BC234E5}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{1E6660BB-1500-4A65-98E3-33003128CA1C}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{8BB8FFE5-E268-4DFE-A923-6EA4AD324CAC}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{F90A9A34-4E50-45EF-9C93-49AF3775D905}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{E131C7E7-EACC-4697-A4CD-0AE37A858F07}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{E42858F3-A50A-4CBC-B418-FACF4ECF2C1A}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{B6DB5C8E-212D-4444-81B3-CE77FC95E3CA}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{20BB1475-51CD-4C6A-8930-A9F3ADF9A80D}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{5E7D9FF6-3B46-43F5-8CDA-B3A8428DD38E}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{778A6B80-FEC1-438C-AB24-7901EBDD68EA}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{842CF253-0D1E-40E3-BAD1-A7E8972A979A}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{46EC810C-B74E-403F-9C9C-4DB94C4766D9}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{F530D1B8-A959-44D6-8EA5-9E82FDDA02B9}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{25290090-F735-4B74-8F24-0EA95702FF40}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{EA3670D9-08C1-44C2-B55E-4BC33EB037D2}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{D4638AC0-D09D-43E4-9AFA-73B8F99E004F}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{595AC1CE-C6ED-4F93-9EFC-1735BF645530}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{E4F937D3-7D2F-4F29-A77A-26136CBEAC23}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{2523A6F8-437B-4C5F-9DF8-E537CA83C11E}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{5439FC17-16EC-474F-928E-9AECE4D15295}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{1BE0EC4B-0EB3-48FD-93A7-F92BB28154FA}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{BCF4F22F-751C-43FC-BAD1-AE0E57061E31}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{3B1D1047-72C1-4140-B82F-6897EDC9E23E}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{6641D6CE-BE73-48D8-85B3-7593ECB936DE}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{D5F585EB-CA7B-48A1-8B97-7C8956BFF8A5}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{7D5C53F8-0B1C-4E73-B524-B635AB5E6951}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{DCC438CA-AFE8-4C99-8F22-34E2F28E2B52}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{3FB9B61A-6EB7-4987-AA63-0642B2A653E2}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{89F43572-95A9-464C-8530-AB3BB6F4430B}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{8D94421C-9190-4712-8E33-0DD5DA40800E}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{1956D1C4-0EDD-48ED-8A5A-325075C57F4D}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{B1FE081A-F35B-4A6D-8ED6-BB53CD115255}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{1B913B53-0299-45AC-8C6B-796C96807EFF}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{0B3EA5EC-A013-4867-B015-A332605828D4}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{570BBBCE-1C31-4353-9976-5D2739617983}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{14BEC2C1-25EF-4668-BCBD-AC4EC4D91D11}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{9574C2FB-A4CF-4FD8-9633-EEC1F16FCACF}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{195EC7F1-CA60-4BF9-960D-0B1EFB16FA3A}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{63071E06-ED46-4DEC-978E-D4C2E00E3B98}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{7807FB3B-12D1-44E8-818B-B63E922E9226}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{C26A62AB-F98E-47E9-A4C3-AEE7ABD9FB2D}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{951F3A63-332F-439F-B428-03555CFB9640}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{749B707C-6C83-4549-8D1A-977F23635F67}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{A5C0E6E7-9C49-49E7-9B2A-BE2C23486415}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{030C9652-9871-40F5-A72A-D2E3832E9EC3}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{69797A38-9E75-456C-9909-61906AAA8A8E}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{CA03BC49-1AB2-4B91-8910-8C5BED15707C}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{2952BF17-F9B7-420D-B34F-CB65FC8544D1}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{CE5FCC0C-4045-4EBF-8721-F2AD2847B65B}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{E498B230-2A9C-47CC-9B56-BC274830F857}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{FCCE68F9-B3B6-4E85-A43E-88D35A0FFF2E}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{6443244A-C371-447F-96ED-5987CFD9F870}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{CA5DA4BE-4E2C-45C9-8E44-359016F428FD}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{E5BBE734-D696-415F-94CB-C695707AADBE}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{C9D8545B-4D1E-4889-8D78-7221A5ADF387}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{59321A90-42B4-4B9F-8B54-3AF712975CFE}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{0A0178F0-3C59-4BC8-953A-F8D9B017DB31}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{33A75BB2-7B6D-4B25-A8F6-C43F08DA41B3}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{56C4932C-21C5-41BA-A28B-78919B0B5B7A}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{2E899971-DAC0-48F5-8C3F-16BD065BEBE1}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{FFE20643-CE0C-4782-866D-50A76CC53ACE}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{DAD7BAA0-8C4E-4420-A795-D2CC1C183C5F}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{422A098D-6D95-4CB1-8F03-0289BA95D71B}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{BBED4DE6-1E55-496A-ABF1-1982FB835E48}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{6E6A2D82-0591-441B-BB83-62AF5866947B}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{003990AC-666C-4E6A-8D6C-F9C677449A22}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{071A30FD-5971-4528-8A88-DC07E802D74C}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{2A5B708A-EECC-4677-8DC0-D4CA4137903A}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{FC9DAD5D-2000-4C6F-A3CD-776C5C6FE8CA}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{4D7BA322-B965-4178-A528-40E4F491024A}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{1541DB96-D2A6-4DD0-8EDA-9DBC1C2D7537}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{C7C488E9-FD65-44A3-8B2A-BE0C3EC4F2D2}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{AF8C7FB2-1BA3-46AF-9478-A9088B76DE48}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{0DABE799-17C0-4C3B-B9DD-7F2F9C26F9C8}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{EF8607F7-1696-4EC9-9EE9-883F37F6EFE7}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{C0031684-87C0-4C96-9A3D-9959CCFEFE62}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{452D6DC8-E308-432F-9CE1-A9A0BB80EDEC}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{543AEEF9-AB70-435B-B66B-C0C954B89238}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{ED873D10-810C-4A06-8928-2E2E75B1583C}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{04EAF3EC-6723-4826-9764-6CC08A280A7F}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{B0E11EF0-A9FF-4980-A896-092D70F6BD74}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{01E638F5-8118-4AA6-A3F4-C13AD59EA28E}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{C6FD9027-CA06-4A7D-8B00-B7E5651D9EBB}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{1F4A6A9D-9152-48BC-B6CD-3FB07672CFBB}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{FFB57BFA-9BD9-41AC-A679-D5D626B22CDD}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{133DB319-1543-4F2F-9CC7-14B5C16A282E}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{1B8F4AFD-D753-422D-BDB8-B6E64E256DA6}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{5007EA32-EA09-46C1-B989-A5647DF350E9}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{0DAD3C59-FFF2-462A-ABA5-A752880C38F6}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{3308D9E6-EB99-4E97-B76A-F02BF02D51A6}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{C1AA08F2-BDFA-4917-9A4F-2756AFCF23C8}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{FAD8D075-0455-4CF1-B34F-0E6D9D0E7434}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{5CA93736-8CF3-4F90-9CD2-658FB095C420}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{38D5C8F0-EFD2-4FA6-AD89-4B9D7D070445}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{B95713DB-4EDA-4082-ABD4-7347A02572F5}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{7F425E4D-A79C-44FD-AB57-880C4DC21184}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{E7885B60-F938-4FB7-B2B2-42F442EC4435}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{6CB3B4D6-DCB4-4756-A50D-E4628968269E}"/>
-    <hyperlink ref="U47" r:id="rId163" xr:uid="{5064F66E-B893-489C-9CEA-DACE50D37FBB}"/>
-    <hyperlink ref="V47" r:id="rId164" xr:uid="{203D9850-5425-43C3-B054-F76E457C806A}"/>
-    <hyperlink ref="W47" r:id="rId165" xr:uid="{7751D484-B400-4F27-AA0E-5687B968E730}"/>
-    <hyperlink ref="X47" r:id="rId166" xr:uid="{C909687C-C11E-40F7-A28E-C1D3F9639F3A}"/>
-    <hyperlink ref="U48" r:id="rId167" xr:uid="{52EFB059-CF86-409F-87D0-A6DF6BB4AEAF}"/>
-    <hyperlink ref="V48" r:id="rId168" xr:uid="{F842C504-84DB-48E1-9B41-36D391F84DEB}"/>
-    <hyperlink ref="W48" r:id="rId169" xr:uid="{94C970DB-6F91-4392-8D05-24B858AE3EFE}"/>
-    <hyperlink ref="X48" r:id="rId170" xr:uid="{D42E0461-B543-4FA3-AE5D-8E64841C55AE}"/>
-    <hyperlink ref="U49" r:id="rId171" xr:uid="{94CA8AA7-6AC6-47A4-B884-AC11EF18D8DD}"/>
-    <hyperlink ref="V49" r:id="rId172" xr:uid="{94E92EB0-F012-4886-B027-6AD59FB4399E}"/>
-    <hyperlink ref="W49" r:id="rId173" xr:uid="{8AD91B48-E993-42CE-8B95-45A263B91F2E}"/>
-    <hyperlink ref="X49" r:id="rId174" xr:uid="{4F4D5575-7997-44CC-87C1-1817C2D77CF8}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{24840A53-0D9F-4FB7-9829-AACFF35D7A4C}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{E31E9C56-13DA-4818-B898-2EECD0FD0911}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{CBEF14D8-DA20-4298-9D99-81D9D34D22CD}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{18EE46B3-BAF2-4A54-B7BF-DC495A8CD38B}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{9B67D365-2592-476F-8589-9D69CB19E659}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{D2D517AB-417F-41A9-8A16-C3AEF237A2A4}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{E0BC0518-9783-4BC3-A7D3-7AD304C98105}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{608DD207-09D3-4438-A7E0-FCF7FD6189DF}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{39E9A11D-2204-4C76-9FDD-8BCA2E7111D1}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{D6410C08-D394-4B72-9AA4-7C7966569333}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{B9F86F9A-142E-40A3-809F-FC020E270902}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{296E9C1D-30D0-46EB-A392-8EBBC73C9775}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{415BA41B-2377-4ED2-93B5-A09CD9A7A56A}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{8D2BCA0A-CFC1-46FE-8303-AD42FE73C30B}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{19645437-02D9-43EE-815E-E30E932637FE}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{2D7EF939-91A4-4A3A-8DB2-7E4A5946036F}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{F33AEBDC-4B36-4AD4-990C-BAF8747748EB}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{835B2419-A752-4C2E-9903-C30AA2739042}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{04CEA735-E69D-411B-9D75-5DBDC9AC9215}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{F0820406-43AF-433C-98D6-96A868F77C6E}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{A12E5D97-FED9-4EF6-8BE0-B8731BA36D82}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{0B4472D5-1B42-445E-8EF7-4AB24461AA23}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{AE90C0B1-3D48-416F-B5F7-84792414AF2E}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{461D1D29-A84E-4A9C-BE4F-AFBA8882E853}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{0165C924-91E4-4A84-97C5-815BFB88BAD2}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{6FEE2985-3446-4D47-9ADF-38015AB6C8F7}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{5A8354D9-F678-43E1-8514-510E38B7041C}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{1BF0D57C-0600-4E6A-A5E2-F3D200491043}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{A26ED909-7E7F-4447-A9F0-B517C6CA0984}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{E3E891AF-F38E-44D5-A291-56D702B096E6}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{2AADE899-D8B3-4098-BED6-51A60C83C267}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{F780BCA8-3F46-4FD8-90BB-4FA92C5F6B36}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{84BCD973-5836-4FBC-AA6E-196511A42517}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{19334CA5-682A-4DB6-B811-08FAF68A7A92}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{5CD8D155-9258-4FDC-9D21-8C08583B217E}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{3E2548FD-728E-42A2-B191-5C04575FDFE7}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{C6F996FB-ECCF-4457-87BC-885ADD3FEFBB}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{DCF12ADA-DCB3-4F71-8802-15A4B55C5F35}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{358A87F5-FB3E-41FE-844D-E12FCA28182F}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{0D16291E-B324-4D53-9A75-AB8D26A5470B}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{C78561E6-6421-4D1E-9A47-D83BFA75DA4A}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{B055C7F4-BDF7-4CE4-893C-16EB5021D9C0}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{6831D432-1FE6-41F4-9FD8-E4B171707490}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{62A1B213-F2C4-4884-9C4E-835B63057EE3}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{FA8C5364-B4C0-4164-A04B-F18BE7FE2430}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{64B3AF7F-B2AF-4328-B75E-0DD01FE9C53A}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{4681BB06-00E9-4BEB-A8D6-F5C7FDFEEA8B}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{1D14EE08-9106-4D48-B486-E766EE11FF57}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{BADE6ED6-C03D-4208-8C2B-3628EDA5F68C}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{707C08C2-559F-490C-905E-DA18AA141F71}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{2361E213-9D6D-4AB0-9A29-C7F9758AD1A1}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{196363BB-14B9-4F55-8AE2-3E765C2C3EC2}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{1643F68F-AFEE-40F5-BB6D-0A5F9398D78B}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{332F80D9-7AD6-4C89-A46A-28F4F3AB9FC8}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{9A436988-A437-4315-A66C-EFFE554A52F2}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{87D520B5-BD1F-4545-A07C-79CB7362DDDB}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{C80DA050-6ADD-4ED9-A6F0-16409111C51A}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{397DEEB2-801F-408B-9B6D-F2DB9D937E33}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{21CE78B8-1B26-47F6-96CC-106502D7D965}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{29DBBCFC-01A9-4223-B2E9-B3F6E48F8CF1}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{8BD8B9F9-A794-4CEC-9615-A5438306B42E}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{6C25E9FA-64D2-42D1-B158-951F6DD3333D}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{430B76F2-E1AE-4AB8-A96B-66CB67DE997E}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{1B36DE0E-31E8-44C8-86E0-F23D369B5CC9}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{0FC6F7A1-ADEA-4A4B-BFAA-C214CC4B4CFF}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{AB1C528E-86EC-46DD-914A-F07D2EAC9872}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{7126E654-BD5A-47FA-8D07-8314DF2A32AA}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{5CC96FEB-6958-47B9-BD84-E793F3C164C8}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{45187E00-F92E-468D-981B-50D96B3638D9}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{A94C2308-729F-4596-A11F-C0D1D7218146}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{E0342F70-769B-49BC-B135-4B40289FA661}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{68620238-3EDB-4F8F-B6FC-B86E7835B50D}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{E6A9D1FE-01F2-475E-9893-3B664E1DEED1}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{BE9C924E-8157-41FD-834F-A63278782421}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{EBC9C468-B7C0-4D42-8AC0-81D3716E0C4B}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{F9B82B02-6088-4336-80EF-C70171C9EFA3}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{DB30266A-2CE1-4CBA-B5DA-BA5E1D7951CC}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{2F420E44-6A5C-4AA0-8ADE-FDE5557C61B3}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{3681C826-FA7C-4EB8-9A1C-503DB4D9600B}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{66E13639-4F49-4312-98BB-3A1DDBF80E6D}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{670B7EFC-818D-4702-A1C6-A61A71FFB352}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{5D114BEF-2EC0-42AC-854A-9C6E2686CA62}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{8104CE66-06DD-423B-9BA5-46348F12F613}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{6B1F7169-FED2-4681-923F-E14F89865C9E}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{0369BB86-E134-492C-BE04-DC95E8B02C48}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{5F3F11CF-B8E4-4D23-939E-EEE75AB96D10}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{FD571A49-4435-4E4C-B320-5FF6579037B5}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{51553996-102A-42C1-8A58-85AA95E00383}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{F28C1D5F-B4B7-4511-AB78-A12E9831AF33}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{D952BEF3-8FDC-4E22-98D4-90FE7D409544}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{1D8C70EF-603A-4DA8-96DA-DE882DC4C4CA}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{BFF6C83C-A60B-4138-A499-32066EE82ADE}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{A71F2ADA-4948-4FE5-B3D3-923161020D5C}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{384B3510-D834-43C9-AE12-17B7EF40D4A3}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{EA3030EC-7BB4-4F76-831C-4D3D54090B1A}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{3FB9533E-E1E0-4256-8FAE-C473EC794E66}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{1E05D3E1-B905-44E0-92BC-DC2A00CD55F8}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{EAB44384-75DF-47AD-BEC7-FECBBC4B0393}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{F1994D3F-622E-46D3-B7FF-16BF3AE809EA}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{4452FE24-8276-4CA1-AD47-16B2CD6958BB}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{F63C7613-07C7-44C6-88DF-A69C9BE1EB49}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{14CDA284-6E6D-4716-A799-1DEA36E07880}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{2D9F8725-D2B7-43AE-A0E4-3BA1C09F17EB}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{90D413F6-80DD-4081-92EF-8657ED37B063}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{9C0E4E4A-1781-4716-AE54-19CFAB7BA70D}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{ABD53ACE-D206-413F-B1E3-D701576C3AD1}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{DB2741B8-5384-4979-8878-22030CBAE765}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{A5D4A384-C26C-45EF-9E76-53C7BEFB9CDA}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{8875BE84-4A45-4511-9B7D-7E823CD294BF}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{2DCA0B60-F06D-4EFE-A61B-2BFF0C1D383F}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{BAA22668-0B1D-4852-8C63-12619BF4E2E4}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{8005E6C4-A51E-4C29-927B-0C58789354B4}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{A3C558A3-6240-4F35-A9C4-E1FF4C08254F}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{D584D751-2C6C-481E-B76A-98AA68DC7169}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{EB8383D1-DC4F-4960-B00C-D0CAA9575E35}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{D8CD5DD1-86A8-4BC3-B10C-7BD46BF86885}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{9D65C362-47C3-4AB5-B8E5-B6F3B540593F}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{5FD299A3-D8C2-4A66-B48E-BED837840472}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{97333630-2AA1-477F-A8AC-3EDEDBB20AC7}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{BDDAAEC6-AC94-4758-A047-5EFE7AF410D1}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{86539285-BD10-4AC3-BDBD-EBBC27B5C12C}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{E449785D-6C16-48D9-9921-2EDFC4EFD87A}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{06BF76DF-F9B9-426D-9E13-CECE7E8553FF}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{F0FC1FF2-77D2-46C1-A67D-D7C136F87B28}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{AAF804D0-93E0-4CBA-BC74-F18383752407}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{3F598118-19C9-4AD6-B2C8-A1C5B8DBF195}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{D2366979-9EEB-4AFD-8EF8-8DD567B9D893}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{99538AA3-F34F-4BD7-9C0E-A586B8FEE158}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{D78342CC-33C3-4093-8CD0-E112960CC07D}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{C43E8E65-1CFD-4E9C-945B-0454F6C7899A}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{A124DECD-A9D0-4A42-9F6B-957F3C36220A}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{AD7DDECF-473A-4EDE-AEDD-90C882B518DF}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{786A8733-9A93-4F2E-B727-C4E26BD1867F}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{63D2788B-5743-4FD6-B8F0-89E5B8D938A2}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{2D81C8B8-6F26-4413-8DDE-631883D9C7D1}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{F3221CAE-FD53-4989-B512-13F4F3463729}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{B82926E4-591D-433D-8403-CA8781B4F5E1}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{94287FF9-0624-40E6-AB64-D80142504892}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{2778DA68-C1B9-4242-9724-2F4E3206B05F}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{9971F478-0F4A-46FD-B444-D3E419C61BE5}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{737A2010-982C-4AD7-A08F-2EAA29C442D8}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{C63BCAB8-532C-4421-8958-24EE7B99E612}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{8806A5F9-DFB3-47D6-AAED-DDE89B114C70}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{7F22805F-713C-42EA-978A-A3A31906F946}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{42CD0C74-CC77-4E85-BC3B-DFAD372BFDBC}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{ADAC97E1-4CE1-46C9-8821-8CC74B308FC7}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{C2709819-0798-4AEF-9515-D985890BC33E}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{D4EE8B7F-2905-4E26-9364-02A2FD978A34}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{E12D2B30-9B5C-4B29-92A4-0F7961E26060}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{1DA5A7CD-209A-4AFF-971B-00EBB4A3D0DE}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{DF3EAD04-C798-4C1B-8BD4-D4528FED033E}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{9A7E10AB-3234-4A42-8D90-4C999C804192}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{E01D8228-6322-4E7E-B53A-9BA0C915560C}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{DE58A923-123B-4849-A5C5-D08FF1655911}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{B671CB43-D027-4D96-9983-9FACFB879450}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{AEA6D413-F728-422F-B12C-60D6F24FA33F}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{07707909-A140-4063-B094-EA9BB1A7A31A}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{37C8E2AD-FED0-4E02-9C87-709D608289BD}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{13CEA6F0-F52F-40F9-9DD7-13074D704F62}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{4734A898-132D-40CF-9F8E-7551A014D2BF}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{442CDB75-9EE3-4E35-B2C3-172C5E4877F0}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{3688F25A-2B00-4D9F-864D-C1E21D296960}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{49639566-E494-4A88-AF8A-4CE6445AE87C}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{D9D3A0C8-52D3-4443-B809-0CAFAACE1BFC}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{222DB88B-143E-44FF-91E4-A83BF1A567B3}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{8DE17295-1836-477C-90F2-F51325293385}"/>
+    <hyperlink ref="U48" r:id="rId167" xr:uid="{3730A5EE-8E66-43DB-8344-5716E65E7977}"/>
+    <hyperlink ref="V48" r:id="rId168" xr:uid="{4721ECC4-816F-4E29-B1CC-BE5D35AA210D}"/>
+    <hyperlink ref="W48" r:id="rId169" xr:uid="{F4F18070-3D05-4C13-9FC0-E1CAEE2C298C}"/>
+    <hyperlink ref="X48" r:id="rId170" xr:uid="{9D3DD41D-E6B7-4A66-90F5-DA101EE0639F}"/>
+    <hyperlink ref="U49" r:id="rId171" xr:uid="{37DF9766-35C2-4931-9050-52225F820DC3}"/>
+    <hyperlink ref="V49" r:id="rId172" xr:uid="{C572019C-3F0D-4B1D-B5DB-DA26B0905CEC}"/>
+    <hyperlink ref="W49" r:id="rId173" xr:uid="{467FE25C-EAA6-47BF-A1D1-C1B722436838}"/>
+    <hyperlink ref="X49" r:id="rId174" xr:uid="{C1E989C2-EF0A-404E-B4BA-58E845190560}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno VTR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF13174-F61E-4682-8ACA-5ABFD4F9EB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C44439-C3C5-4E81-9CBE-0CDF5A4E7214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="438">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1532,6 +1532,24 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1_k81iD8sO1N3-jqZHJHpo_yONU6UPC_b</t>
+  </si>
+  <si>
+    <t>1-3NWP0QWL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radal 1498 casa 18, Quinta Normal </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18UqvbkY3KeodgQJgaRGa92vrL3i_O1pb</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HyRdfZAs5_cmlSTaVTCGJS2e-A3Si_-a</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1pSmPYRJRf0QplqEC0KyyTvvIYPYhPtOJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se instala extensor sin cable utp a petición de cliente </t>
   </si>
 </sst>
 </file>
@@ -2384,8 +2402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ49" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ49" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ50" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ50" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="25"/>
@@ -2635,7 +2653,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -7504,187 +7522,291 @@
         <v>-</v>
       </c>
     </row>
+    <row r="50" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46287.316370625005</v>
+      </c>
+      <c r="B50" s="10">
+        <v>9</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T50" s="3">
+        <v>4</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="V50" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="X50" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="Y50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB50" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="AC50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH50" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI50" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ50" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{24840A53-0D9F-4FB7-9829-AACFF35D7A4C}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{E31E9C56-13DA-4818-B898-2EECD0FD0911}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{CBEF14D8-DA20-4298-9D99-81D9D34D22CD}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{18EE46B3-BAF2-4A54-B7BF-DC495A8CD38B}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{9B67D365-2592-476F-8589-9D69CB19E659}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{D2D517AB-417F-41A9-8A16-C3AEF237A2A4}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{E0BC0518-9783-4BC3-A7D3-7AD304C98105}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{608DD207-09D3-4438-A7E0-FCF7FD6189DF}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{39E9A11D-2204-4C76-9FDD-8BCA2E7111D1}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{D6410C08-D394-4B72-9AA4-7C7966569333}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{B9F86F9A-142E-40A3-809F-FC020E270902}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{296E9C1D-30D0-46EB-A392-8EBBC73C9775}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{415BA41B-2377-4ED2-93B5-A09CD9A7A56A}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{8D2BCA0A-CFC1-46FE-8303-AD42FE73C30B}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{19645437-02D9-43EE-815E-E30E932637FE}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{2D7EF939-91A4-4A3A-8DB2-7E4A5946036F}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{F33AEBDC-4B36-4AD4-990C-BAF8747748EB}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{835B2419-A752-4C2E-9903-C30AA2739042}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{04CEA735-E69D-411B-9D75-5DBDC9AC9215}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{F0820406-43AF-433C-98D6-96A868F77C6E}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{A12E5D97-FED9-4EF6-8BE0-B8731BA36D82}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{0B4472D5-1B42-445E-8EF7-4AB24461AA23}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{AE90C0B1-3D48-416F-B5F7-84792414AF2E}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{461D1D29-A84E-4A9C-BE4F-AFBA8882E853}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{0165C924-91E4-4A84-97C5-815BFB88BAD2}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{6FEE2985-3446-4D47-9ADF-38015AB6C8F7}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{5A8354D9-F678-43E1-8514-510E38B7041C}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{1BF0D57C-0600-4E6A-A5E2-F3D200491043}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{A26ED909-7E7F-4447-A9F0-B517C6CA0984}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{E3E891AF-F38E-44D5-A291-56D702B096E6}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{2AADE899-D8B3-4098-BED6-51A60C83C267}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{F780BCA8-3F46-4FD8-90BB-4FA92C5F6B36}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{84BCD973-5836-4FBC-AA6E-196511A42517}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{19334CA5-682A-4DB6-B811-08FAF68A7A92}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{5CD8D155-9258-4FDC-9D21-8C08583B217E}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{3E2548FD-728E-42A2-B191-5C04575FDFE7}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{C6F996FB-ECCF-4457-87BC-885ADD3FEFBB}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{DCF12ADA-DCB3-4F71-8802-15A4B55C5F35}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{358A87F5-FB3E-41FE-844D-E12FCA28182F}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{0D16291E-B324-4D53-9A75-AB8D26A5470B}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{C78561E6-6421-4D1E-9A47-D83BFA75DA4A}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{B055C7F4-BDF7-4CE4-893C-16EB5021D9C0}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{6831D432-1FE6-41F4-9FD8-E4B171707490}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{62A1B213-F2C4-4884-9C4E-835B63057EE3}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{FA8C5364-B4C0-4164-A04B-F18BE7FE2430}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{64B3AF7F-B2AF-4328-B75E-0DD01FE9C53A}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{4681BB06-00E9-4BEB-A8D6-F5C7FDFEEA8B}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{1D14EE08-9106-4D48-B486-E766EE11FF57}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{BADE6ED6-C03D-4208-8C2B-3628EDA5F68C}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{707C08C2-559F-490C-905E-DA18AA141F71}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{2361E213-9D6D-4AB0-9A29-C7F9758AD1A1}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{196363BB-14B9-4F55-8AE2-3E765C2C3EC2}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{1643F68F-AFEE-40F5-BB6D-0A5F9398D78B}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{332F80D9-7AD6-4C89-A46A-28F4F3AB9FC8}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{9A436988-A437-4315-A66C-EFFE554A52F2}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{87D520B5-BD1F-4545-A07C-79CB7362DDDB}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{C80DA050-6ADD-4ED9-A6F0-16409111C51A}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{397DEEB2-801F-408B-9B6D-F2DB9D937E33}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{21CE78B8-1B26-47F6-96CC-106502D7D965}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{29DBBCFC-01A9-4223-B2E9-B3F6E48F8CF1}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{8BD8B9F9-A794-4CEC-9615-A5438306B42E}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{6C25E9FA-64D2-42D1-B158-951F6DD3333D}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{430B76F2-E1AE-4AB8-A96B-66CB67DE997E}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{1B36DE0E-31E8-44C8-86E0-F23D369B5CC9}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{0FC6F7A1-ADEA-4A4B-BFAA-C214CC4B4CFF}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{AB1C528E-86EC-46DD-914A-F07D2EAC9872}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{7126E654-BD5A-47FA-8D07-8314DF2A32AA}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{5CC96FEB-6958-47B9-BD84-E793F3C164C8}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{45187E00-F92E-468D-981B-50D96B3638D9}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{A94C2308-729F-4596-A11F-C0D1D7218146}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{E0342F70-769B-49BC-B135-4B40289FA661}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{68620238-3EDB-4F8F-B6FC-B86E7835B50D}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{E6A9D1FE-01F2-475E-9893-3B664E1DEED1}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{BE9C924E-8157-41FD-834F-A63278782421}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{EBC9C468-B7C0-4D42-8AC0-81D3716E0C4B}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{F9B82B02-6088-4336-80EF-C70171C9EFA3}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{DB30266A-2CE1-4CBA-B5DA-BA5E1D7951CC}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{2F420E44-6A5C-4AA0-8ADE-FDE5557C61B3}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{3681C826-FA7C-4EB8-9A1C-503DB4D9600B}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{66E13639-4F49-4312-98BB-3A1DDBF80E6D}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{670B7EFC-818D-4702-A1C6-A61A71FFB352}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{5D114BEF-2EC0-42AC-854A-9C6E2686CA62}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{8104CE66-06DD-423B-9BA5-46348F12F613}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{6B1F7169-FED2-4681-923F-E14F89865C9E}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{0369BB86-E134-492C-BE04-DC95E8B02C48}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{5F3F11CF-B8E4-4D23-939E-EEE75AB96D10}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{FD571A49-4435-4E4C-B320-5FF6579037B5}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{51553996-102A-42C1-8A58-85AA95E00383}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{F28C1D5F-B4B7-4511-AB78-A12E9831AF33}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{D952BEF3-8FDC-4E22-98D4-90FE7D409544}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{1D8C70EF-603A-4DA8-96DA-DE882DC4C4CA}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{BFF6C83C-A60B-4138-A499-32066EE82ADE}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{A71F2ADA-4948-4FE5-B3D3-923161020D5C}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{384B3510-D834-43C9-AE12-17B7EF40D4A3}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{EA3030EC-7BB4-4F76-831C-4D3D54090B1A}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{3FB9533E-E1E0-4256-8FAE-C473EC794E66}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{1E05D3E1-B905-44E0-92BC-DC2A00CD55F8}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{EAB44384-75DF-47AD-BEC7-FECBBC4B0393}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{F1994D3F-622E-46D3-B7FF-16BF3AE809EA}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{4452FE24-8276-4CA1-AD47-16B2CD6958BB}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{F63C7613-07C7-44C6-88DF-A69C9BE1EB49}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{14CDA284-6E6D-4716-A799-1DEA36E07880}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{2D9F8725-D2B7-43AE-A0E4-3BA1C09F17EB}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{90D413F6-80DD-4081-92EF-8657ED37B063}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{9C0E4E4A-1781-4716-AE54-19CFAB7BA70D}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{ABD53ACE-D206-413F-B1E3-D701576C3AD1}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{DB2741B8-5384-4979-8878-22030CBAE765}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{A5D4A384-C26C-45EF-9E76-53C7BEFB9CDA}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{8875BE84-4A45-4511-9B7D-7E823CD294BF}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{2DCA0B60-F06D-4EFE-A61B-2BFF0C1D383F}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{BAA22668-0B1D-4852-8C63-12619BF4E2E4}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{8005E6C4-A51E-4C29-927B-0C58789354B4}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{A3C558A3-6240-4F35-A9C4-E1FF4C08254F}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{D584D751-2C6C-481E-B76A-98AA68DC7169}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{EB8383D1-DC4F-4960-B00C-D0CAA9575E35}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{D8CD5DD1-86A8-4BC3-B10C-7BD46BF86885}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{9D65C362-47C3-4AB5-B8E5-B6F3B540593F}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{5FD299A3-D8C2-4A66-B48E-BED837840472}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{97333630-2AA1-477F-A8AC-3EDEDBB20AC7}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{BDDAAEC6-AC94-4758-A047-5EFE7AF410D1}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{86539285-BD10-4AC3-BDBD-EBBC27B5C12C}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{E449785D-6C16-48D9-9921-2EDFC4EFD87A}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{06BF76DF-F9B9-426D-9E13-CECE7E8553FF}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{F0FC1FF2-77D2-46C1-A67D-D7C136F87B28}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{AAF804D0-93E0-4CBA-BC74-F18383752407}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{3F598118-19C9-4AD6-B2C8-A1C5B8DBF195}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{D2366979-9EEB-4AFD-8EF8-8DD567B9D893}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{99538AA3-F34F-4BD7-9C0E-A586B8FEE158}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{D78342CC-33C3-4093-8CD0-E112960CC07D}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{C43E8E65-1CFD-4E9C-945B-0454F6C7899A}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{A124DECD-A9D0-4A42-9F6B-957F3C36220A}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{AD7DDECF-473A-4EDE-AEDD-90C882B518DF}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{786A8733-9A93-4F2E-B727-C4E26BD1867F}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{63D2788B-5743-4FD6-B8F0-89E5B8D938A2}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{2D81C8B8-6F26-4413-8DDE-631883D9C7D1}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{F3221CAE-FD53-4989-B512-13F4F3463729}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{B82926E4-591D-433D-8403-CA8781B4F5E1}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{94287FF9-0624-40E6-AB64-D80142504892}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{2778DA68-C1B9-4242-9724-2F4E3206B05F}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{9971F478-0F4A-46FD-B444-D3E419C61BE5}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{737A2010-982C-4AD7-A08F-2EAA29C442D8}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{C63BCAB8-532C-4421-8958-24EE7B99E612}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{8806A5F9-DFB3-47D6-AAED-DDE89B114C70}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{7F22805F-713C-42EA-978A-A3A31906F946}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{42CD0C74-CC77-4E85-BC3B-DFAD372BFDBC}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{ADAC97E1-4CE1-46C9-8821-8CC74B308FC7}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{C2709819-0798-4AEF-9515-D985890BC33E}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{D4EE8B7F-2905-4E26-9364-02A2FD978A34}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{E12D2B30-9B5C-4B29-92A4-0F7961E26060}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{1DA5A7CD-209A-4AFF-971B-00EBB4A3D0DE}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{DF3EAD04-C798-4C1B-8BD4-D4528FED033E}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{9A7E10AB-3234-4A42-8D90-4C999C804192}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{E01D8228-6322-4E7E-B53A-9BA0C915560C}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{DE58A923-123B-4849-A5C5-D08FF1655911}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{B671CB43-D027-4D96-9983-9FACFB879450}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{AEA6D413-F728-422F-B12C-60D6F24FA33F}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{07707909-A140-4063-B094-EA9BB1A7A31A}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{37C8E2AD-FED0-4E02-9C87-709D608289BD}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{13CEA6F0-F52F-40F9-9DD7-13074D704F62}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{4734A898-132D-40CF-9F8E-7551A014D2BF}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{442CDB75-9EE3-4E35-B2C3-172C5E4877F0}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{3688F25A-2B00-4D9F-864D-C1E21D296960}"/>
-    <hyperlink ref="U47" r:id="rId163" xr:uid="{49639566-E494-4A88-AF8A-4CE6445AE87C}"/>
-    <hyperlink ref="V47" r:id="rId164" xr:uid="{D9D3A0C8-52D3-4443-B809-0CAFAACE1BFC}"/>
-    <hyperlink ref="W47" r:id="rId165" xr:uid="{222DB88B-143E-44FF-91E4-A83BF1A567B3}"/>
-    <hyperlink ref="X47" r:id="rId166" xr:uid="{8DE17295-1836-477C-90F2-F51325293385}"/>
-    <hyperlink ref="U48" r:id="rId167" xr:uid="{3730A5EE-8E66-43DB-8344-5716E65E7977}"/>
-    <hyperlink ref="V48" r:id="rId168" xr:uid="{4721ECC4-816F-4E29-B1CC-BE5D35AA210D}"/>
-    <hyperlink ref="W48" r:id="rId169" xr:uid="{F4F18070-3D05-4C13-9FC0-E1CAEE2C298C}"/>
-    <hyperlink ref="X48" r:id="rId170" xr:uid="{9D3DD41D-E6B7-4A66-90F5-DA101EE0639F}"/>
-    <hyperlink ref="U49" r:id="rId171" xr:uid="{37DF9766-35C2-4931-9050-52225F820DC3}"/>
-    <hyperlink ref="V49" r:id="rId172" xr:uid="{C572019C-3F0D-4B1D-B5DB-DA26B0905CEC}"/>
-    <hyperlink ref="W49" r:id="rId173" xr:uid="{467FE25C-EAA6-47BF-A1D1-C1B722436838}"/>
-    <hyperlink ref="X49" r:id="rId174" xr:uid="{C1E989C2-EF0A-404E-B4BA-58E845190560}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{60280969-4C05-45B8-8DAC-792C20A21FF1}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{C49349F3-FB06-40A9-9FEE-C1518F81CB44}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{1072A1AF-87D4-458F-9F43-211BADDC5643}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{A59D2BDC-7FF5-481E-8ABA-A1B4922DC61E}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{597F033F-C858-4D95-B7F0-09FC23ECA8F2}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{54A7FB09-9E5B-4566-8FC2-CACA3E74DDBA}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{7BDE6B6B-7860-4AEB-AC6D-3A4F034CEDCF}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{A4F98DA6-6AFD-44A8-8B14-B063D1FEC609}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{B56314BF-034B-4613-894A-386434CACD9E}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{347287C9-BC9E-4007-ADCD-C89705F3585D}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{6EC4B715-B8FB-45E6-BBBD-E035BE8F6BA1}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{7055F46D-B028-45D6-9D91-142AB688DD93}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{950FAE59-9C69-4A89-9F26-5CD1949C5291}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{6D323449-C8EE-4C7F-A9D9-2B21660887D3}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{A264C511-78A6-43C1-A383-1932C98F9453}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{F8BF22A5-5347-4F53-A784-AB48EE5634ED}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{49FC44D3-61F1-4449-AB87-5F8BC21081AF}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{DD219BAD-490A-4CDB-B50B-1EA886EADABD}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{F8699B30-E83E-490B-BD28-7B77FD679A09}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{572209D8-2310-4A80-BC42-599A3151975D}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{D62BE699-37D8-4BD8-895C-FA6682ACCECB}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{22A9F273-3F9F-4BF1-A8E1-182EA82ED0A0}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{820E57F7-6EF3-4141-A8C8-9E850A02F7BD}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{8757353A-4CBB-497C-9687-61BA82A45F76}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{EBF9B388-0598-4DC0-A030-AD04BD233207}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{2EE4BE17-FC28-4AD5-9CDE-306EAA8FCAE9}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{DDAD9C1D-2D89-4848-8EB2-0B7EA8075F6A}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{730EC768-2F64-446C-9E51-AF9FE57701B0}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{D8D8D350-51E7-4107-988A-924C11B6A67F}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{E8CA14C7-1C18-4595-992B-9E068E2C8D51}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{55A02C3F-2D4B-4C6F-9EDB-E13D620F640C}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{3B3F197F-DE49-4361-A0CD-885F589515A6}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{DECE774C-A2E4-486C-AA35-CED11E990F7A}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{0FAA765E-E194-4173-AF11-61D2B64BE70F}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{2B7BE6C9-61C7-43BB-8871-9E1FD3CEEA61}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{84F38CEC-4793-462F-8AFE-3CF458691014}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{4C2AFB27-0237-429C-A391-7027CC0724F7}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{9DD97C5C-6265-4591-8972-3482E8A6BBE7}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{FBA6CD41-939E-4084-A18C-46BE6D870895}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{B4F7F8D3-623B-4F5C-AABB-E7959820D2BC}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{A46B10F4-66F5-4EE9-9160-15D588963AB2}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{D4CEA82F-7D89-404A-A569-31F0A6265E2A}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{9C419958-C4A0-4B9F-93EB-CEA11CEE5EB0}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{60EA7058-5910-491B-8D4A-73BCDFCCD82F}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{D43AAF9C-99DA-4A7E-8451-F7C189F6504F}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{12353CE2-8E11-41A0-8214-CD7E6A93C958}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{5E83BB8D-FCCB-4FA4-AF77-D23EC1CD82E6}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{EA64F158-EE87-4AC5-977F-9DD5E51C6597}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{2394837C-6E80-4EC7-9D61-AD5627AE7D56}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{F5F7B514-9391-447D-A247-9779DB791609}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{CC61B56B-C6B9-431E-83A5-6D660A07D700}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{A5DB4B00-E709-46C3-8416-79E72F6E4D24}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{99226092-C430-4A41-AE30-8D4A10D679F1}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{3EC6DDE1-0590-407E-9C13-24C5A3F43E0B}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{733B8580-D375-4ECB-9377-768BF4D9604B}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{265CDCF3-D352-46E8-AA46-B70EE0AADEA7}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{3771804C-05D8-43DB-824E-35BB0266653D}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{87E723A5-5B95-4F14-A953-EFD61A120FA0}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{3992CED9-3D65-49EF-89E4-D22BDE428588}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{68C0B37F-C6D3-480F-94C4-E40CFBF2A271}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{21FA6FB2-96EF-4371-9F99-183C7CC08D77}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{C5967A64-F98C-41DF-9D70-5B80E27224EF}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{C5EF43D6-C063-4C7B-9D2F-ABBB86FAF141}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{7815962B-D25D-4FAB-9F0E-14F796BFE231}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{3B9EA14E-672F-4012-BDD1-921BC073016E}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{851C45FF-4BFD-4BFE-9F63-4420C0ED9D3B}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{13899E81-4784-493E-9C59-676DBE13B84F}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{15F601F9-FA7D-40A0-87E2-0ADC9A29A313}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{C0409B5C-AD39-4F9C-8D5B-8B8B47A3F475}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{71E1C45D-FF81-42A5-903A-2E93F9A2D82E}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{34DBCA31-7A23-40F9-994C-61CA69D79726}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{C452D671-0B49-4608-93CC-49C38FA5F1B3}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{417D31CD-7694-4237-B23D-F4247A460997}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{9C795611-FDA3-4249-B4B9-AF3B6F8ACECB}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{A4550A94-CF6B-4373-95EC-AF97B5BC9787}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{404E787B-0E71-4B2C-B974-EE54C578FD6A}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{5AAF7280-ADCB-48EA-A5AA-D2025D10519C}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{AACAA574-EE32-4E29-8E48-9F28624F93AE}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{E9DCEC2F-AC90-4FF3-A2E8-7A455F7D07DD}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{D7C1E598-9452-4945-989F-0D24D8E28E9D}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{C3FC1F0E-612B-4AF2-94A8-839C9854DC97}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{70055CC1-218A-4CB8-82FD-E1BD557CF5CF}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{86D612BF-5BFF-4B6F-9D5F-4EEB18A7796D}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{A26425BF-DD3B-4454-8A3A-EBCABB6160A6}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{29DE5BDD-7055-4057-A914-7B272769311B}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{C64DC4B9-3050-45C0-9FFC-AD7D794D6FA3}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{43CA7DD8-75E6-484D-ADE1-254271AD4BCF}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{6154A050-007A-46F7-96A4-109BCCD73641}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{20F53C4B-6B75-4C38-B60B-CC0C415AF24D}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{63941D71-9778-4401-B1A7-3D9A6490DA4E}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{4BD89CCA-4D26-4F90-AF9B-270E915A10F4}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{D7153AB6-33BB-4DD2-9957-0CFACE41F030}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{D70800BD-75D8-4613-984B-BE23E8F8892D}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{83DB92C3-2A1E-424A-9892-E8E77D1AB441}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{0F59C6F4-9902-46F3-B60B-464B13116083}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{28EFB803-69CF-4E4F-9F41-FF3A5ECD9BA1}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{A436E968-0268-411D-BBC6-7158B175725E}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{AFEAE60F-5422-46A8-BF19-ECAF712F172F}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{EDFAE9CC-E7D9-4BC7-9A89-5C00EF857665}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{AB98CFAB-A573-462B-BD8F-E5AC54316D9C}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{3F44D9AE-B6D9-4586-9ED8-A6A8E996ACFA}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{1E2CF4A6-4FFA-4690-B9B0-4C40E6DDBC99}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{8B750292-E7FE-4EE6-B016-253BBB19EA70}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{62C16B21-88AA-4AFD-A864-22A49713A17B}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{AEAC82CC-2374-4B81-877E-297F7A70903E}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{145C5DE5-34C0-4A54-A4A8-CB5CCCD4AD88}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{98B852ED-BC24-4393-8BC6-021006D039CD}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{9AB518FA-00F3-42CF-987C-FA5C668E6A74}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{F0432DD7-86DC-4C13-87F6-6E712646DC16}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{3822F8DE-666B-4431-B40C-4C9F0D4A1587}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{C0C8F61E-2E1F-466B-A0F8-FD9E1A8CF69A}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{A7297C5B-4E10-4B74-95BE-87E5319E7545}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{867E8EC5-53D2-4B38-89CB-5C7456E4B433}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{1AE0B0E9-F755-41FE-95C3-158FE4F23477}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{D4B86CD5-2162-4C77-8E78-BACABDE05BFD}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{A36853F7-8C3B-492E-AB9C-1FBAFC00723C}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{88020604-FEA3-42CF-B420-4BDA8750DFA0}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{B39A46C1-4DFE-4A8D-A2CF-9136711E24F8}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{5CC684A8-EF55-4077-9674-066285D1F8D5}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{C13B8867-7C87-4886-AF94-E4785A1859C0}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{4B1B3334-3082-421A-BDA5-5B7F2A4C9608}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{E1598CC6-59B8-49A3-B8AC-65A429CC7C8C}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{E6A2359F-5508-49C7-A9D2-7E8466A19D3E}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{2601B2D5-5EE8-4704-806F-CE69297D5BD2}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{3C979135-0A70-47E1-B698-77A4D8B59F64}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{19F8F05C-544B-40FF-A32B-E1D71982F55B}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{41E25DB1-2222-49D8-9F76-8593E7A5E220}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{9FAC0850-0897-4F4C-A688-33EF7839C249}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{4CC0972D-251C-49F4-B164-A0F5EC39B6CB}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{5A7B5FE7-D7C9-426E-B883-5DDE3813AC3D}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{2E02FD53-EE2A-4D62-9F98-B77DDD0B7551}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{E0673AAF-DE72-4958-9CAB-1B4F5CD29B8D}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{2F580A05-1E40-48DA-AA0F-7743BD903527}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{7037269F-9418-454F-A61B-9963BE130B23}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{6A5FDCD7-D31F-4B87-B1A9-D543D1448974}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{683814BA-F3A5-4D92-B56C-81A5C0AF2026}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{21BB2034-0A78-4A67-97CB-851958998385}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{27E11BE1-06E8-42F7-A2BA-076EAF219728}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{0929BF70-85DB-43FF-831D-E73813C2E074}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{82C14AA2-4A50-483F-9E09-418F2A3C426D}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{D619BAEA-C436-484B-9E13-C069763700D8}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{AAFF4C99-8866-4E2D-90F8-C1F6D71993E5}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{09FC4D9D-E915-4D06-AE0E-3160BF0D6842}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{C1FA22A8-93BD-4B5C-83B8-3ECD90CA869B}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{D9D41D77-6A72-442E-A4B0-5756854D771F}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{0732B99C-1F21-4519-8E91-5BDC1F971F5B}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{9F2B455B-DEF7-4C10-BB37-49A7267F1E3E}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{40AB449B-EE32-4940-9710-9498E6E7ECA6}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{24B86EC9-9EC5-4ED6-BBC6-5F551A76ABB7}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{FD865ACB-538E-4B2B-A9EE-BEB052F7D2EE}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{F0DFAA6C-5BE1-45F5-925E-68F85E46BDFD}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{AB67E4E4-95C0-4A3E-A5DE-2C2FE5C66A09}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{ECB28427-172D-45F3-8F76-A8995F558EEC}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{05909992-C319-465C-A63C-812977856BA9}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{FB40CF2E-9152-4266-8C53-B90E73A671AB}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{BA678044-5E6B-42C0-A9BD-3012E4785E3A}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{5CED3A4F-6AA4-4FFF-8369-10CD3C90123F}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{A5B28CC1-FDBB-49FF-A796-08E147FDE9EB}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{9C1BE70C-DEC6-48BA-99DD-9F92C24D2366}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{61C2B1DC-B878-4DFA-851D-24008A390511}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{CA43A30A-A19B-4847-A030-1C8316669F85}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{335B2EB1-D4E4-4FB4-BC90-60CB9FDBC190}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{2069C53B-B6DB-4D61-9B2F-F819A1330371}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{325F1155-DCE5-4544-B0DE-1711555CAE5C}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{EEE19D61-07FC-4F62-A383-47774CADC44B}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{63DA9FD3-04B4-41EF-A4CE-B6127A648731}"/>
+    <hyperlink ref="U48" r:id="rId167" xr:uid="{33589F7E-693A-494A-AD3A-4795B596B8CB}"/>
+    <hyperlink ref="V48" r:id="rId168" xr:uid="{28A6ED11-A321-46F7-9B86-E3727E3A7C7A}"/>
+    <hyperlink ref="W48" r:id="rId169" xr:uid="{E0B592FE-300C-4772-9C51-B22F5FB80CB0}"/>
+    <hyperlink ref="X48" r:id="rId170" xr:uid="{EE74E89B-4844-4FB8-8D13-CFDAAFAF0488}"/>
+    <hyperlink ref="U49" r:id="rId171" xr:uid="{FA0C5D0A-AA2B-4E1C-96E2-F2DD88803A32}"/>
+    <hyperlink ref="V49" r:id="rId172" xr:uid="{ABE95339-DB6F-4303-A3B0-6A5E320E0CA0}"/>
+    <hyperlink ref="W49" r:id="rId173" xr:uid="{D2D77F45-DA36-4979-9812-0908D51FFAA2}"/>
+    <hyperlink ref="X49" r:id="rId174" xr:uid="{507D6960-6871-45B4-BBEB-CFDB20707256}"/>
+    <hyperlink ref="U50" r:id="rId175" xr:uid="{98D4AF68-6A29-41DA-9FD4-AEDE3BB1209F}"/>
+    <hyperlink ref="V50" r:id="rId176" xr:uid="{DF8EB615-E31B-4827-A4E6-DA490BE367F6}"/>
+    <hyperlink ref="X50" r:id="rId177" xr:uid="{CC6C0CAC-96C6-4DC9-B8CE-D82058800B3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId175"/>
+    <tablePart r:id="rId178"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno VTR\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C44439-C3C5-4E81-9CBE-0CDF5A4E7214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC540340-D94D-4040-9A96-B7ED2E5CF293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="477">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1550,6 +1550,124 @@
   </si>
   <si>
     <t xml:space="preserve">Se instala extensor sin cable utp a petición de cliente </t>
+  </si>
+  <si>
+    <t>1-3NYDXWDZ</t>
+  </si>
+  <si>
+    <t>Jose Joaquin Perez 5002, Quinta Normal</t>
+  </si>
+  <si>
+    <t>Xion yung</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SVjdL1SREykm7ChzJpenb8I47kfK1UzE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12LZ9p5FtvnC68vpX9IRY0k7Kt2z7ctyX</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Gu2K57sxhqPfh1X9tDm9uMhxRJwc6BsI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1WY8wTjEVAmSVDGt_l_SmDLZojmOg5Fh9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roseta fuera de norma, no utiliza tornillos, cabe destacar que cliente solicita instalación en ese lugar del restaurante </t>
+  </si>
+  <si>
+    <t>1-3NULQF4Y</t>
+  </si>
+  <si>
+    <t>Renaico 20</t>
+  </si>
+  <si>
+    <t>Mariela Salinas Olivares</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cESVRqpdJjeOszcnv3Da_BgsOU8HvWdM</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1i3FZTherkoIMBaWCLspoJ6BJNJLyaqHM</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Ju5vTKFWsmbCWbXDH0-DKehIc1kUdVDr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=170uojWKRP6agDUOtvY7h7RA3eY8EctjO</t>
+  </si>
+  <si>
+    <t>Técnico cumple con protocolos.</t>
+  </si>
+  <si>
+    <t>1-3NWS5VBF</t>
+  </si>
+  <si>
+    <t>Cuarta 203</t>
+  </si>
+  <si>
+    <t>Nicolle Bazaez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1A5zdCYMDpDZbe2cOK2q_w86m0nlqlS6y</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1hwnvV18sbklFOftopkLg9K9ph8gM_K2A</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YA4tvvOzypDQxKSpvGyr7KS0raSthwVO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Jgo67AwJBKn-PzuLf_j0B0y11n39Prjv</t>
+  </si>
+  <si>
+    <t>Reparación del servicio conector y roseta , sin pasamuro drop ya instalado.</t>
+  </si>
+  <si>
+    <t>1-3NU93QNJ</t>
+  </si>
+  <si>
+    <t>Dickens 73</t>
+  </si>
+  <si>
+    <t>Mauricio Aguilar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1t0rl7ZhanneL1kDYdamFHO1ClKyQzDhu</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FTpaTqw8FzFwWFFZV4c94VfZwU0M7dwr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1CqgCiO4Jg6z0ZZwXbYOZqc6zcSupYUOf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12_1fCYbIYsFxLMEREWMJfYoHwjfo8zSf</t>
+  </si>
+  <si>
+    <t>1-3NQE982C</t>
+  </si>
+  <si>
+    <t>Vicentico 163 - A</t>
+  </si>
+  <si>
+    <t>Decía Moreno</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1eoQygdTcLraes4KFY9NrbNhXgsAMY6CS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZEMVSFWl7lIlcjueJPB8r3jhcFV07qjb</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=143zIjtMBlBRGuy39Zy1SCu8sN8bC_HLf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18iqN_nNvmsQsFAuH2O4vwZLe9hq91gh5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico cumple con protocolos
+</t>
   </si>
 </sst>
 </file>
@@ -1729,6 +1847,42 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2195,6 +2349,24 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2220,60 +2392,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2402,43 +2520,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ50" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ50" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ55" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ55" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="29"/>
-    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="1"/>
-    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="28"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Quien recibe en domicilio" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Nota de Estética del cableado " dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Fotografía  Módem" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Fotografía Roseta  Óptica Atornillada " dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Fotografías Pasa-muros " dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Fotografías" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Estado Auditoria " dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Técnico cumple correctamente con su función?  " dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Con que nota se evalúa al técnico " dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Observaciones (detallar observaciones)" dataDxfId="5"/>
+    <tableColumn id="33" xr3:uid="{6654FF87-3155-4898-9A65-816C7D124028}" name="Utiliza OneClick para realizar limpieza a conectores " dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{2662FBBF-EEE5-4E82-98C0-8584BF84424E}" name="Drop se encuentra encuentra dentro de norma de instalaciones " dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="27" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2653,7 +2771,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -7623,190 +7741,718 @@
         <v>-</v>
       </c>
     </row>
+    <row r="51" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46287.763552685181</v>
+      </c>
+      <c r="B51" s="10">
+        <v>6</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="T51" s="3">
+        <v>4</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="V51" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="W51" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="X51" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="Y51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB51" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="AD51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH51" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI51" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ51" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46287.95001443287</v>
+      </c>
+      <c r="B52" s="10">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="T52" s="3">
+        <v>4</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="V52" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="X52" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH52" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI52" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ52" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>Auque se nota una mejora, se realizara evantualemete seguimiento a los trabajos</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46287.957272013889</v>
+      </c>
+      <c r="B53" s="10">
+        <v>7</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="T53" s="3">
+        <v>3</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="V53" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="W53" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="X53" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB53" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="AC53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH53" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI53" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ53" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46287.965805486107</v>
+      </c>
+      <c r="B54" s="10">
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P54" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="T54" s="3">
+        <v>3</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="V54" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="W54" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="X54" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH54" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI54" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ54" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46287.972631261575</v>
+      </c>
+      <c r="B55" s="10">
+        <v>10</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P55" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="T55" s="3">
+        <v>3</v>
+      </c>
+      <c r="U55" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="V55" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="W55" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="X55" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA55" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB55" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="AC55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH55" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>-</v>
+      </c>
+      <c r="AI55" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ55" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{60280969-4C05-45B8-8DAC-792C20A21FF1}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{C49349F3-FB06-40A9-9FEE-C1518F81CB44}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{1072A1AF-87D4-458F-9F43-211BADDC5643}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{A59D2BDC-7FF5-481E-8ABA-A1B4922DC61E}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{597F033F-C858-4D95-B7F0-09FC23ECA8F2}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{54A7FB09-9E5B-4566-8FC2-CACA3E74DDBA}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{7BDE6B6B-7860-4AEB-AC6D-3A4F034CEDCF}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{A4F98DA6-6AFD-44A8-8B14-B063D1FEC609}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{B56314BF-034B-4613-894A-386434CACD9E}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{347287C9-BC9E-4007-ADCD-C89705F3585D}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{6EC4B715-B8FB-45E6-BBBD-E035BE8F6BA1}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{7055F46D-B028-45D6-9D91-142AB688DD93}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{950FAE59-9C69-4A89-9F26-5CD1949C5291}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{6D323449-C8EE-4C7F-A9D9-2B21660887D3}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{A264C511-78A6-43C1-A383-1932C98F9453}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{F8BF22A5-5347-4F53-A784-AB48EE5634ED}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{49FC44D3-61F1-4449-AB87-5F8BC21081AF}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{DD219BAD-490A-4CDB-B50B-1EA886EADABD}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{F8699B30-E83E-490B-BD28-7B77FD679A09}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{572209D8-2310-4A80-BC42-599A3151975D}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{D62BE699-37D8-4BD8-895C-FA6682ACCECB}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{22A9F273-3F9F-4BF1-A8E1-182EA82ED0A0}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{820E57F7-6EF3-4141-A8C8-9E850A02F7BD}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{8757353A-4CBB-497C-9687-61BA82A45F76}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{EBF9B388-0598-4DC0-A030-AD04BD233207}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{2EE4BE17-FC28-4AD5-9CDE-306EAA8FCAE9}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{DDAD9C1D-2D89-4848-8EB2-0B7EA8075F6A}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{730EC768-2F64-446C-9E51-AF9FE57701B0}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{D8D8D350-51E7-4107-988A-924C11B6A67F}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{E8CA14C7-1C18-4595-992B-9E068E2C8D51}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{55A02C3F-2D4B-4C6F-9EDB-E13D620F640C}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{3B3F197F-DE49-4361-A0CD-885F589515A6}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{DECE774C-A2E4-486C-AA35-CED11E990F7A}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{0FAA765E-E194-4173-AF11-61D2B64BE70F}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{2B7BE6C9-61C7-43BB-8871-9E1FD3CEEA61}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{84F38CEC-4793-462F-8AFE-3CF458691014}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{4C2AFB27-0237-429C-A391-7027CC0724F7}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{9DD97C5C-6265-4591-8972-3482E8A6BBE7}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{FBA6CD41-939E-4084-A18C-46BE6D870895}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{B4F7F8D3-623B-4F5C-AABB-E7959820D2BC}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{A46B10F4-66F5-4EE9-9160-15D588963AB2}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{D4CEA82F-7D89-404A-A569-31F0A6265E2A}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{9C419958-C4A0-4B9F-93EB-CEA11CEE5EB0}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{60EA7058-5910-491B-8D4A-73BCDFCCD82F}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{D43AAF9C-99DA-4A7E-8451-F7C189F6504F}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{12353CE2-8E11-41A0-8214-CD7E6A93C958}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{5E83BB8D-FCCB-4FA4-AF77-D23EC1CD82E6}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{EA64F158-EE87-4AC5-977F-9DD5E51C6597}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{2394837C-6E80-4EC7-9D61-AD5627AE7D56}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{F5F7B514-9391-447D-A247-9779DB791609}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{CC61B56B-C6B9-431E-83A5-6D660A07D700}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{A5DB4B00-E709-46C3-8416-79E72F6E4D24}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{99226092-C430-4A41-AE30-8D4A10D679F1}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{3EC6DDE1-0590-407E-9C13-24C5A3F43E0B}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{733B8580-D375-4ECB-9377-768BF4D9604B}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{265CDCF3-D352-46E8-AA46-B70EE0AADEA7}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{3771804C-05D8-43DB-824E-35BB0266653D}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{87E723A5-5B95-4F14-A953-EFD61A120FA0}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{3992CED9-3D65-49EF-89E4-D22BDE428588}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{68C0B37F-C6D3-480F-94C4-E40CFBF2A271}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{21FA6FB2-96EF-4371-9F99-183C7CC08D77}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{C5967A64-F98C-41DF-9D70-5B80E27224EF}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{C5EF43D6-C063-4C7B-9D2F-ABBB86FAF141}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{7815962B-D25D-4FAB-9F0E-14F796BFE231}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{3B9EA14E-672F-4012-BDD1-921BC073016E}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{851C45FF-4BFD-4BFE-9F63-4420C0ED9D3B}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{13899E81-4784-493E-9C59-676DBE13B84F}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{15F601F9-FA7D-40A0-87E2-0ADC9A29A313}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{C0409B5C-AD39-4F9C-8D5B-8B8B47A3F475}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{71E1C45D-FF81-42A5-903A-2E93F9A2D82E}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{34DBCA31-7A23-40F9-994C-61CA69D79726}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{C452D671-0B49-4608-93CC-49C38FA5F1B3}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{417D31CD-7694-4237-B23D-F4247A460997}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{9C795611-FDA3-4249-B4B9-AF3B6F8ACECB}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{A4550A94-CF6B-4373-95EC-AF97B5BC9787}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{404E787B-0E71-4B2C-B974-EE54C578FD6A}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{5AAF7280-ADCB-48EA-A5AA-D2025D10519C}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{AACAA574-EE32-4E29-8E48-9F28624F93AE}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{E9DCEC2F-AC90-4FF3-A2E8-7A455F7D07DD}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{D7C1E598-9452-4945-989F-0D24D8E28E9D}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{C3FC1F0E-612B-4AF2-94A8-839C9854DC97}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{70055CC1-218A-4CB8-82FD-E1BD557CF5CF}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{86D612BF-5BFF-4B6F-9D5F-4EEB18A7796D}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{A26425BF-DD3B-4454-8A3A-EBCABB6160A6}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{29DE5BDD-7055-4057-A914-7B272769311B}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{C64DC4B9-3050-45C0-9FFC-AD7D794D6FA3}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{43CA7DD8-75E6-484D-ADE1-254271AD4BCF}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{6154A050-007A-46F7-96A4-109BCCD73641}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{20F53C4B-6B75-4C38-B60B-CC0C415AF24D}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{63941D71-9778-4401-B1A7-3D9A6490DA4E}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{4BD89CCA-4D26-4F90-AF9B-270E915A10F4}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{D7153AB6-33BB-4DD2-9957-0CFACE41F030}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{D70800BD-75D8-4613-984B-BE23E8F8892D}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{83DB92C3-2A1E-424A-9892-E8E77D1AB441}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{0F59C6F4-9902-46F3-B60B-464B13116083}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{28EFB803-69CF-4E4F-9F41-FF3A5ECD9BA1}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{A436E968-0268-411D-BBC6-7158B175725E}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{AFEAE60F-5422-46A8-BF19-ECAF712F172F}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{EDFAE9CC-E7D9-4BC7-9A89-5C00EF857665}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{AB98CFAB-A573-462B-BD8F-E5AC54316D9C}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{3F44D9AE-B6D9-4586-9ED8-A6A8E996ACFA}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{1E2CF4A6-4FFA-4690-B9B0-4C40E6DDBC99}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{8B750292-E7FE-4EE6-B016-253BBB19EA70}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{62C16B21-88AA-4AFD-A864-22A49713A17B}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{AEAC82CC-2374-4B81-877E-297F7A70903E}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{145C5DE5-34C0-4A54-A4A8-CB5CCCD4AD88}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{98B852ED-BC24-4393-8BC6-021006D039CD}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{9AB518FA-00F3-42CF-987C-FA5C668E6A74}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{F0432DD7-86DC-4C13-87F6-6E712646DC16}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{3822F8DE-666B-4431-B40C-4C9F0D4A1587}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{C0C8F61E-2E1F-466B-A0F8-FD9E1A8CF69A}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{A7297C5B-4E10-4B74-95BE-87E5319E7545}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{867E8EC5-53D2-4B38-89CB-5C7456E4B433}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{1AE0B0E9-F755-41FE-95C3-158FE4F23477}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{D4B86CD5-2162-4C77-8E78-BACABDE05BFD}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{A36853F7-8C3B-492E-AB9C-1FBAFC00723C}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{88020604-FEA3-42CF-B420-4BDA8750DFA0}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{B39A46C1-4DFE-4A8D-A2CF-9136711E24F8}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{5CC684A8-EF55-4077-9674-066285D1F8D5}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{C13B8867-7C87-4886-AF94-E4785A1859C0}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{4B1B3334-3082-421A-BDA5-5B7F2A4C9608}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{E1598CC6-59B8-49A3-B8AC-65A429CC7C8C}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{E6A2359F-5508-49C7-A9D2-7E8466A19D3E}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{2601B2D5-5EE8-4704-806F-CE69297D5BD2}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{3C979135-0A70-47E1-B698-77A4D8B59F64}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{19F8F05C-544B-40FF-A32B-E1D71982F55B}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{41E25DB1-2222-49D8-9F76-8593E7A5E220}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{9FAC0850-0897-4F4C-A688-33EF7839C249}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{4CC0972D-251C-49F4-B164-A0F5EC39B6CB}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{5A7B5FE7-D7C9-426E-B883-5DDE3813AC3D}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{2E02FD53-EE2A-4D62-9F98-B77DDD0B7551}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{E0673AAF-DE72-4958-9CAB-1B4F5CD29B8D}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{2F580A05-1E40-48DA-AA0F-7743BD903527}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{7037269F-9418-454F-A61B-9963BE130B23}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{6A5FDCD7-D31F-4B87-B1A9-D543D1448974}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{683814BA-F3A5-4D92-B56C-81A5C0AF2026}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{21BB2034-0A78-4A67-97CB-851958998385}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{27E11BE1-06E8-42F7-A2BA-076EAF219728}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{0929BF70-85DB-43FF-831D-E73813C2E074}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{82C14AA2-4A50-483F-9E09-418F2A3C426D}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{D619BAEA-C436-484B-9E13-C069763700D8}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{AAFF4C99-8866-4E2D-90F8-C1F6D71993E5}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{09FC4D9D-E915-4D06-AE0E-3160BF0D6842}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{C1FA22A8-93BD-4B5C-83B8-3ECD90CA869B}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{D9D41D77-6A72-442E-A4B0-5756854D771F}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{0732B99C-1F21-4519-8E91-5BDC1F971F5B}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{9F2B455B-DEF7-4C10-BB37-49A7267F1E3E}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{40AB449B-EE32-4940-9710-9498E6E7ECA6}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{24B86EC9-9EC5-4ED6-BBC6-5F551A76ABB7}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{FD865ACB-538E-4B2B-A9EE-BEB052F7D2EE}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{F0DFAA6C-5BE1-45F5-925E-68F85E46BDFD}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{AB67E4E4-95C0-4A3E-A5DE-2C2FE5C66A09}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{ECB28427-172D-45F3-8F76-A8995F558EEC}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{05909992-C319-465C-A63C-812977856BA9}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{FB40CF2E-9152-4266-8C53-B90E73A671AB}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{BA678044-5E6B-42C0-A9BD-3012E4785E3A}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{5CED3A4F-6AA4-4FFF-8369-10CD3C90123F}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{A5B28CC1-FDBB-49FF-A796-08E147FDE9EB}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{9C1BE70C-DEC6-48BA-99DD-9F92C24D2366}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{61C2B1DC-B878-4DFA-851D-24008A390511}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{CA43A30A-A19B-4847-A030-1C8316669F85}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{335B2EB1-D4E4-4FB4-BC90-60CB9FDBC190}"/>
-    <hyperlink ref="U47" r:id="rId163" xr:uid="{2069C53B-B6DB-4D61-9B2F-F819A1330371}"/>
-    <hyperlink ref="V47" r:id="rId164" xr:uid="{325F1155-DCE5-4544-B0DE-1711555CAE5C}"/>
-    <hyperlink ref="W47" r:id="rId165" xr:uid="{EEE19D61-07FC-4F62-A383-47774CADC44B}"/>
-    <hyperlink ref="X47" r:id="rId166" xr:uid="{63DA9FD3-04B4-41EF-A4CE-B6127A648731}"/>
-    <hyperlink ref="U48" r:id="rId167" xr:uid="{33589F7E-693A-494A-AD3A-4795B596B8CB}"/>
-    <hyperlink ref="V48" r:id="rId168" xr:uid="{28A6ED11-A321-46F7-9B86-E3727E3A7C7A}"/>
-    <hyperlink ref="W48" r:id="rId169" xr:uid="{E0B592FE-300C-4772-9C51-B22F5FB80CB0}"/>
-    <hyperlink ref="X48" r:id="rId170" xr:uid="{EE74E89B-4844-4FB8-8D13-CFDAAFAF0488}"/>
-    <hyperlink ref="U49" r:id="rId171" xr:uid="{FA0C5D0A-AA2B-4E1C-96E2-F2DD88803A32}"/>
-    <hyperlink ref="V49" r:id="rId172" xr:uid="{ABE95339-DB6F-4303-A3B0-6A5E320E0CA0}"/>
-    <hyperlink ref="W49" r:id="rId173" xr:uid="{D2D77F45-DA36-4979-9812-0908D51FFAA2}"/>
-    <hyperlink ref="X49" r:id="rId174" xr:uid="{507D6960-6871-45B4-BBEB-CFDB20707256}"/>
-    <hyperlink ref="U50" r:id="rId175" xr:uid="{98D4AF68-6A29-41DA-9FD4-AEDE3BB1209F}"/>
-    <hyperlink ref="V50" r:id="rId176" xr:uid="{DF8EB615-E31B-4827-A4E6-DA490BE367F6}"/>
-    <hyperlink ref="X50" r:id="rId177" xr:uid="{CC6C0CAC-96C6-4DC9-B8CE-D82058800B3D}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{B3A5F38D-EDDF-4828-9702-C9236BDDA9B7}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{0DBBD551-8C7D-4139-9ED9-5BDE1E334094}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{ADF2E360-2B97-4F58-A084-246C0C10B92A}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{36BBE5B7-5D5A-4E82-8C60-D590E2CF7C13}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{72756C59-CEA6-4F85-BF1F-5222701B2965}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{F6193FD9-0793-4B78-BFF8-8FBAE0C14110}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{89DEE9F3-78FD-44EE-A407-B96B8ED63102}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{BDACBDE8-FA90-45CA-860D-AA595DAE6E8E}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{D086C867-55E8-4453-ADB6-24592F5D59FF}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{43A91B99-61AE-4372-9269-E51D66A00DDD}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{71AEC4F9-BF37-4C31-861B-AF1A43ED7B44}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{1C6DE4B2-65F1-4133-A433-F41BC76C2387}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{8FD7B858-0037-42C0-8540-31F5F46D0287}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{04D79B66-0448-4AEC-AD03-65182619AE84}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{2DD75C4A-343D-4A6F-A3C6-5E6223FCE922}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{EDBD85DD-A477-4DD7-A907-0C9D82505968}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{A3B8A259-C1EF-4184-A8C9-F7D0A82BF7FD}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{326C3368-D659-47BE-A645-39811A8E47C9}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{C33BF675-F160-41AF-933D-BE0313775D8A}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{791AAB93-ABBE-416E-B98F-75377C9EA140}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{4064B3F9-3D52-48AB-AA9B-A75BADD14785}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{0A8F9A9D-58B8-439B-807D-EA61FCC8B500}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{1B9377A0-3A0A-4B99-890B-CB6C6DDCD3DE}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{B2350013-22C1-4AD2-8F6A-A3A3D475AE8F}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{0F4EEFFD-E65E-4FD2-ACBF-063353BCF6BC}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{89246D6F-54E8-444E-B3B4-725DEB9B531E}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{C711B2D4-B9C4-46DF-B46A-276207CAE1D2}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{F09D6CCE-581E-44DB-B382-3A31BA02F0F0}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{A859C2E8-F4E1-4110-9911-6188EF7DCC95}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{7A2017B3-9B48-42CD-9461-EAFE1C4FD378}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{07EDE847-D1E0-467D-97FF-4E57CADF23D8}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{9014AB93-6E34-4800-B759-1643FD662C1D}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{9D94A5CA-036C-45BC-8678-EBC36C446B6A}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{5EE07356-74A4-436E-B5FB-27AFD76E88FC}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{957EC399-D4D7-4CB5-83E6-53D9A4B6B13E}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{297CC1DB-ACE7-4E0E-A35F-533150A2B6D1}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{1BB6373F-AC5D-4F2B-875D-7E5E42151527}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{D3837138-72C0-426D-89F0-0C19850E1F01}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{7D3CED0C-8C48-4E42-B42E-48735E2A4066}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{B2995FF1-1CD9-401D-B851-2518B19EE9F6}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{E748B020-A150-4129-9B73-74526908DE75}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{0A0818DE-4D47-4797-8078-D4E3714FE21E}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{C47DA0BA-66C6-4E06-B8D6-654A01B71AC5}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{B971A77D-07C6-47E8-842B-EBCC2B6EEE75}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{8C36CC5C-8593-443C-BE70-E1B24EC96CC1}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{AFCCFB44-51E4-4765-ABCD-C78E65C58F09}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{34AD1948-8C8F-472C-B392-0D8C3D62FF76}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{A51C0DF1-5B78-4EB1-9183-A5E0C9AA7F5A}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{D8ECE85C-8B29-4A80-A51E-C66000C26C97}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{B93A55FD-4F61-443C-91E9-CEEE21EEE85A}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{6B04102D-7C33-4072-8B00-A865E399C755}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{24081079-3941-4058-B74B-E24034383CC7}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{6F49DB97-AB04-461F-B3D0-6E6FF1213F10}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{9B3783AA-EE0F-4BFF-8A44-03986686CDE9}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{25C9ECAD-8FEA-4483-B0ED-633016342628}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{09AD9FFE-7ADA-4B2D-9DB6-44397DFD2303}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{FB911DC9-C0E3-4785-A075-9D1FA301E83E}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{C5E1F554-4DB6-4155-A995-B5CD912B6929}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{D30CB38E-C2A6-477E-BEE6-73E8B86E1A89}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{1B974ACE-D3E7-4D2A-99B5-87FBB8912EAD}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{D5BF16D5-5E77-4AE5-98CC-56481098CF96}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{A413F3A8-E91F-4186-9013-5D6C07EDD444}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{626E6DB1-E61F-4A17-9E63-72FB8A714CF1}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{0DCD3BD5-C312-4A90-85AE-6B93DA4831D8}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{7589D367-014B-4EBD-B01F-CBB244E262D7}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{3DEFAFB1-1827-4C71-AA39-4F79AB10CBC3}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{1935C7C7-16D5-4962-84FE-96CB298A1B01}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{617E869E-F49B-4F60-8A31-F001E08D8FA4}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{90254925-5566-43F5-9B2E-36D595044B96}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{A38BB7DF-DC5C-40AB-8FF9-4C8CD4A068A6}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{7F577F91-B9AC-4BC5-93FE-397F937B69C8}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{3FBD07D9-794F-49BE-B021-A6E40B8293BE}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{606361BF-1DDF-423F-B72A-3F0934C929E1}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{7D616A24-973D-46D3-BD21-24610A72EC2C}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{F403BDB0-6E22-4E04-93CD-53E45844E9BD}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{DA8D3516-E373-425D-B187-A7988FDCABB0}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{054E9506-4713-4490-BEF2-7113BBDFB4D4}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{B914E51B-DE4B-4078-B648-333B67EE76A1}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{9437CCE1-0C88-47D5-AE76-33B1516948DC}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{481B7474-922B-455B-B6F0-1AF397E0A09E}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{7D862C7A-4DA8-4C80-9BCE-9D4F3DA0EDB0}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{F64A4717-4587-4C2D-A3DC-8ED0586790F8}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{F19ADEA3-60EC-4310-8CF8-35C3430A1687}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{B7AB6255-DDC7-4F76-8FCA-B86C3323875A}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{134E78B0-F7A0-404B-B11F-E50F3CC92630}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{625D8FAC-B648-4088-A6AA-81D0861AFC3B}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{DD8D8B68-F9A7-4280-A574-724EE3504AC2}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{46EE0927-9FFF-426A-BF64-7E3B200C6277}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{4EFAC31D-C0B2-4178-98F7-08AF216FBBA0}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{69841135-B4E5-46CD-80F9-B2276B921FDA}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{5B91C613-A24E-4B87-B635-11F46013AA99}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{DAB71918-2A28-4E73-99B9-5F6DC1981716}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{37298348-8393-4E58-BF21-0ADD54C30B43}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{14BD1455-C7DE-4A10-B662-0863D92E30EB}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{DEDEC98B-A9D9-465C-A9E0-E0661456ABE8}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{15E3A5D2-3A09-430C-AC1B-A53B3244F14B}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{33FAD053-7B3D-450A-8014-B1B93476EB87}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{2BC70F2B-C42E-4081-A865-CAED98225680}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{819C9EF9-2A2F-441D-B1A6-7FCD95C9E72C}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{032D570A-87A6-43AC-B32B-4E26D665E4BB}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{E5BAC028-569D-4724-AA2B-A303C682EBDA}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{F7748380-CAB6-4192-BD85-07AE76A18A36}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{8383526A-9DD5-4777-8356-C38E3EE7EFA9}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{2C41F98F-CD32-4934-884D-39ABC3AA39BD}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{00D5BF34-479F-49F0-B76D-609BD69460D8}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{B3811D3A-2AD7-45FA-A428-868FFB93E7B6}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{4353677B-A942-4B87-913C-4DBCB42F9E52}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{33B58678-09CE-4E06-9458-35E3192DE525}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{7B57022A-B29D-4A18-8FCA-68553821CEA7}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{9EFBA8B9-706D-4883-8FAF-05DECBD32F71}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{B332B00B-020E-4874-B5FE-FAC2957E038B}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{759EB46D-E26B-4F44-AC88-CBE7E86A58AB}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{182509CF-B2FA-4DCE-8D62-2F22FFB08654}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{6DF4C7AA-250E-4DC5-AED0-B16700050F91}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{D29C034F-96B6-45E6-BDD8-521FB7936400}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{CE3A9D89-78E7-40A1-B669-C6147493E290}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{7351CA86-2A1D-4CC2-8C2B-B471F138062B}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{B9F13B63-D6DE-413C-A65E-775C45D1DE4F}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{343555E6-FC46-4C94-93D8-DB38D42D937A}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{47E853F4-3ECD-4B0E-9BD8-D2F6A34B9A9A}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{1A421245-0304-4810-BF05-E809F398E76D}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{E47F4A91-3CD1-4ACA-9C89-67A162236878}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{44858AD6-57F2-4C8B-82D1-D0CF96B15B9F}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{D1A4C8F3-5D12-45EC-AAD3-39D577D81B18}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{DE9D6634-E1A8-4A7A-B9B8-543CCBB11B53}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{C4DDA06C-AEFA-4409-B622-AEDFB36A4FE6}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{D018DADA-D92A-4053-8B42-0CF3D45FE7EB}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{72A79916-B101-45B8-B3F1-E3FD6975B549}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{E084271B-5102-46CA-BE6A-B4E1D89AE9A3}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{58439126-DAA2-49DF-9B0C-FD60CD573C83}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{CD9B502D-312B-4218-BA55-41A13AB300E8}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{29C8EE78-BC6D-4D2D-BA42-3A1A45EC0096}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{AF1F93B3-7D72-4328-AB61-0255A2508644}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{C5673770-FFFE-4A9B-BBE7-DE7CE0C38B8C}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{B5B153B8-73A9-43C0-A970-5C7713595E94}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{B986FE6C-7618-4826-90C2-80DCABF8FC4E}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{B64AFCBF-2172-4223-B149-6E9B340B4EF9}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{1C9E60DF-16AF-4108-8EBC-FD2188321680}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{6BFB4C02-1097-40C9-9217-ADAA1FDFD1F6}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{5EFD1353-6D55-42E1-A7A3-CFAB2E244F0C}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{0CEE35ED-672E-4F8C-8656-D7E8636384BB}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{E4202853-B5C0-4BA2-8A1E-CA1E84A6FCFB}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{C385271A-B3C0-4E84-A632-3C8F6437EC74}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{9BC551BC-88DD-4EBD-96E1-EBAC47EDAC4C}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{2F4568E5-31FC-45B4-9E08-C09983AB8554}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{889B9349-DC3D-4FB5-BD9B-9255B0DEB160}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{05F7E2BC-5900-4D6B-8E56-FDEB4609004E}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{9B179A54-72A9-45DD-96A9-165EBE85997E}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{BA02A9A3-7FC0-412E-ACD8-2DE257FC3BB8}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{3EF71326-1AF7-4D03-9B5A-5EF2F2632084}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{8FABFE51-4924-4C16-A82C-A551940E7AE3}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{1E0CC394-C3ED-48D2-A333-4345AB5E88D6}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{46BDD443-98C8-45D3-A7D8-F6785E911374}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{C7322890-8CEB-49C6-A399-30473F24EC47}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{DF5113DB-AF44-46FC-BD1C-004259FE1E46}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{AFC49FB9-E6F6-425D-A4F8-AF67DC742DBB}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{95758C4D-3EC4-4D00-A330-67D3B824AA3B}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{BFB4F511-B042-4A52-8348-DEF2DDFFB274}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{F0661BCA-41E5-4345-B031-90C3678C0BBA}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{C812D66D-92B3-4F3D-ACCA-F02CC4491533}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{12792CAE-4CF7-4930-8086-B768676E4BDF}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{B8EC95CB-84E2-4199-9460-8D4B12797C76}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{DB17285E-F840-4D6E-B1ED-76B59B0F6C32}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{296FB3F8-822A-4E06-9967-DF9E326482FF}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{CE0BC54E-4B01-481C-AC0E-C14FF643DB03}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{A1B01FDC-43D2-40E5-AD63-0C20F8217388}"/>
+    <hyperlink ref="U48" r:id="rId167" xr:uid="{C38CF517-34E5-41FA-A361-5EF23BC1C3A5}"/>
+    <hyperlink ref="V48" r:id="rId168" xr:uid="{77FD05FC-73FB-4F7C-AAA0-5FF5CED56608}"/>
+    <hyperlink ref="W48" r:id="rId169" xr:uid="{C1C180AF-F19E-43F1-9084-9173A47774B1}"/>
+    <hyperlink ref="X48" r:id="rId170" xr:uid="{EE0DD63B-2AFF-4ED0-904F-7E384C052377}"/>
+    <hyperlink ref="U49" r:id="rId171" xr:uid="{20E631F9-2B0C-4CDA-A5C6-8BA11AF7E247}"/>
+    <hyperlink ref="V49" r:id="rId172" xr:uid="{C8E2D86C-C898-4D27-952A-C3C1EDBFFEAF}"/>
+    <hyperlink ref="W49" r:id="rId173" xr:uid="{32A687A4-CE0A-48DE-97A9-0B1479A78D55}"/>
+    <hyperlink ref="X49" r:id="rId174" xr:uid="{901A7E71-4A94-40C9-B577-FCAB92593CC8}"/>
+    <hyperlink ref="U50" r:id="rId175" xr:uid="{35A36B82-DF3E-4D98-B543-FFA4AEF73B8D}"/>
+    <hyperlink ref="V50" r:id="rId176" xr:uid="{1CFFEF07-6327-45A1-93C7-31600551CCDA}"/>
+    <hyperlink ref="X50" r:id="rId177" xr:uid="{D7CFE948-B2D5-408E-B42E-7F8AE2C9D59D}"/>
+    <hyperlink ref="U51" r:id="rId178" xr:uid="{D9718A02-3A49-4BEB-854B-C095B9F76C31}"/>
+    <hyperlink ref="V51" r:id="rId179" xr:uid="{A138B24F-AA46-431F-BCDF-35E8F473CE7F}"/>
+    <hyperlink ref="W51" r:id="rId180" xr:uid="{59C6F935-9436-450B-A9B2-B328183F5E52}"/>
+    <hyperlink ref="X51" r:id="rId181" xr:uid="{4C1AE58A-7E4D-48AA-B294-9A3F96411DB7}"/>
+    <hyperlink ref="U52" r:id="rId182" xr:uid="{950F25AB-F90F-45A5-A2CD-A7F1893046B3}"/>
+    <hyperlink ref="V52" r:id="rId183" xr:uid="{6E11E7D2-1A13-4208-9CEE-E915FC973AA9}"/>
+    <hyperlink ref="W52" r:id="rId184" xr:uid="{5653FA69-B1A0-46BD-A0F6-7AB67CF14EB7}"/>
+    <hyperlink ref="X52" r:id="rId185" xr:uid="{D9131B1C-B4CE-4F46-B3CA-7B833B2FEE6D}"/>
+    <hyperlink ref="U53" r:id="rId186" xr:uid="{FF14CCAD-B305-4779-92AF-BA71914CB200}"/>
+    <hyperlink ref="V53" r:id="rId187" xr:uid="{2BC456AD-A5E9-463F-BF47-9ADBA1D534EA}"/>
+    <hyperlink ref="W53" r:id="rId188" xr:uid="{7AD421DE-50B0-4E24-98A2-ABECFA638C0D}"/>
+    <hyperlink ref="X53" r:id="rId189" xr:uid="{B204C1C1-D076-4A5F-B505-7CA4A9BBA18E}"/>
+    <hyperlink ref="U54" r:id="rId190" xr:uid="{7FFF031B-FD50-4ED5-B1B0-F277622CC50E}"/>
+    <hyperlink ref="V54" r:id="rId191" xr:uid="{97672537-630A-42E2-A9B7-70F4785B5B12}"/>
+    <hyperlink ref="W54" r:id="rId192" xr:uid="{62EC8669-543A-4117-8984-14A1B0B6EA6E}"/>
+    <hyperlink ref="X54" r:id="rId193" xr:uid="{C33E003D-753F-4CAF-965F-C977A680DAA5}"/>
+    <hyperlink ref="U55" r:id="rId194" xr:uid="{1434C0FF-4C18-4B6F-9B99-49E461E2E81B}"/>
+    <hyperlink ref="V55" r:id="rId195" xr:uid="{2B11A316-756D-4CC5-A5E9-0F3B34FEF66B}"/>
+    <hyperlink ref="W55" r:id="rId196" xr:uid="{A841B1CC-B3E3-46B3-84CC-34672B0E950B}"/>
+    <hyperlink ref="X55" r:id="rId197" xr:uid="{478340C6-9F40-497C-A656-EF9F4B21CDD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId178"/>
+    <tablePart r:id="rId198"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/BBDD_Supervisores.xlsx
+++ b/data/BBDD_Supervisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AuditoriasTerreno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC540340-D94D-4040-9A96-B7ED2E5CF293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC87F5E3-C78D-4A39-A2EE-F496D551C052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="493">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1668,6 +1668,54 @@
   <si>
     <t xml:space="preserve">Técnico cumple con protocolos
 </t>
+  </si>
+  <si>
+    <t>1-3NZB9JSU</t>
+  </si>
+  <si>
+    <t>Maria Luisa Bombal 392, Estacion Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin Cabezas </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14XCT5GDoYrV01X7yoQluzp5OUtgah7l6</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vuwsc2hwutUdhauSLmv04RBGPlbbjenr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1tBvmHzuC4Wjp_A4FYcFp3v1-K1fB1EOk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1kS62xVDRxAHj-qrD241KERePfDz5zKW8</t>
+  </si>
+  <si>
+    <t>No instala pasa muros, no utiliza one click</t>
+  </si>
+  <si>
+    <t>1-3NZ3J33L</t>
+  </si>
+  <si>
+    <t>Concon 67 eficio k dpto 22, Estacion Central</t>
+  </si>
+  <si>
+    <t>Ana Valdivia</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Hrh8W0L8k-2x6IeBtumYCfThesBdNmHE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LFSXTgac_hRUwg3ZMW9p_4VUEozoKB3Z</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=111kDLoHf7xSz4Rye0Hfn_pTFULHAkIst</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1fwXuIedyxLh6p36N2kwV74tpM6WPSBiP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migración 3 play, instalación no se demoró menos de 2 horas, sin embargo problemas con telefonía y gestión con blip se demoró más de 2 horas para solución </t>
   </si>
 </sst>
 </file>
@@ -2367,6 +2415,24 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="166" formatCode="0&quot; / 31&quot;"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2392,24 +2458,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2520,24 +2568,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ55" headerRowDxfId="34">
-  <autoFilter ref="A1:AJ55" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AJ57" headerRowDxfId="34">
+  <autoFilter ref="A1:AJ57" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Marca temporal" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Puntuación" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="N° PETICIÓN " dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre Técnico" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SUPERVISOR" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Se ejecuto la actividad" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Se concreta auditoria?" dataDxfId="24"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Motivo de la derivación" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Auditoria" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actividad" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Instala drop con soportes" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="DIRECCIÓN (Calle - Numero) " dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Instala Pasa-muros " dataDxfId="19"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Roseta Óptica en norma y atornillada " dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Repetidor Cableado" dataDxfId="32"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Cantidad Decodificadores" dataDxfId="17"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Capacitación  al Cliente" dataDxfId="16"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Deja Área de Trabajo Limpio " dataDxfId="15"/>
@@ -2556,7 +2604,7 @@
     <tableColumn id="35" xr3:uid="{CF2913D1-167E-463D-9DEB-ADD1D59E4B8D}" name="Reutiliza Instalación " dataDxfId="2"/>
     <tableColumn id="34" xr3:uid="{1C1000A3-E2F8-4E7C-A510-442774329E98}" name="Utiliza Alcohol isopropilico " dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{54579B12-B98C-417C-A72D-BAB0E503080E}" name="Reutiliza Instalación de otra compañía " dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="30" dataCellStyle="Bueno">
+    <tableColumn id="29" xr3:uid="{B3B22204-0EB9-42F6-9D1A-876CFB34A91A}" name="Se llevó a cabo la mesa de trabajo." dataDxfId="31" dataCellStyle="Bueno">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{D5B9DC4A-17D5-4220-A758-C20FA12AC150}" name="Se cerró el proceso con el técnico?" dataCellStyle="Bueno">
@@ -2771,7 +2819,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ55"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -8249,210 +8297,426 @@
         <v>-</v>
       </c>
     </row>
+    <row r="56" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46288.718068784721</v>
+      </c>
+      <c r="B56" s="10">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="T56" s="3">
+        <v>4</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="V56" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="W56" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="X56" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA56" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB56" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="AC56" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH56" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI56" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>SI</v>
+      </c>
+      <c r="AJ56" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46289.385532581015</v>
+      </c>
+      <c r="B57" s="10">
+        <v>8</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="T57" s="3">
+        <v>4</v>
+      </c>
+      <c r="U57" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="V57" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="W57" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="X57" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH57" s="15" t="str">
+        <f>IFERROR(VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$C,2,0),"")</f>
+        <v>SI</v>
+      </c>
+      <c r="AI57" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,3,0)</f>
+        <v>-</v>
+      </c>
+      <c r="AJ57" s="12" t="str">
+        <f>VLOOKUP(Form_Responses[[#This Row],[Nombre Técnico]],'masa de trabajo'!$B:$E,4,0)</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{B3A5F38D-EDDF-4828-9702-C9236BDDA9B7}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{0DBBD551-8C7D-4139-9ED9-5BDE1E334094}"/>
-    <hyperlink ref="W2" r:id="rId3" xr:uid="{ADF2E360-2B97-4F58-A084-246C0C10B92A}"/>
-    <hyperlink ref="X2" r:id="rId4" xr:uid="{36BBE5B7-5D5A-4E82-8C60-D590E2CF7C13}"/>
-    <hyperlink ref="U3" r:id="rId5" xr:uid="{72756C59-CEA6-4F85-BF1F-5222701B2965}"/>
-    <hyperlink ref="V3" r:id="rId6" xr:uid="{F6193FD9-0793-4B78-BFF8-8FBAE0C14110}"/>
-    <hyperlink ref="X3" r:id="rId7" xr:uid="{89DEE9F3-78FD-44EE-A407-B96B8ED63102}"/>
-    <hyperlink ref="U4" r:id="rId8" xr:uid="{BDACBDE8-FA90-45CA-860D-AA595DAE6E8E}"/>
-    <hyperlink ref="V4" r:id="rId9" xr:uid="{D086C867-55E8-4453-ADB6-24592F5D59FF}"/>
-    <hyperlink ref="X4" r:id="rId10" xr:uid="{43A91B99-61AE-4372-9269-E51D66A00DDD}"/>
-    <hyperlink ref="U5" r:id="rId11" xr:uid="{71AEC4F9-BF37-4C31-861B-AF1A43ED7B44}"/>
-    <hyperlink ref="V5" r:id="rId12" xr:uid="{1C6DE4B2-65F1-4133-A433-F41BC76C2387}"/>
-    <hyperlink ref="W5" r:id="rId13" xr:uid="{8FD7B858-0037-42C0-8540-31F5F46D0287}"/>
-    <hyperlink ref="X5" r:id="rId14" xr:uid="{04D79B66-0448-4AEC-AD03-65182619AE84}"/>
-    <hyperlink ref="U6" r:id="rId15" xr:uid="{2DD75C4A-343D-4A6F-A3C6-5E6223FCE922}"/>
-    <hyperlink ref="V6" r:id="rId16" xr:uid="{EDBD85DD-A477-4DD7-A907-0C9D82505968}"/>
-    <hyperlink ref="W6" r:id="rId17" xr:uid="{A3B8A259-C1EF-4184-A8C9-F7D0A82BF7FD}"/>
-    <hyperlink ref="X6" r:id="rId18" xr:uid="{326C3368-D659-47BE-A645-39811A8E47C9}"/>
-    <hyperlink ref="U7" r:id="rId19" xr:uid="{C33BF675-F160-41AF-933D-BE0313775D8A}"/>
-    <hyperlink ref="V7" r:id="rId20" xr:uid="{791AAB93-ABBE-416E-B98F-75377C9EA140}"/>
-    <hyperlink ref="X7" r:id="rId21" xr:uid="{4064B3F9-3D52-48AB-AA9B-A75BADD14785}"/>
-    <hyperlink ref="U8" r:id="rId22" xr:uid="{0A8F9A9D-58B8-439B-807D-EA61FCC8B500}"/>
-    <hyperlink ref="V8" r:id="rId23" xr:uid="{1B9377A0-3A0A-4B99-890B-CB6C6DDCD3DE}"/>
-    <hyperlink ref="W8" r:id="rId24" xr:uid="{B2350013-22C1-4AD2-8F6A-A3A3D475AE8F}"/>
-    <hyperlink ref="X8" r:id="rId25" xr:uid="{0F4EEFFD-E65E-4FD2-ACBF-063353BCF6BC}"/>
-    <hyperlink ref="U9" r:id="rId26" xr:uid="{89246D6F-54E8-444E-B3B4-725DEB9B531E}"/>
-    <hyperlink ref="V9" r:id="rId27" xr:uid="{C711B2D4-B9C4-46DF-B46A-276207CAE1D2}"/>
-    <hyperlink ref="W9" r:id="rId28" xr:uid="{F09D6CCE-581E-44DB-B382-3A31BA02F0F0}"/>
-    <hyperlink ref="X9" r:id="rId29" xr:uid="{A859C2E8-F4E1-4110-9911-6188EF7DCC95}"/>
-    <hyperlink ref="U10" r:id="rId30" xr:uid="{7A2017B3-9B48-42CD-9461-EAFE1C4FD378}"/>
-    <hyperlink ref="V10" r:id="rId31" xr:uid="{07EDE847-D1E0-467D-97FF-4E57CADF23D8}"/>
-    <hyperlink ref="X10" r:id="rId32" xr:uid="{9014AB93-6E34-4800-B759-1643FD662C1D}"/>
-    <hyperlink ref="U11" r:id="rId33" xr:uid="{9D94A5CA-036C-45BC-8678-EBC36C446B6A}"/>
-    <hyperlink ref="V11" r:id="rId34" xr:uid="{5EE07356-74A4-436E-B5FB-27AFD76E88FC}"/>
-    <hyperlink ref="W11" r:id="rId35" xr:uid="{957EC399-D4D7-4CB5-83E6-53D9A4B6B13E}"/>
-    <hyperlink ref="X11" r:id="rId36" xr:uid="{297CC1DB-ACE7-4E0E-A35F-533150A2B6D1}"/>
-    <hyperlink ref="U13" r:id="rId37" xr:uid="{1BB6373F-AC5D-4F2B-875D-7E5E42151527}"/>
-    <hyperlink ref="V13" r:id="rId38" xr:uid="{D3837138-72C0-426D-89F0-0C19850E1F01}"/>
-    <hyperlink ref="W13" r:id="rId39" xr:uid="{7D3CED0C-8C48-4E42-B42E-48735E2A4066}"/>
-    <hyperlink ref="X13" r:id="rId40" xr:uid="{B2995FF1-1CD9-401D-B851-2518B19EE9F6}"/>
-    <hyperlink ref="W14" r:id="rId41" xr:uid="{E748B020-A150-4129-9B73-74526908DE75}"/>
-    <hyperlink ref="X14" r:id="rId42" xr:uid="{0A0818DE-4D47-4797-8078-D4E3714FE21E}"/>
-    <hyperlink ref="U15" r:id="rId43" xr:uid="{C47DA0BA-66C6-4E06-B8D6-654A01B71AC5}"/>
-    <hyperlink ref="V15" r:id="rId44" xr:uid="{B971A77D-07C6-47E8-842B-EBCC2B6EEE75}"/>
-    <hyperlink ref="X15" r:id="rId45" xr:uid="{8C36CC5C-8593-443C-BE70-E1B24EC96CC1}"/>
-    <hyperlink ref="U16" r:id="rId46" xr:uid="{AFCCFB44-51E4-4765-ABCD-C78E65C58F09}"/>
-    <hyperlink ref="V16" r:id="rId47" xr:uid="{34AD1948-8C8F-472C-B392-0D8C3D62FF76}"/>
-    <hyperlink ref="W16" r:id="rId48" xr:uid="{A51C0DF1-5B78-4EB1-9183-A5E0C9AA7F5A}"/>
-    <hyperlink ref="X16" r:id="rId49" xr:uid="{D8ECE85C-8B29-4A80-A51E-C66000C26C97}"/>
-    <hyperlink ref="U17" r:id="rId50" xr:uid="{B93A55FD-4F61-443C-91E9-CEEE21EEE85A}"/>
-    <hyperlink ref="V17" r:id="rId51" xr:uid="{6B04102D-7C33-4072-8B00-A865E399C755}"/>
-    <hyperlink ref="X17" r:id="rId52" xr:uid="{24081079-3941-4058-B74B-E24034383CC7}"/>
-    <hyperlink ref="U18" r:id="rId53" xr:uid="{6F49DB97-AB04-461F-B3D0-6E6FF1213F10}"/>
-    <hyperlink ref="V18" r:id="rId54" xr:uid="{9B3783AA-EE0F-4BFF-8A44-03986686CDE9}"/>
-    <hyperlink ref="W18" r:id="rId55" xr:uid="{25C9ECAD-8FEA-4483-B0ED-633016342628}"/>
-    <hyperlink ref="X18" r:id="rId56" xr:uid="{09AD9FFE-7ADA-4B2D-9DB6-44397DFD2303}"/>
-    <hyperlink ref="U19" r:id="rId57" xr:uid="{FB911DC9-C0E3-4785-A075-9D1FA301E83E}"/>
-    <hyperlink ref="V19" r:id="rId58" xr:uid="{C5E1F554-4DB6-4155-A995-B5CD912B6929}"/>
-    <hyperlink ref="W19" r:id="rId59" xr:uid="{D30CB38E-C2A6-477E-BEE6-73E8B86E1A89}"/>
-    <hyperlink ref="X19" r:id="rId60" xr:uid="{1B974ACE-D3E7-4D2A-99B5-87FBB8912EAD}"/>
-    <hyperlink ref="U20" r:id="rId61" xr:uid="{D5BF16D5-5E77-4AE5-98CC-56481098CF96}"/>
-    <hyperlink ref="V20" r:id="rId62" xr:uid="{A413F3A8-E91F-4186-9013-5D6C07EDD444}"/>
-    <hyperlink ref="W20" r:id="rId63" xr:uid="{626E6DB1-E61F-4A17-9E63-72FB8A714CF1}"/>
-    <hyperlink ref="X20" r:id="rId64" xr:uid="{0DCD3BD5-C312-4A90-85AE-6B93DA4831D8}"/>
-    <hyperlink ref="U21" r:id="rId65" xr:uid="{7589D367-014B-4EBD-B01F-CBB244E262D7}"/>
-    <hyperlink ref="V21" r:id="rId66" xr:uid="{3DEFAFB1-1827-4C71-AA39-4F79AB10CBC3}"/>
-    <hyperlink ref="X21" r:id="rId67" xr:uid="{1935C7C7-16D5-4962-84FE-96CB298A1B01}"/>
-    <hyperlink ref="U22" r:id="rId68" xr:uid="{617E869E-F49B-4F60-8A31-F001E08D8FA4}"/>
-    <hyperlink ref="V22" r:id="rId69" xr:uid="{90254925-5566-43F5-9B2E-36D595044B96}"/>
-    <hyperlink ref="W22" r:id="rId70" xr:uid="{A38BB7DF-DC5C-40AB-8FF9-4C8CD4A068A6}"/>
-    <hyperlink ref="X22" r:id="rId71" xr:uid="{7F577F91-B9AC-4BC5-93FE-397F937B69C8}"/>
-    <hyperlink ref="U23" r:id="rId72" xr:uid="{3FBD07D9-794F-49BE-B021-A6E40B8293BE}"/>
-    <hyperlink ref="V23" r:id="rId73" xr:uid="{606361BF-1DDF-423F-B72A-3F0934C929E1}"/>
-    <hyperlink ref="W23" r:id="rId74" xr:uid="{7D616A24-973D-46D3-BD21-24610A72EC2C}"/>
-    <hyperlink ref="X23" r:id="rId75" xr:uid="{F403BDB0-6E22-4E04-93CD-53E45844E9BD}"/>
-    <hyperlink ref="U24" r:id="rId76" xr:uid="{DA8D3516-E373-425D-B187-A7988FDCABB0}"/>
-    <hyperlink ref="V24" r:id="rId77" xr:uid="{054E9506-4713-4490-BEF2-7113BBDFB4D4}"/>
-    <hyperlink ref="W24" r:id="rId78" xr:uid="{B914E51B-DE4B-4078-B648-333B67EE76A1}"/>
-    <hyperlink ref="X24" r:id="rId79" xr:uid="{9437CCE1-0C88-47D5-AE76-33B1516948DC}"/>
-    <hyperlink ref="U25" r:id="rId80" xr:uid="{481B7474-922B-455B-B6F0-1AF397E0A09E}"/>
-    <hyperlink ref="V25" r:id="rId81" xr:uid="{7D862C7A-4DA8-4C80-9BCE-9D4F3DA0EDB0}"/>
-    <hyperlink ref="X25" r:id="rId82" xr:uid="{F64A4717-4587-4C2D-A3DC-8ED0586790F8}"/>
-    <hyperlink ref="U26" r:id="rId83" xr:uid="{F19ADEA3-60EC-4310-8CF8-35C3430A1687}"/>
-    <hyperlink ref="V26" r:id="rId84" xr:uid="{B7AB6255-DDC7-4F76-8FCA-B86C3323875A}"/>
-    <hyperlink ref="W26" r:id="rId85" xr:uid="{134E78B0-F7A0-404B-B11F-E50F3CC92630}"/>
-    <hyperlink ref="U27" r:id="rId86" xr:uid="{625D8FAC-B648-4088-A6AA-81D0861AFC3B}"/>
-    <hyperlink ref="V27" r:id="rId87" xr:uid="{DD8D8B68-F9A7-4280-A574-724EE3504AC2}"/>
-    <hyperlink ref="W27" r:id="rId88" xr:uid="{46EE0927-9FFF-426A-BF64-7E3B200C6277}"/>
-    <hyperlink ref="X27" r:id="rId89" xr:uid="{4EFAC31D-C0B2-4178-98F7-08AF216FBBA0}"/>
-    <hyperlink ref="U28" r:id="rId90" xr:uid="{69841135-B4E5-46CD-80F9-B2276B921FDA}"/>
-    <hyperlink ref="V28" r:id="rId91" xr:uid="{5B91C613-A24E-4B87-B635-11F46013AA99}"/>
-    <hyperlink ref="W28" r:id="rId92" xr:uid="{DAB71918-2A28-4E73-99B9-5F6DC1981716}"/>
-    <hyperlink ref="X28" r:id="rId93" xr:uid="{37298348-8393-4E58-BF21-0ADD54C30B43}"/>
-    <hyperlink ref="U29" r:id="rId94" xr:uid="{14BD1455-C7DE-4A10-B662-0863D92E30EB}"/>
-    <hyperlink ref="V29" r:id="rId95" xr:uid="{DEDEC98B-A9D9-465C-A9E0-E0661456ABE8}"/>
-    <hyperlink ref="W29" r:id="rId96" xr:uid="{15E3A5D2-3A09-430C-AC1B-A53B3244F14B}"/>
-    <hyperlink ref="X29" r:id="rId97" xr:uid="{33FAD053-7B3D-450A-8014-B1B93476EB87}"/>
-    <hyperlink ref="U30" r:id="rId98" xr:uid="{2BC70F2B-C42E-4081-A865-CAED98225680}"/>
-    <hyperlink ref="V30" r:id="rId99" xr:uid="{819C9EF9-2A2F-441D-B1A6-7FCD95C9E72C}"/>
-    <hyperlink ref="W30" r:id="rId100" xr:uid="{032D570A-87A6-43AC-B32B-4E26D665E4BB}"/>
-    <hyperlink ref="X30" r:id="rId101" xr:uid="{E5BAC028-569D-4724-AA2B-A303C682EBDA}"/>
-    <hyperlink ref="U31" r:id="rId102" xr:uid="{F7748380-CAB6-4192-BD85-07AE76A18A36}"/>
-    <hyperlink ref="V31" r:id="rId103" xr:uid="{8383526A-9DD5-4777-8356-C38E3EE7EFA9}"/>
-    <hyperlink ref="W31" r:id="rId104" xr:uid="{2C41F98F-CD32-4934-884D-39ABC3AA39BD}"/>
-    <hyperlink ref="X31" r:id="rId105" xr:uid="{00D5BF34-479F-49F0-B76D-609BD69460D8}"/>
-    <hyperlink ref="U32" r:id="rId106" xr:uid="{B3811D3A-2AD7-45FA-A428-868FFB93E7B6}"/>
-    <hyperlink ref="V32" r:id="rId107" xr:uid="{4353677B-A942-4B87-913C-4DBCB42F9E52}"/>
-    <hyperlink ref="W32" r:id="rId108" xr:uid="{33B58678-09CE-4E06-9458-35E3192DE525}"/>
-    <hyperlink ref="X32" r:id="rId109" xr:uid="{7B57022A-B29D-4A18-8FCA-68553821CEA7}"/>
-    <hyperlink ref="U33" r:id="rId110" xr:uid="{9EFBA8B9-706D-4883-8FAF-05DECBD32F71}"/>
-    <hyperlink ref="V33" r:id="rId111" xr:uid="{B332B00B-020E-4874-B5FE-FAC2957E038B}"/>
-    <hyperlink ref="W33" r:id="rId112" xr:uid="{759EB46D-E26B-4F44-AC88-CBE7E86A58AB}"/>
-    <hyperlink ref="X33" r:id="rId113" xr:uid="{182509CF-B2FA-4DCE-8D62-2F22FFB08654}"/>
-    <hyperlink ref="U34" r:id="rId114" xr:uid="{6DF4C7AA-250E-4DC5-AED0-B16700050F91}"/>
-    <hyperlink ref="V34" r:id="rId115" xr:uid="{D29C034F-96B6-45E6-BDD8-521FB7936400}"/>
-    <hyperlink ref="W34" r:id="rId116" xr:uid="{CE3A9D89-78E7-40A1-B669-C6147493E290}"/>
-    <hyperlink ref="X34" r:id="rId117" xr:uid="{7351CA86-2A1D-4CC2-8C2B-B471F138062B}"/>
-    <hyperlink ref="U35" r:id="rId118" xr:uid="{B9F13B63-D6DE-413C-A65E-775C45D1DE4F}"/>
-    <hyperlink ref="V35" r:id="rId119" xr:uid="{343555E6-FC46-4C94-93D8-DB38D42D937A}"/>
-    <hyperlink ref="W35" r:id="rId120" xr:uid="{47E853F4-3ECD-4B0E-9BD8-D2F6A34B9A9A}"/>
-    <hyperlink ref="X35" r:id="rId121" xr:uid="{1A421245-0304-4810-BF05-E809F398E76D}"/>
-    <hyperlink ref="U36" r:id="rId122" xr:uid="{E47F4A91-3CD1-4ACA-9C89-67A162236878}"/>
-    <hyperlink ref="V36" r:id="rId123" xr:uid="{44858AD6-57F2-4C8B-82D1-D0CF96B15B9F}"/>
-    <hyperlink ref="X36" r:id="rId124" xr:uid="{D1A4C8F3-5D12-45EC-AAD3-39D577D81B18}"/>
-    <hyperlink ref="U37" r:id="rId125" xr:uid="{DE9D6634-E1A8-4A7A-B9B8-543CCBB11B53}"/>
-    <hyperlink ref="V37" r:id="rId126" xr:uid="{C4DDA06C-AEFA-4409-B622-AEDFB36A4FE6}"/>
-    <hyperlink ref="X37" r:id="rId127" xr:uid="{D018DADA-D92A-4053-8B42-0CF3D45FE7EB}"/>
-    <hyperlink ref="U38" r:id="rId128" xr:uid="{72A79916-B101-45B8-B3F1-E3FD6975B549}"/>
-    <hyperlink ref="V38" r:id="rId129" xr:uid="{E084271B-5102-46CA-BE6A-B4E1D89AE9A3}"/>
-    <hyperlink ref="X38" r:id="rId130" xr:uid="{58439126-DAA2-49DF-9B0C-FD60CD573C83}"/>
-    <hyperlink ref="U39" r:id="rId131" xr:uid="{CD9B502D-312B-4218-BA55-41A13AB300E8}"/>
-    <hyperlink ref="V39" r:id="rId132" xr:uid="{29C8EE78-BC6D-4D2D-BA42-3A1A45EC0096}"/>
-    <hyperlink ref="W39" r:id="rId133" xr:uid="{AF1F93B3-7D72-4328-AB61-0255A2508644}"/>
-    <hyperlink ref="X39" r:id="rId134" xr:uid="{C5673770-FFFE-4A9B-BBE7-DE7CE0C38B8C}"/>
-    <hyperlink ref="U40" r:id="rId135" xr:uid="{B5B153B8-73A9-43C0-A970-5C7713595E94}"/>
-    <hyperlink ref="V40" r:id="rId136" xr:uid="{B986FE6C-7618-4826-90C2-80DCABF8FC4E}"/>
-    <hyperlink ref="W40" r:id="rId137" xr:uid="{B64AFCBF-2172-4223-B149-6E9B340B4EF9}"/>
-    <hyperlink ref="X40" r:id="rId138" xr:uid="{1C9E60DF-16AF-4108-8EBC-FD2188321680}"/>
-    <hyperlink ref="U41" r:id="rId139" xr:uid="{6BFB4C02-1097-40C9-9217-ADAA1FDFD1F6}"/>
-    <hyperlink ref="V41" r:id="rId140" xr:uid="{5EFD1353-6D55-42E1-A7A3-CFAB2E244F0C}"/>
-    <hyperlink ref="W41" r:id="rId141" xr:uid="{0CEE35ED-672E-4F8C-8656-D7E8636384BB}"/>
-    <hyperlink ref="X41" r:id="rId142" xr:uid="{E4202853-B5C0-4BA2-8A1E-CA1E84A6FCFB}"/>
-    <hyperlink ref="U42" r:id="rId143" xr:uid="{C385271A-B3C0-4E84-A632-3C8F6437EC74}"/>
-    <hyperlink ref="V42" r:id="rId144" xr:uid="{9BC551BC-88DD-4EBD-96E1-EBAC47EDAC4C}"/>
-    <hyperlink ref="W42" r:id="rId145" xr:uid="{2F4568E5-31FC-45B4-9E08-C09983AB8554}"/>
-    <hyperlink ref="X42" r:id="rId146" xr:uid="{889B9349-DC3D-4FB5-BD9B-9255B0DEB160}"/>
-    <hyperlink ref="U43" r:id="rId147" xr:uid="{05F7E2BC-5900-4D6B-8E56-FDEB4609004E}"/>
-    <hyperlink ref="V43" r:id="rId148" xr:uid="{9B179A54-72A9-45DD-96A9-165EBE85997E}"/>
-    <hyperlink ref="W43" r:id="rId149" xr:uid="{BA02A9A3-7FC0-412E-ACD8-2DE257FC3BB8}"/>
-    <hyperlink ref="X43" r:id="rId150" xr:uid="{3EF71326-1AF7-4D03-9B5A-5EF2F2632084}"/>
-    <hyperlink ref="U44" r:id="rId151" xr:uid="{8FABFE51-4924-4C16-A82C-A551940E7AE3}"/>
-    <hyperlink ref="V44" r:id="rId152" xr:uid="{1E0CC394-C3ED-48D2-A333-4345AB5E88D6}"/>
-    <hyperlink ref="W44" r:id="rId153" xr:uid="{46BDD443-98C8-45D3-A7D8-F6785E911374}"/>
-    <hyperlink ref="X44" r:id="rId154" xr:uid="{C7322890-8CEB-49C6-A399-30473F24EC47}"/>
-    <hyperlink ref="U45" r:id="rId155" xr:uid="{DF5113DB-AF44-46FC-BD1C-004259FE1E46}"/>
-    <hyperlink ref="V45" r:id="rId156" xr:uid="{AFC49FB9-E6F6-425D-A4F8-AF67DC742DBB}"/>
-    <hyperlink ref="W45" r:id="rId157" xr:uid="{95758C4D-3EC4-4D00-A330-67D3B824AA3B}"/>
-    <hyperlink ref="X45" r:id="rId158" xr:uid="{BFB4F511-B042-4A52-8348-DEF2DDFFB274}"/>
-    <hyperlink ref="U46" r:id="rId159" xr:uid="{F0661BCA-41E5-4345-B031-90C3678C0BBA}"/>
-    <hyperlink ref="V46" r:id="rId160" xr:uid="{C812D66D-92B3-4F3D-ACCA-F02CC4491533}"/>
-    <hyperlink ref="W46" r:id="rId161" xr:uid="{12792CAE-4CF7-4930-8086-B768676E4BDF}"/>
-    <hyperlink ref="X46" r:id="rId162" xr:uid="{B8EC95CB-84E2-4199-9460-8D4B12797C76}"/>
-    <hyperlink ref="U47" r:id="rId163" xr:uid="{DB17285E-F840-4D6E-B1ED-76B59B0F6C32}"/>
-    <hyperlink ref="V47" r:id="rId164" xr:uid="{296FB3F8-822A-4E06-9967-DF9E326482FF}"/>
-    <hyperlink ref="W47" r:id="rId165" xr:uid="{CE0BC54E-4B01-481C-AC0E-C14FF643DB03}"/>
-    <hyperlink ref="X47" r:id="rId166" xr:uid="{A1B01FDC-43D2-40E5-AD63-0C20F8217388}"/>
-    <hyperlink ref="U48" r:id="rId167" xr:uid="{C38CF517-34E5-41FA-A361-5EF23BC1C3A5}"/>
-    <hyperlink ref="V48" r:id="rId168" xr:uid="{77FD05FC-73FB-4F7C-AAA0-5FF5CED56608}"/>
-    <hyperlink ref="W48" r:id="rId169" xr:uid="{C1C180AF-F19E-43F1-9084-9173A47774B1}"/>
-    <hyperlink ref="X48" r:id="rId170" xr:uid="{EE0DD63B-2AFF-4ED0-904F-7E384C052377}"/>
-    <hyperlink ref="U49" r:id="rId171" xr:uid="{20E631F9-2B0C-4CDA-A5C6-8BA11AF7E247}"/>
-    <hyperlink ref="V49" r:id="rId172" xr:uid="{C8E2D86C-C898-4D27-952A-C3C1EDBFFEAF}"/>
-    <hyperlink ref="W49" r:id="rId173" xr:uid="{32A687A4-CE0A-48DE-97A9-0B1479A78D55}"/>
-    <hyperlink ref="X49" r:id="rId174" xr:uid="{901A7E71-4A94-40C9-B577-FCAB92593CC8}"/>
-    <hyperlink ref="U50" r:id="rId175" xr:uid="{35A36B82-DF3E-4D98-B543-FFA4AEF73B8D}"/>
-    <hyperlink ref="V50" r:id="rId176" xr:uid="{1CFFEF07-6327-45A1-93C7-31600551CCDA}"/>
-    <hyperlink ref="X50" r:id="rId177" xr:uid="{D7CFE948-B2D5-408E-B42E-7F8AE2C9D59D}"/>
-    <hyperlink ref="U51" r:id="rId178" xr:uid="{D9718A02-3A49-4BEB-854B-C095B9F76C31}"/>
-    <hyperlink ref="V51" r:id="rId179" xr:uid="{A138B24F-AA46-431F-BCDF-35E8F473CE7F}"/>
-    <hyperlink ref="W51" r:id="rId180" xr:uid="{59C6F935-9436-450B-A9B2-B328183F5E52}"/>
-    <hyperlink ref="X51" r:id="rId181" xr:uid="{4C1AE58A-7E4D-48AA-B294-9A3F96411DB7}"/>
-    <hyperlink ref="U52" r:id="rId182" xr:uid="{950F25AB-F90F-45A5-A2CD-A7F1893046B3}"/>
-    <hyperlink ref="V52" r:id="rId183" xr:uid="{6E11E7D2-1A13-4208-9CEE-E915FC973AA9}"/>
-    <hyperlink ref="W52" r:id="rId184" xr:uid="{5653FA69-B1A0-46BD-A0F6-7AB67CF14EB7}"/>
-    <hyperlink ref="X52" r:id="rId185" xr:uid="{D9131B1C-B4CE-4F46-B3CA-7B833B2FEE6D}"/>
-    <hyperlink ref="U53" r:id="rId186" xr:uid="{FF14CCAD-B305-4779-92AF-BA71914CB200}"/>
-    <hyperlink ref="V53" r:id="rId187" xr:uid="{2BC456AD-A5E9-463F-BF47-9ADBA1D534EA}"/>
-    <hyperlink ref="W53" r:id="rId188" xr:uid="{7AD421DE-50B0-4E24-98A2-ABECFA638C0D}"/>
-    <hyperlink ref="X53" r:id="rId189" xr:uid="{B204C1C1-D076-4A5F-B505-7CA4A9BBA18E}"/>
-    <hyperlink ref="U54" r:id="rId190" xr:uid="{7FFF031B-FD50-4ED5-B1B0-F277622CC50E}"/>
-    <hyperlink ref="V54" r:id="rId191" xr:uid="{97672537-630A-42E2-A9B7-70F4785B5B12}"/>
-    <hyperlink ref="W54" r:id="rId192" xr:uid="{62EC8669-543A-4117-8984-14A1B0B6EA6E}"/>
-    <hyperlink ref="X54" r:id="rId193" xr:uid="{C33E003D-753F-4CAF-965F-C977A680DAA5}"/>
-    <hyperlink ref="U55" r:id="rId194" xr:uid="{1434C0FF-4C18-4B6F-9B99-49E461E2E81B}"/>
-    <hyperlink ref="V55" r:id="rId195" xr:uid="{2B11A316-756D-4CC5-A5E9-0F3B34FEF66B}"/>
-    <hyperlink ref="W55" r:id="rId196" xr:uid="{A841B1CC-B3E3-46B3-84CC-34672B0E950B}"/>
-    <hyperlink ref="X55" r:id="rId197" xr:uid="{478340C6-9F40-497C-A656-EF9F4B21CDD2}"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{E8979444-689B-46FD-AE53-A0F191F7B8B9}"/>
+    <hyperlink ref="V2" r:id="rId2" xr:uid="{F8D7F6A2-35EB-4DB8-A8EA-D640C170ECC6}"/>
+    <hyperlink ref="W2" r:id="rId3" xr:uid="{7A5A9C7B-59F3-458B-B1C9-A326F28DF9A0}"/>
+    <hyperlink ref="X2" r:id="rId4" xr:uid="{449483E9-043E-4E85-9273-EBAA2CB9239D}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{46912D59-606A-4C2D-923C-DC353FA71AE1}"/>
+    <hyperlink ref="V3" r:id="rId6" xr:uid="{EEDBC9E1-AEF4-497D-827D-F3B7F19188B2}"/>
+    <hyperlink ref="X3" r:id="rId7" xr:uid="{A85CEE9F-9C04-4E93-8A86-9CD00D3AC51C}"/>
+    <hyperlink ref="U4" r:id="rId8" xr:uid="{6E1A4C31-1F89-4E4F-86BD-5B948D58575A}"/>
+    <hyperlink ref="V4" r:id="rId9" xr:uid="{93A1CC50-0551-490B-9915-E8A72AE1ED80}"/>
+    <hyperlink ref="X4" r:id="rId10" xr:uid="{99A3065B-8C15-4814-AEC9-2CCD9459FBC9}"/>
+    <hyperlink ref="U5" r:id="rId11" xr:uid="{B1C7ED3E-A89B-48BB-A4E2-145DAFBFCA93}"/>
+    <hyperlink ref="V5" r:id="rId12" xr:uid="{B589C07D-375D-40E5-A150-BF572C922D49}"/>
+    <hyperlink ref="W5" r:id="rId13" xr:uid="{C65BF8DA-CE21-4734-9DC0-6A973D254756}"/>
+    <hyperlink ref="X5" r:id="rId14" xr:uid="{CAA2DBE7-4418-4644-A99B-2F2695443019}"/>
+    <hyperlink ref="U6" r:id="rId15" xr:uid="{2A6711D3-5A7E-45A2-820B-4D92E5F7A801}"/>
+    <hyperlink ref="V6" r:id="rId16" xr:uid="{1CA3E102-268C-43AB-9C4C-E1E16BC85172}"/>
+    <hyperlink ref="W6" r:id="rId17" xr:uid="{7C3470AF-9F8A-4539-8420-318AC884E9C2}"/>
+    <hyperlink ref="X6" r:id="rId18" xr:uid="{A88FC652-AB51-4213-8029-6A244EDC0298}"/>
+    <hyperlink ref="U7" r:id="rId19" xr:uid="{2245B3C1-7466-4AC5-BA51-23C5049F9731}"/>
+    <hyperlink ref="V7" r:id="rId20" xr:uid="{589D5664-6758-4CB1-A701-ABC70E018AD2}"/>
+    <hyperlink ref="X7" r:id="rId21" xr:uid="{C1764CCD-CAFB-46AB-851F-CF8060C8FCD8}"/>
+    <hyperlink ref="U8" r:id="rId22" xr:uid="{0A841368-D65D-401E-8C68-3EF0DD797298}"/>
+    <hyperlink ref="V8" r:id="rId23" xr:uid="{2FFCBA85-C703-46C4-9636-FC98F15D1731}"/>
+    <hyperlink ref="W8" r:id="rId24" xr:uid="{FA2993EC-B051-49C4-BFB4-1DBF3DAE8FA2}"/>
+    <hyperlink ref="X8" r:id="rId25" xr:uid="{21B61C6F-32C9-474F-B54A-668502129CCC}"/>
+    <hyperlink ref="U9" r:id="rId26" xr:uid="{CD455A92-EC6F-433C-B31A-54CA55B61D93}"/>
+    <hyperlink ref="V9" r:id="rId27" xr:uid="{2456CF8B-B340-4ABC-94F4-9B366D6236E6}"/>
+    <hyperlink ref="W9" r:id="rId28" xr:uid="{10559507-3CDD-4001-BDDF-3F25141D432C}"/>
+    <hyperlink ref="X9" r:id="rId29" xr:uid="{57F7C9B8-23A5-43F2-90EF-2F19B34EBD80}"/>
+    <hyperlink ref="U10" r:id="rId30" xr:uid="{FE549301-990C-401E-B5E3-77CD5D35588F}"/>
+    <hyperlink ref="V10" r:id="rId31" xr:uid="{46661D3B-E759-4EFB-8109-169A82B6C893}"/>
+    <hyperlink ref="X10" r:id="rId32" xr:uid="{D5804800-7891-4DA1-83E8-F5EC47A07D89}"/>
+    <hyperlink ref="U11" r:id="rId33" xr:uid="{CA690510-6A93-4917-A603-2483D61F1F2A}"/>
+    <hyperlink ref="V11" r:id="rId34" xr:uid="{62221443-351F-40FD-B6D1-DF357082A9CF}"/>
+    <hyperlink ref="W11" r:id="rId35" xr:uid="{C254A952-A5BF-4D54-923D-6C64770DECC2}"/>
+    <hyperlink ref="X11" r:id="rId36" xr:uid="{FB1F47D7-AFFE-40C0-B8C2-9A47D2054412}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{754912EF-A1E3-4D78-9274-5897DFCA9B6C}"/>
+    <hyperlink ref="V13" r:id="rId38" xr:uid="{6E1922D7-2A54-4F8C-A8AF-33DD80B05899}"/>
+    <hyperlink ref="W13" r:id="rId39" xr:uid="{0ECFFE20-03CA-4E26-A63F-2C4CB8221088}"/>
+    <hyperlink ref="X13" r:id="rId40" xr:uid="{951A3A4B-513B-4472-AC77-AE462B6E4EA6}"/>
+    <hyperlink ref="W14" r:id="rId41" xr:uid="{ADD87A42-59D9-4E36-A416-106A3CDC52B5}"/>
+    <hyperlink ref="X14" r:id="rId42" xr:uid="{2FCC7FDE-AE45-46FE-83AA-8EF9A13C6689}"/>
+    <hyperlink ref="U15" r:id="rId43" xr:uid="{0F107D39-F717-4F01-8914-61C8E9807A09}"/>
+    <hyperlink ref="V15" r:id="rId44" xr:uid="{ADF61232-4188-432D-B5C9-04AC13A6FBF8}"/>
+    <hyperlink ref="X15" r:id="rId45" xr:uid="{36C843B9-8E23-4C51-9E2F-A47ED1A28111}"/>
+    <hyperlink ref="U16" r:id="rId46" xr:uid="{B2FCAB42-F544-4394-A143-F06A3F4D4667}"/>
+    <hyperlink ref="V16" r:id="rId47" xr:uid="{8176292D-FCAE-4DF0-A3BD-17A8A0569538}"/>
+    <hyperlink ref="W16" r:id="rId48" xr:uid="{0E2E9B59-6AFF-48D6-84EC-83D2CB008134}"/>
+    <hyperlink ref="X16" r:id="rId49" xr:uid="{871F9680-02F1-4423-AE87-9E540CD4CAA5}"/>
+    <hyperlink ref="U17" r:id="rId50" xr:uid="{671CB1E9-5159-4647-8F88-065BA4C36DF1}"/>
+    <hyperlink ref="V17" r:id="rId51" xr:uid="{F27B9EF5-5DE8-4B06-B42D-09B222B447E2}"/>
+    <hyperlink ref="X17" r:id="rId52" xr:uid="{06881458-EC0D-4302-A3F4-55204476B18C}"/>
+    <hyperlink ref="U18" r:id="rId53" xr:uid="{FF55B8AE-1563-4592-8125-646860499571}"/>
+    <hyperlink ref="V18" r:id="rId54" xr:uid="{34FA7B71-9553-417D-85F6-8523E6582C8F}"/>
+    <hyperlink ref="W18" r:id="rId55" xr:uid="{1181A831-CE3C-4D7C-8A94-ACEF9A244A10}"/>
+    <hyperlink ref="X18" r:id="rId56" xr:uid="{FDC33755-A3A1-4449-840B-BBCDBEC341A8}"/>
+    <hyperlink ref="U19" r:id="rId57" xr:uid="{CDF55054-61E4-49B3-BD00-AE72C07AE14A}"/>
+    <hyperlink ref="V19" r:id="rId58" xr:uid="{557285A0-B87F-4B63-AF40-72F8A4E93CB4}"/>
+    <hyperlink ref="W19" r:id="rId59" xr:uid="{3098EC58-4F0E-42A1-92B8-0961CCE20606}"/>
+    <hyperlink ref="X19" r:id="rId60" xr:uid="{8EE05E77-61BA-44C8-8022-B2DCD4496692}"/>
+    <hyperlink ref="U20" r:id="rId61" xr:uid="{E7B2E4FF-123B-44F0-B936-20ABC29902B3}"/>
+    <hyperlink ref="V20" r:id="rId62" xr:uid="{EB1E1B35-2E7B-4AE3-8AB2-ED6B47181F84}"/>
+    <hyperlink ref="W20" r:id="rId63" xr:uid="{27B40189-8D65-4BEB-9C33-48D2877B8238}"/>
+    <hyperlink ref="X20" r:id="rId64" xr:uid="{57DE8DE2-3261-4A28-B628-42AE17075C6E}"/>
+    <hyperlink ref="U21" r:id="rId65" xr:uid="{FF58FFF7-C25D-47BF-AAC4-57B39540E692}"/>
+    <hyperlink ref="V21" r:id="rId66" xr:uid="{1D02B7E6-EA33-4296-8E0F-DE693EC70536}"/>
+    <hyperlink ref="X21" r:id="rId67" xr:uid="{EF38330D-C020-4335-B6E5-AC1F56A23AD2}"/>
+    <hyperlink ref="U22" r:id="rId68" xr:uid="{D07C9153-0D83-4FFE-84F6-847840AE16DA}"/>
+    <hyperlink ref="V22" r:id="rId69" xr:uid="{855C7E4D-0207-47B8-B690-E43435661DE7}"/>
+    <hyperlink ref="W22" r:id="rId70" xr:uid="{480D920E-B81A-419B-9CB0-DF6A7A3266F1}"/>
+    <hyperlink ref="X22" r:id="rId71" xr:uid="{656F439B-B459-4221-A151-FE8C14B6ECFC}"/>
+    <hyperlink ref="U23" r:id="rId72" xr:uid="{433283E5-3AD8-4E68-B3DE-74E58D96B966}"/>
+    <hyperlink ref="V23" r:id="rId73" xr:uid="{992E963C-06BA-45AE-85FA-6A57771C78EC}"/>
+    <hyperlink ref="W23" r:id="rId74" xr:uid="{357E862C-A268-47E5-968A-676365FF8EEF}"/>
+    <hyperlink ref="X23" r:id="rId75" xr:uid="{FC999FCB-93E6-48F2-8537-64ED9B97F55A}"/>
+    <hyperlink ref="U24" r:id="rId76" xr:uid="{2355386A-93C0-4CFF-91BA-92F4DF4EED74}"/>
+    <hyperlink ref="V24" r:id="rId77" xr:uid="{07E0B41C-AB27-4D80-BD73-9D1EA42CCC58}"/>
+    <hyperlink ref="W24" r:id="rId78" xr:uid="{48DD5F0D-A9EF-45C2-B853-5BC9E1E763E1}"/>
+    <hyperlink ref="X24" r:id="rId79" xr:uid="{16F91193-661A-49B3-8E10-6AD58CABA2B1}"/>
+    <hyperlink ref="U25" r:id="rId80" xr:uid="{9B721CD4-D99D-43D7-9F72-9318C6476D0F}"/>
+    <hyperlink ref="V25" r:id="rId81" xr:uid="{E9434E2E-FF98-47A9-B666-18644249FD50}"/>
+    <hyperlink ref="X25" r:id="rId82" xr:uid="{912830AD-C736-4DAD-81CC-49B862EA9E32}"/>
+    <hyperlink ref="U26" r:id="rId83" xr:uid="{C49A16C6-FC11-4513-B9A7-52C420EBE8C4}"/>
+    <hyperlink ref="V26" r:id="rId84" xr:uid="{DD3E0A16-E410-466A-BB56-74698A40705B}"/>
+    <hyperlink ref="W26" r:id="rId85" xr:uid="{B305C15A-79DC-4F1B-8DCD-DA144DCCCCA4}"/>
+    <hyperlink ref="U27" r:id="rId86" xr:uid="{25C7D915-2265-47E4-A536-B2C9FEC2895D}"/>
+    <hyperlink ref="V27" r:id="rId87" xr:uid="{64A4372A-BB79-47B5-9A13-433FFFC5123E}"/>
+    <hyperlink ref="W27" r:id="rId88" xr:uid="{B7E19081-E594-4686-8D7A-3B9CCA54EE30}"/>
+    <hyperlink ref="X27" r:id="rId89" xr:uid="{6B9BBEF5-BA29-486C-AEF3-DA4D8EB23B14}"/>
+    <hyperlink ref="U28" r:id="rId90" xr:uid="{0131FF1D-CC01-40A8-AD8D-060D2917447C}"/>
+    <hyperlink ref="V28" r:id="rId91" xr:uid="{D500C0D2-31E9-48EB-ADD1-1AD095C6F393}"/>
+    <hyperlink ref="W28" r:id="rId92" xr:uid="{43E6C181-B704-4756-AF5E-115EF6C1A63F}"/>
+    <hyperlink ref="X28" r:id="rId93" xr:uid="{8E3FCF5D-C9F0-4363-87B4-32D38CC0BB51}"/>
+    <hyperlink ref="U29" r:id="rId94" xr:uid="{FFFE8F01-C5D0-4986-AB73-3FC97FB115B0}"/>
+    <hyperlink ref="V29" r:id="rId95" xr:uid="{C2BACA83-BC74-4EB5-949C-FFD50C84ED6A}"/>
+    <hyperlink ref="W29" r:id="rId96" xr:uid="{FC2372C9-49A4-447E-A9D1-207DBD3F47EA}"/>
+    <hyperlink ref="X29" r:id="rId97" xr:uid="{59AC22F2-1E85-4931-8057-FAE80942AB79}"/>
+    <hyperlink ref="U30" r:id="rId98" xr:uid="{D42374E5-7B29-4ECE-B418-688C5592369B}"/>
+    <hyperlink ref="V30" r:id="rId99" xr:uid="{65E9A2C9-7DBD-491F-83BB-491BF538BB3D}"/>
+    <hyperlink ref="W30" r:id="rId100" xr:uid="{40E71A4A-0AF1-4D1E-A5CC-BE42F9F7DB78}"/>
+    <hyperlink ref="X30" r:id="rId101" xr:uid="{2D5A90C1-5215-4E51-A507-42ADA1A34603}"/>
+    <hyperlink ref="U31" r:id="rId102" xr:uid="{F088E194-2E5F-4CF3-BCAA-E04276A963E3}"/>
+    <hyperlink ref="V31" r:id="rId103" xr:uid="{074836E1-A204-4584-97C2-015F6868F0BE}"/>
+    <hyperlink ref="W31" r:id="rId104" xr:uid="{BFF50F21-288E-4530-BDB3-1FD4F51E060C}"/>
+    <hyperlink ref="X31" r:id="rId105" xr:uid="{B5B4DE02-BF37-4674-B2F6-7757B59A1D5D}"/>
+    <hyperlink ref="U32" r:id="rId106" xr:uid="{B4D4FFF5-A1B7-4CB7-929A-19717E9D0D0F}"/>
+    <hyperlink ref="V32" r:id="rId107" xr:uid="{F3F6F61A-86AE-48FD-AD00-22FB310ACFCC}"/>
+    <hyperlink ref="W32" r:id="rId108" xr:uid="{73E5A61C-C9E5-4298-B573-882F88468462}"/>
+    <hyperlink ref="X32" r:id="rId109" xr:uid="{BBFAD8EA-2747-4490-84CB-04F9AB169CEB}"/>
+    <hyperlink ref="U33" r:id="rId110" xr:uid="{649BC10A-AE65-4653-B697-BA55745051E3}"/>
+    <hyperlink ref="V33" r:id="rId111" xr:uid="{E73E0AC5-204F-4E36-ABA7-63FFE8E5833B}"/>
+    <hyperlink ref="W33" r:id="rId112" xr:uid="{DC8E7991-7A81-495F-99B3-CD3C0F1B0CC2}"/>
+    <hyperlink ref="X33" r:id="rId113" xr:uid="{B3022C2E-6713-4721-B132-1889B598DF69}"/>
+    <hyperlink ref="U34" r:id="rId114" xr:uid="{03813859-A001-4D37-8B44-62CEE987CF47}"/>
+    <hyperlink ref="V34" r:id="rId115" xr:uid="{1E15C435-57C4-4868-B06D-3FB73403A2C4}"/>
+    <hyperlink ref="W34" r:id="rId116" xr:uid="{38B213E4-BFA9-4A80-81E5-007B230DEFDB}"/>
+    <hyperlink ref="X34" r:id="rId117" xr:uid="{774A7003-15A7-458D-B3A8-1D4E8E570BB6}"/>
+    <hyperlink ref="U35" r:id="rId118" xr:uid="{514E5D97-5821-4055-B156-88948C86156F}"/>
+    <hyperlink ref="V35" r:id="rId119" xr:uid="{69D139DE-D618-426D-88B2-1EE48BF2275B}"/>
+    <hyperlink ref="W35" r:id="rId120" xr:uid="{06DC392E-3815-4384-B5E9-25630BD083CF}"/>
+    <hyperlink ref="X35" r:id="rId121" xr:uid="{B030F6B1-CB5D-40F0-9FFA-9B9031469644}"/>
+    <hyperlink ref="U36" r:id="rId122" xr:uid="{E6C739F4-CF9C-4E19-A6AE-A59D3CCA7222}"/>
+    <hyperlink ref="V36" r:id="rId123" xr:uid="{4E759293-AC9F-41DB-A972-B1493131D507}"/>
+    <hyperlink ref="X36" r:id="rId124" xr:uid="{22C98856-66E3-4530-81B7-7E3E0F1A7201}"/>
+    <hyperlink ref="U37" r:id="rId125" xr:uid="{2382BFDF-1818-4CAE-8034-3E36FF6A5BD0}"/>
+    <hyperlink ref="V37" r:id="rId126" xr:uid="{42E585CF-DFCB-446F-ABB4-777D9BEBE3AE}"/>
+    <hyperlink ref="X37" r:id="rId127" xr:uid="{9625557A-B7D4-4510-8BE8-FAA0C888FFAA}"/>
+    <hyperlink ref="U38" r:id="rId128" xr:uid="{FDF3BB34-7EFC-494B-A857-0D0A234EFB80}"/>
+    <hyperlink ref="V38" r:id="rId129" xr:uid="{11FC893D-8F10-4DB7-B4BF-777178486586}"/>
+    <hyperlink ref="X38" r:id="rId130" xr:uid="{21CBA0E7-BF2D-469A-8D8F-4E669A9101D5}"/>
+    <hyperlink ref="U39" r:id="rId131" xr:uid="{D291B76A-9551-4755-A32B-B077868B28FB}"/>
+    <hyperlink ref="V39" r:id="rId132" xr:uid="{6296CD96-9B16-4AE4-BACC-25494158917A}"/>
+    <hyperlink ref="W39" r:id="rId133" xr:uid="{8FE0590A-6AEE-491A-BD2E-C56A7E8816B4}"/>
+    <hyperlink ref="X39" r:id="rId134" xr:uid="{74391AF9-4BAC-4283-AAEA-5EF4D43E92DF}"/>
+    <hyperlink ref="U40" r:id="rId135" xr:uid="{1D112AE4-0558-44D6-AC93-34E279B34884}"/>
+    <hyperlink ref="V40" r:id="rId136" xr:uid="{E07315C7-CE57-47FB-BDC4-82663FA103A1}"/>
+    <hyperlink ref="W40" r:id="rId137" xr:uid="{10C4641E-3224-4BA3-8C33-ED61339A48B4}"/>
+    <hyperlink ref="X40" r:id="rId138" xr:uid="{9F16A584-81F1-4637-9343-640D8CF395C1}"/>
+    <hyperlink ref="U41" r:id="rId139" xr:uid="{C4C41B59-9B2B-4A63-8F4C-8E2642D72DD9}"/>
+    <hyperlink ref="V41" r:id="rId140" xr:uid="{2794C51B-E5C8-4A0F-9650-9596E8C850CC}"/>
+    <hyperlink ref="W41" r:id="rId141" xr:uid="{2256B853-73E8-4D8C-966A-B58F27395790}"/>
+    <hyperlink ref="X41" r:id="rId142" xr:uid="{39814ADE-A0B5-43F1-A5D4-4AC845AC0808}"/>
+    <hyperlink ref="U42" r:id="rId143" xr:uid="{3454A1ED-BA90-4E89-86BB-CE7CF9E0BA72}"/>
+    <hyperlink ref="V42" r:id="rId144" xr:uid="{09890701-8528-48AD-BE73-F368DC5F0C42}"/>
+    <hyperlink ref="W42" r:id="rId145" xr:uid="{67E64C9A-AF96-4A7A-AFEC-B28C809DCAC5}"/>
+    <hyperlink ref="X42" r:id="rId146" xr:uid="{C8800101-0A12-42D7-B419-3D48492EC29E}"/>
+    <hyperlink ref="U43" r:id="rId147" xr:uid="{D1196DFA-2653-4F25-A1EB-51DE7EC5287B}"/>
+    <hyperlink ref="V43" r:id="rId148" xr:uid="{4236FCC0-D175-4B86-B677-F5A00FA657AA}"/>
+    <hyperlink ref="W43" r:id="rId149" xr:uid="{FF0838AB-50EF-4B07-BD32-82E03D5AEA4B}"/>
+    <hyperlink ref="X43" r:id="rId150" xr:uid="{EDBD20B9-A206-46E4-82B9-C963A8FC6977}"/>
+    <hyperlink ref="U44" r:id="rId151" xr:uid="{F777E625-2368-4B06-A6C7-0D684DAFCE1D}"/>
+    <hyperlink ref="V44" r:id="rId152" xr:uid="{91B44F98-CB22-410B-A5D2-C46674AF9841}"/>
+    <hyperlink ref="W44" r:id="rId153" xr:uid="{0D373F9D-8ABF-487D-9D09-31ED10325B75}"/>
+    <hyperlink ref="X44" r:id="rId154" xr:uid="{06005896-9678-4B49-93F8-407FE35604A4}"/>
+    <hyperlink ref="U45" r:id="rId155" xr:uid="{D1B5837F-3DF2-4E88-9A40-641B023B12C5}"/>
+    <hyperlink ref="V45" r:id="rId156" xr:uid="{0F784948-DA70-4AC7-A735-9B5794C900FC}"/>
+    <hyperlink ref="W45" r:id="rId157" xr:uid="{769D48D2-C204-4294-8BA4-3F8CA082F2DE}"/>
+    <hyperlink ref="X45" r:id="rId158" xr:uid="{551C7F41-9972-4096-B90A-45CE4DDE8C15}"/>
+    <hyperlink ref="U46" r:id="rId159" xr:uid="{907AA86A-21C5-4E4F-9A0E-2B4B714A4287}"/>
+    <hyperlink ref="V46" r:id="rId160" xr:uid="{5BACED19-25DE-484C-9B87-9AA46F84572C}"/>
+    <hyperlink ref="W46" r:id="rId161" xr:uid="{16C26443-A59E-464A-9D89-0064D9B259DF}"/>
+    <hyperlink ref="X46" r:id="rId162" xr:uid="{26E96AEC-84B9-4059-ACA1-BEDF60406BB7}"/>
+    <hyperlink ref="U47" r:id="rId163" xr:uid="{0C08D67A-0AA4-47A2-9A85-9F60087F1FFE}"/>
+    <hyperlink ref="V47" r:id="rId164" xr:uid="{32353774-0DA0-480D-BEE3-A96754057A1A}"/>
+    <hyperlink ref="W47" r:id="rId165" xr:uid="{2EB7FFBF-DF2C-4ACF-9633-B46E2197FDCE}"/>
+    <hyperlink ref="X47" r:id="rId166" xr:uid="{0A93D997-ECE8-45FB-9626-15306ABC7B1E}"/>
+    <hyperlink ref="U48" r:id="rId167" xr:uid="{AB1420AB-B271-4113-9B67-2FB3E15F5FDC}"/>
+    <hyperlink ref="V48" r:id="rId168" xr:uid="{D6785B10-6DD4-4CF5-895E-341F9BDDE256}"/>
+    <hyperlink ref="W48" r:id="rId169" xr:uid="{DA6AB8AE-6683-4A04-AD7E-03E396A2981D}"/>
+    <hyperlink ref="X48" r:id="rId170" xr:uid="{D9CA1A88-A52F-458A-8C2C-88AE33A608E6}"/>
+    <hyperlink ref="U49" r:id="rId171" xr:uid="{56D7F098-43FE-49F2-B761-6D8BD6FD5BB4}"/>
+    <hyperlink ref="V49" r:id="rId172" xr:uid="{C6DDC6D2-CEFB-4459-8F29-BEFBA77DB364}"/>
+    <hyperlink ref="W49" r:id="rId173" xr:uid="{F5956EEB-7E53-48C4-AA87-3F43B1C37818}"/>
+    <hyperlink ref="X49" r:id="rId174" xr:uid="{5DD6646B-873C-4C83-A538-6CAD67222E70}"/>
+    <hyperlink ref="U50" r:id="rId175" xr:uid="{5A986BEB-6586-48D0-8E07-227E7140E482}"/>
+    <hyperlink ref="V50" r:id="rId176" xr:uid="{1DECB395-7DC7-4AA1-943B-A8F81D78B1E7}"/>
+    <hyperlink ref="X50" r:id="rId177" xr:uid="{EB480108-0150-49BC-8D28-F17DFA499303}"/>
+    <hyperlink ref="U51" r:id="rId178" xr:uid="{3FA5303B-68CB-43CF-97E3-482EAE969809}"/>
+    <hyperlink ref="V51" r:id="rId179" xr:uid="{47B77639-F7FE-4DA5-9277-ECAB013297AB}"/>
+    <hyperlink ref="W51" r:id="rId180" xr:uid="{5CA428BC-27E8-4AE2-A3B4-93CEB9CD5BB3}"/>
+    <hyperlink ref="X51" r:id="rId181" xr:uid="{3A2CAC8D-AB02-4FA1-8A4E-988A40B82A54}"/>
+    <hyperlink ref="U52" r:id="rId182" xr:uid="{D00567FA-CAF9-4536-882C-5FBCC054D7E7}"/>
+    <hyperlink ref="V52" r:id="rId183" xr:uid="{901B2E8C-5D22-4832-B53C-249B297238F6}"/>
+    <hyperlink ref="W52" r:id="rId184" xr:uid="{C6FBB57B-7F0F-4198-9A87-34E1C1E1BCF4}"/>
+    <hyperlink ref="X52" r:id="rId185" xr:uid="{CD8FC443-E9F3-4BC4-942A-75D16CA621F6}"/>
+    <hyperlink ref="U53" r:id="rId186" xr:uid="{589BBD7C-93C5-45FE-8FB2-604BB4517009}"/>
+    <hyperlink ref="V53" r:id="rId187" xr:uid="{AC31EDE3-9CA3-4C20-B6FC-52CE9543B81F}"/>
+    <hyperlink ref="W53" r:id="rId188" xr:uid="{CACC7112-7801-4020-89FD-40E7C19C3D8A}"/>
+    <hyperlink ref="X53" r:id="rId189" xr:uid="{008F734D-C27F-4017-AB5B-4B81B7C77303}"/>
+    <hyperlink ref="U54" r:id="rId190" xr:uid="{F608EF9F-9CE9-4F6E-912E-C831B5E3CECD}"/>
+    <hyperlink ref="V54" r:id="rId191" xr:uid="{BA360B94-E664-43F2-B437-3D92CD7D9DA6}"/>
+    <hyperlink ref="W54" r:id="rId192" xr:uid="{E36FCADA-747B-4EBE-9789-1F9852523BE5}"/>
+    <hyperlink ref="X54" r:id="rId193" xr:uid="{958D4D82-E2B6-40D5-9CBC-D00FD53FF55A}"/>
+    <hyperlink ref="U55" r:id="rId194" xr:uid="{6190D080-6D25-46AE-8DF0-1D6ECA2F4859}"/>
+    <hyperlink ref="V55" r:id="rId195" xr:uid="{C915CF92-9CC9-42D6-A89C-69F499FE0CA9}"/>
+    <hyperlink ref="W55" r:id="rId196" xr:uid="{B02435C5-9F3F-4515-B006-FFAEC1B9C131}"/>
+    <hyperlink ref="X55" r:id="rId197" xr:uid="{01C82FA3-F6F4-427A-9F98-101EAF6B895E}"/>
+    <hyperlink ref="U56" r:id="rId198" xr:uid="{F13984EB-8311-4DC1-BD57-C73C62E2C3F2}"/>
+    <hyperlink ref="V56" r:id="rId199" xr:uid="{D0919FAB-09C1-4DD9-9A20-580383B36B18}"/>
+    <hyperlink ref="W56" r:id="rId200" xr:uid="{BA1D962E-30D7-4487-A359-15BFFFC5FE8C}"/>
+    <hyperlink ref="X56" r:id="rId201" xr:uid="{765DC18A-D922-4FF8-BF78-16762430DC89}"/>
+    <hyperlink ref="U57" r:id="rId202" xr:uid="{61BC6840-9F2E-4D19-963D-9A4F02D1975B}"/>
+    <hyperlink ref="V57" r:id="rId203" xr:uid="{3206318E-76F5-46D2-8A0F-54EEA33F6AC9}"/>
+    <hyperlink ref="W57" r:id="rId204" xr:uid="{70AD4A34-202D-47D3-A916-593E5A5A843D}"/>
+    <hyperlink ref="X57" r:id="rId205" xr:uid="{4CA22343-C394-431E-836D-A55A59861DE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId198"/>
+    <tablePart r:id="rId206"/>
   </tableParts>
 </worksheet>
 </file>
